--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GO96"/>
+  <dimension ref="A1:GO107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73183,6 +73183,8039 @@
       <c r="GN96" t="inlineStr"/>
       <c r="GO96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>IsTiBa8d</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>chevalier lucas</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>WUyrShAL</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>meunier thomas</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0hxFjbCm</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>mandi aissa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>YeGIfsnH</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>diakite bafode</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>6kFjexWI</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>alexsandro</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0zzTdK1T</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>gudmundsson gabriel</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>KjBOZTeI</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>sahraoui osame</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>YPYwQXje</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>andre benjamin</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>OADlCrGQ</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>mbappe ethan</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>UZDgIuNN</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>haraldsson hakon arnar</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>CSvtXj2E</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>david jonathan</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>rqDavwpd</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>fofana yahia</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>lvXo8mgi</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>carlens arcus</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>ngxkIxtK</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>bamba abdoulaye</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>dpU7jLLp</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>hountondji cedric</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>ADepyvio</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>lefort jordan</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>f9CImc7o</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>ekomie jacques</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>zshOz5Bl</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>capelle pierrick</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Q1LRmF1l</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>ould khaled zinedine</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>4ErwI0V0</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>belkhdim yassine</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>tSVHHLjn</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>cherif sidiki</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>tIm0BT62</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>abdelli himad</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr">
+        <is>
+          <t>dtOEHzit</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>bayo mohamed</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>dpoNasPg</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>bouaddi ayyoub</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>bB2Nv4qL</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>burlet vincent</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>hl6k3P1f</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>cabella remy</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>rLf7HAcp</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>ilic andrej</t>
+        </is>
+      </c>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>GKEd9ext</t>
+        </is>
+      </c>
+      <c r="BE97" t="inlineStr">
+        <is>
+          <t>mannone vito</t>
+        </is>
+      </c>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>2Nyle1h2</t>
+        </is>
+      </c>
+      <c r="BG97" t="inlineStr">
+        <is>
+          <t>mukau ngal ayel</t>
+        </is>
+      </c>
+      <c r="BH97" t="inlineStr">
+        <is>
+          <t>vBypn8GA</t>
+        </is>
+      </c>
+      <c r="BI97" t="inlineStr">
+        <is>
+          <t>santos tiago</t>
+        </is>
+      </c>
+      <c r="BJ97" t="inlineStr">
+        <is>
+          <t>0l0PGXES</t>
+        </is>
+      </c>
+      <c r="BK97" t="inlineStr">
+        <is>
+          <t>toure ousmane</t>
+        </is>
+      </c>
+      <c r="BL97" t="inlineStr">
+        <is>
+          <t>rgmBFVFk</t>
+        </is>
+      </c>
+      <c r="BM97" t="inlineStr">
+        <is>
+          <t>biumla emmanuel</t>
+        </is>
+      </c>
+      <c r="BN97" t="inlineStr">
+        <is>
+          <t>Yu4ZEgGr</t>
+        </is>
+      </c>
+      <c r="BO97" t="inlineStr">
+        <is>
+          <t>el melali farid</t>
+        </is>
+      </c>
+      <c r="BP97" t="inlineStr">
+        <is>
+          <t>hA8XZuUp</t>
+        </is>
+      </c>
+      <c r="BQ97" t="inlineStr">
+        <is>
+          <t>ferhat zinedine</t>
+        </is>
+      </c>
+      <c r="BR97" t="inlineStr">
+        <is>
+          <t>GAXAKdkE</t>
+        </is>
+      </c>
+      <c r="BS97" t="inlineStr">
+        <is>
+          <t>hanin florent</t>
+        </is>
+      </c>
+      <c r="BT97" t="inlineStr">
+        <is>
+          <t>GGw2OEMr</t>
+        </is>
+      </c>
+      <c r="BU97" t="inlineStr">
+        <is>
+          <t>lepaul esteban</t>
+        </is>
+      </c>
+      <c r="BV97" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="BW97" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="BX97" t="inlineStr">
+        <is>
+          <t>ba3tpFaU</t>
+        </is>
+      </c>
+      <c r="BY97" t="inlineStr">
+        <is>
+          <t>niane ibrahima</t>
+        </is>
+      </c>
+      <c r="BZ97" t="inlineStr">
+        <is>
+          <t>dlgWt8kH</t>
+        </is>
+      </c>
+      <c r="CA97" t="inlineStr">
+        <is>
+          <t>rao lisoa lilian</t>
+        </is>
+      </c>
+      <c r="CB97" t="inlineStr">
+        <is>
+          <t>Agm4z1Gk</t>
+        </is>
+      </c>
+      <c r="CC97" t="inlineStr">
+        <is>
+          <t>zinga melvin</t>
+        </is>
+      </c>
+      <c r="CD97" t="inlineStr">
+        <is>
+          <t>hl6k3P1f</t>
+        </is>
+      </c>
+      <c r="CE97" t="inlineStr">
+        <is>
+          <t>cabella remy</t>
+        </is>
+      </c>
+      <c r="CF97" t="inlineStr">
+        <is>
+          <t>hl6k3P1f</t>
+        </is>
+      </c>
+      <c r="CG97" t="inlineStr">
+        <is>
+          <t>cabella remy</t>
+        </is>
+      </c>
+      <c r="CH97" t="inlineStr">
+        <is>
+          <t>OADlCrGQ</t>
+        </is>
+      </c>
+      <c r="CI97" t="inlineStr">
+        <is>
+          <t>mbappe ethan</t>
+        </is>
+      </c>
+      <c r="CJ97" t="inlineStr">
+        <is>
+          <t>2Nyle1h2</t>
+        </is>
+      </c>
+      <c r="CK97" t="inlineStr">
+        <is>
+          <t>mukau ngal ayel</t>
+        </is>
+      </c>
+      <c r="CL97" t="inlineStr">
+        <is>
+          <t>2Nyle1h2</t>
+        </is>
+      </c>
+      <c r="CM97" t="inlineStr">
+        <is>
+          <t>mukau ngal ayel</t>
+        </is>
+      </c>
+      <c r="CN97" t="inlineStr">
+        <is>
+          <t>UZDgIuNN</t>
+        </is>
+      </c>
+      <c r="CO97" t="inlineStr">
+        <is>
+          <t>haraldsson hakon arnar</t>
+        </is>
+      </c>
+      <c r="CP97" t="inlineStr">
+        <is>
+          <t>vBypn8GA</t>
+        </is>
+      </c>
+      <c r="CQ97" t="inlineStr">
+        <is>
+          <t>santos tiago</t>
+        </is>
+      </c>
+      <c r="CR97" t="inlineStr">
+        <is>
+          <t>vBypn8GA</t>
+        </is>
+      </c>
+      <c r="CS97" t="inlineStr">
+        <is>
+          <t>santos tiago</t>
+        </is>
+      </c>
+      <c r="CT97" t="inlineStr">
+        <is>
+          <t>WUyrShAL</t>
+        </is>
+      </c>
+      <c r="CU97" t="inlineStr">
+        <is>
+          <t>meunier thomas</t>
+        </is>
+      </c>
+      <c r="CV97" t="inlineStr">
+        <is>
+          <t>dtOEHzit</t>
+        </is>
+      </c>
+      <c r="CW97" t="inlineStr">
+        <is>
+          <t>bayo mohamed</t>
+        </is>
+      </c>
+      <c r="CX97" t="inlineStr">
+        <is>
+          <t>dtOEHzit</t>
+        </is>
+      </c>
+      <c r="CY97" t="inlineStr">
+        <is>
+          <t>bayo mohamed</t>
+        </is>
+      </c>
+      <c r="CZ97" t="inlineStr">
+        <is>
+          <t>CSvtXj2E</t>
+        </is>
+      </c>
+      <c r="DA97" t="inlineStr">
+        <is>
+          <t>david jonathan</t>
+        </is>
+      </c>
+      <c r="DB97" t="inlineStr">
+        <is>
+          <t>dpoNasPg</t>
+        </is>
+      </c>
+      <c r="DC97" t="inlineStr">
+        <is>
+          <t>bouaddi ayyoub</t>
+        </is>
+      </c>
+      <c r="DD97" t="inlineStr">
+        <is>
+          <t>dpoNasPg</t>
+        </is>
+      </c>
+      <c r="DE97" t="inlineStr">
+        <is>
+          <t>bouaddi ayyoub</t>
+        </is>
+      </c>
+      <c r="DF97" t="inlineStr">
+        <is>
+          <t>KjBOZTeI</t>
+        </is>
+      </c>
+      <c r="DG97" t="inlineStr">
+        <is>
+          <t>sahraoui osame</t>
+        </is>
+      </c>
+      <c r="DH97" t="inlineStr"/>
+      <c r="DI97" t="inlineStr"/>
+      <c r="DJ97" t="inlineStr"/>
+      <c r="DK97" t="inlineStr"/>
+      <c r="DL97" t="inlineStr"/>
+      <c r="DM97" t="inlineStr"/>
+      <c r="DN97" t="inlineStr">
+        <is>
+          <t>Yu4ZEgGr</t>
+        </is>
+      </c>
+      <c r="DO97" t="inlineStr">
+        <is>
+          <t>el melali farid</t>
+        </is>
+      </c>
+      <c r="DP97" t="inlineStr">
+        <is>
+          <t>Yu4ZEgGr</t>
+        </is>
+      </c>
+      <c r="DQ97" t="inlineStr">
+        <is>
+          <t>el melali farid</t>
+        </is>
+      </c>
+      <c r="DR97" t="inlineStr">
+        <is>
+          <t>Q1LRmF1l</t>
+        </is>
+      </c>
+      <c r="DS97" t="inlineStr">
+        <is>
+          <t>ould khaled zinedine</t>
+        </is>
+      </c>
+      <c r="DT97" t="inlineStr">
+        <is>
+          <t>hA8XZuUp</t>
+        </is>
+      </c>
+      <c r="DU97" t="inlineStr">
+        <is>
+          <t>ferhat zinedine</t>
+        </is>
+      </c>
+      <c r="DV97" t="inlineStr">
+        <is>
+          <t>hA8XZuUp</t>
+        </is>
+      </c>
+      <c r="DW97" t="inlineStr">
+        <is>
+          <t>ferhat zinedine</t>
+        </is>
+      </c>
+      <c r="DX97" t="inlineStr">
+        <is>
+          <t>zshOz5Bl</t>
+        </is>
+      </c>
+      <c r="DY97" t="inlineStr">
+        <is>
+          <t>capelle pierrick</t>
+        </is>
+      </c>
+      <c r="DZ97" t="inlineStr">
+        <is>
+          <t>GGw2OEMr</t>
+        </is>
+      </c>
+      <c r="EA97" t="inlineStr">
+        <is>
+          <t>lepaul esteban</t>
+        </is>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>GGw2OEMr</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>lepaul esteban</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>tSVHHLjn</t>
+        </is>
+      </c>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>cherif sidiki</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr">
+        <is>
+          <t>rgmBFVFk</t>
+        </is>
+      </c>
+      <c r="EG97" t="inlineStr">
+        <is>
+          <t>biumla emmanuel</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>rgmBFVFk</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>biumla emmanuel</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>ngxkIxtK</t>
+        </is>
+      </c>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>bamba abdoulaye</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr">
+        <is>
+          <t>ba3tpFaU</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr">
+        <is>
+          <t>niane ibrahima</t>
+        </is>
+      </c>
+      <c r="EN97" t="inlineStr">
+        <is>
+          <t>ba3tpFaU</t>
+        </is>
+      </c>
+      <c r="EO97" t="inlineStr">
+        <is>
+          <t>niane ibrahima</t>
+        </is>
+      </c>
+      <c r="EP97" t="inlineStr">
+        <is>
+          <t>f9CImc7o</t>
+        </is>
+      </c>
+      <c r="EQ97" t="inlineStr">
+        <is>
+          <t>ekomie jacques</t>
+        </is>
+      </c>
+      <c r="ER97" t="inlineStr"/>
+      <c r="ES97" t="inlineStr"/>
+      <c r="ET97" t="inlineStr"/>
+      <c r="EU97" t="inlineStr"/>
+      <c r="EV97" t="inlineStr"/>
+      <c r="EW97" t="inlineStr"/>
+      <c r="EX97" t="inlineStr">
+        <is>
+          <t>UVRm5Kjk</t>
+        </is>
+      </c>
+      <c r="EY97" t="inlineStr">
+        <is>
+          <t>bentaleb nabil</t>
+        </is>
+      </c>
+      <c r="EZ97" t="inlineStr">
+        <is>
+          <t>AmAtkgFg</t>
+        </is>
+      </c>
+      <c r="FA97" t="inlineStr">
+        <is>
+          <t>gomes angel</t>
+        </is>
+      </c>
+      <c r="FB97" t="inlineStr">
+        <is>
+          <t>QiEHuYPM</t>
+        </is>
+      </c>
+      <c r="FC97" t="inlineStr">
+        <is>
+          <t>allevinah jim</t>
+        </is>
+      </c>
+      <c r="FD97" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="FE97" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="FF97" t="inlineStr"/>
+      <c r="FG97" t="inlineStr"/>
+      <c r="FH97" t="inlineStr">
+        <is>
+          <t>neNU9A9F</t>
+        </is>
+      </c>
+      <c r="FI97" t="inlineStr">
+        <is>
+          <t>ismaily</t>
+        </is>
+      </c>
+      <c r="FJ97" t="inlineStr"/>
+      <c r="FK97" t="inlineStr"/>
+      <c r="FL97" t="inlineStr"/>
+      <c r="FM97" t="inlineStr"/>
+      <c r="FN97" t="inlineStr"/>
+      <c r="FO97" t="inlineStr"/>
+      <c r="FP97" t="inlineStr">
+        <is>
+          <t>zsH7aMfI</t>
+        </is>
+      </c>
+      <c r="FQ97" t="inlineStr">
+        <is>
+          <t>umtiti samuel</t>
+        </is>
+      </c>
+      <c r="FR97" t="inlineStr"/>
+      <c r="FS97" t="inlineStr"/>
+      <c r="FT97" t="inlineStr">
+        <is>
+          <t>xGol69CN</t>
+        </is>
+      </c>
+      <c r="FU97" t="inlineStr">
+        <is>
+          <t>zedadka akim</t>
+        </is>
+      </c>
+      <c r="FV97" t="inlineStr">
+        <is>
+          <t>vqK5oQ8e</t>
+        </is>
+      </c>
+      <c r="FW97" t="inlineStr">
+        <is>
+          <t>zhegrova edon</t>
+        </is>
+      </c>
+      <c r="FX97" t="inlineStr"/>
+      <c r="FY97" t="inlineStr"/>
+      <c r="FZ97" t="inlineStr"/>
+      <c r="GA97" t="inlineStr"/>
+      <c r="GB97" t="inlineStr"/>
+      <c r="GC97" t="inlineStr"/>
+      <c r="GD97" t="inlineStr"/>
+      <c r="GE97" t="inlineStr"/>
+      <c r="GF97" t="inlineStr"/>
+      <c r="GG97" t="inlineStr"/>
+      <c r="GH97" t="inlineStr"/>
+      <c r="GI97" t="inlineStr"/>
+      <c r="GJ97" t="inlineStr"/>
+      <c r="GK97" t="inlineStr"/>
+      <c r="GL97" t="inlineStr"/>
+      <c r="GM97" t="inlineStr"/>
+      <c r="GN97" t="inlineStr"/>
+      <c r="GO97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2qYBqH5q</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>lucas perri</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>6PvHspma</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>clinton mata</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>K44QNA2A</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>caleta car duje</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>tdnibGHH</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>niakhate moussa</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>CCz5z9Ug</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>abner</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>CnBQp2sj</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>maitland niles ainsley</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0U8JJaVd</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>caqueret maxence</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>rsiloRPO</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>nuamah ernest</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Qyrn555R</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>benrahma said</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>6N65iDOI</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>fofana malick</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>YegtWFr9</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>lacazette alexandre</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>WYUNrwz4</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>kohn philipp</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>OjKXB6ns</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>vanderson</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>UXQPdpOB</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>kehrer thilo</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>zuFTjQI5</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>salisu mohammed</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>0YpRCTwo</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>jakobs ismail</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>d23lOQrL</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>zakaria denis</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>boBGHitI</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>camara lamine</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>0UP6MLGJ</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>akliouche maghnes</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>hIwtloy3</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>minamino takumi</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>S2dMSJX1</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>ben seghir eliesse</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>CpKkPKuP</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>embolo breel</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
+          <t>Qc9B0Q23</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>adryelson</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>2c931iLK</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>balde mama</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>WG2O5tgf</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>diawara mahamadou</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>vaX5DmSc</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>kumbedi sael</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>dKmI2jJT</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>lopes anthony</t>
+        </is>
+      </c>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>EisQ8ABn</t>
+        </is>
+      </c>
+      <c r="BE98" t="inlineStr">
+        <is>
+          <t>mangala orel</t>
+        </is>
+      </c>
+      <c r="BF98" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="BG98" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="BH98" t="inlineStr">
+        <is>
+          <t>QgN9t9CH</t>
+        </is>
+      </c>
+      <c r="BI98" t="inlineStr">
+        <is>
+          <t>mikautadze georges</t>
+        </is>
+      </c>
+      <c r="BJ98" t="inlineStr">
+        <is>
+          <t>hQOIoFOs</t>
+        </is>
+      </c>
+      <c r="BK98" t="inlineStr">
+        <is>
+          <t>tolisso corentin</t>
+        </is>
+      </c>
+      <c r="BL98" t="inlineStr">
+        <is>
+          <t>rVZLmUsU</t>
+        </is>
+      </c>
+      <c r="BM98" t="inlineStr">
+        <is>
+          <t>balgun folarin</t>
+        </is>
+      </c>
+      <c r="BN98" t="inlineStr">
+        <is>
+          <t>dr5D8pxI</t>
+        </is>
+      </c>
+      <c r="BO98" t="inlineStr">
+        <is>
+          <t>caio henrique</t>
+        </is>
+      </c>
+      <c r="BP98" t="inlineStr">
+        <is>
+          <t>t41NlDfO</t>
+        </is>
+      </c>
+      <c r="BQ98" t="inlineStr">
+        <is>
+          <t>ilenikhena george</t>
+        </is>
+      </c>
+      <c r="BR98" t="inlineStr">
+        <is>
+          <t>OfVIIvoN</t>
+        </is>
+      </c>
+      <c r="BS98" t="inlineStr">
+        <is>
+          <t>lienard yann</t>
+        </is>
+      </c>
+      <c r="BT98" t="inlineStr">
+        <is>
+          <t>zsPNUcJd</t>
+        </is>
+      </c>
+      <c r="BU98" t="inlineStr">
+        <is>
+          <t>magassa soungoutou</t>
+        </is>
+      </c>
+      <c r="BV98" t="inlineStr">
+        <is>
+          <t>QkOX3B5N</t>
+        </is>
+      </c>
+      <c r="BW98" t="inlineStr">
+        <is>
+          <t>mawissa christian</t>
+        </is>
+      </c>
+      <c r="BX98" t="inlineStr">
+        <is>
+          <t>x0We5RpI</t>
+        </is>
+      </c>
+      <c r="BY98" t="inlineStr">
+        <is>
+          <t>ouattara kassoum</t>
+        </is>
+      </c>
+      <c r="BZ98" t="inlineStr">
+        <is>
+          <t>Ym8dZot0</t>
+        </is>
+      </c>
+      <c r="CA98" t="inlineStr">
+        <is>
+          <t>singo wilfried</t>
+        </is>
+      </c>
+      <c r="CB98" t="inlineStr">
+        <is>
+          <t>Sbk0VFPJ</t>
+        </is>
+      </c>
+      <c r="CC98" t="inlineStr">
+        <is>
+          <t>teze jordan</t>
+        </is>
+      </c>
+      <c r="CD98" t="inlineStr">
+        <is>
+          <t>QgN9t9CH</t>
+        </is>
+      </c>
+      <c r="CE98" t="inlineStr">
+        <is>
+          <t>mikautadze georges</t>
+        </is>
+      </c>
+      <c r="CF98" t="inlineStr">
+        <is>
+          <t>QgN9t9CH</t>
+        </is>
+      </c>
+      <c r="CG98" t="inlineStr">
+        <is>
+          <t>mikautadze georges</t>
+        </is>
+      </c>
+      <c r="CH98" t="inlineStr">
+        <is>
+          <t>rsiloRPO</t>
+        </is>
+      </c>
+      <c r="CI98" t="inlineStr">
+        <is>
+          <t>nuamah ernest</t>
+        </is>
+      </c>
+      <c r="CJ98" t="inlineStr">
+        <is>
+          <t>2c931iLK</t>
+        </is>
+      </c>
+      <c r="CK98" t="inlineStr">
+        <is>
+          <t>balde mama</t>
+        </is>
+      </c>
+      <c r="CL98" t="inlineStr">
+        <is>
+          <t>2c931iLK</t>
+        </is>
+      </c>
+      <c r="CM98" t="inlineStr">
+        <is>
+          <t>balde mama</t>
+        </is>
+      </c>
+      <c r="CN98" t="inlineStr">
+        <is>
+          <t>6N65iDOI</t>
+        </is>
+      </c>
+      <c r="CO98" t="inlineStr">
+        <is>
+          <t>fofana malick</t>
+        </is>
+      </c>
+      <c r="CP98" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="CQ98" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="CR98" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="CS98" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="CT98" t="inlineStr">
+        <is>
+          <t>CCz5z9Ug</t>
+        </is>
+      </c>
+      <c r="CU98" t="inlineStr">
+        <is>
+          <t>abner</t>
+        </is>
+      </c>
+      <c r="CV98" t="inlineStr">
+        <is>
+          <t>hQOIoFOs</t>
+        </is>
+      </c>
+      <c r="CW98" t="inlineStr">
+        <is>
+          <t>tolisso corentin</t>
+        </is>
+      </c>
+      <c r="CX98" t="inlineStr">
+        <is>
+          <t>hQOIoFOs</t>
+        </is>
+      </c>
+      <c r="CY98" t="inlineStr">
+        <is>
+          <t>tolisso corentin</t>
+        </is>
+      </c>
+      <c r="CZ98" t="inlineStr">
+        <is>
+          <t>0U8JJaVd</t>
+        </is>
+      </c>
+      <c r="DA98" t="inlineStr">
+        <is>
+          <t>caqueret maxence</t>
+        </is>
+      </c>
+      <c r="DB98" t="inlineStr">
+        <is>
+          <t>WG2O5tgf</t>
+        </is>
+      </c>
+      <c r="DC98" t="inlineStr">
+        <is>
+          <t>diawara mahamadou</t>
+        </is>
+      </c>
+      <c r="DD98" t="inlineStr">
+        <is>
+          <t>WG2O5tgf</t>
+        </is>
+      </c>
+      <c r="DE98" t="inlineStr">
+        <is>
+          <t>diawara mahamadou</t>
+        </is>
+      </c>
+      <c r="DF98" t="inlineStr">
+        <is>
+          <t>Qyrn555R</t>
+        </is>
+      </c>
+      <c r="DG98" t="inlineStr">
+        <is>
+          <t>benrahma said</t>
+        </is>
+      </c>
+      <c r="DH98" t="inlineStr"/>
+      <c r="DI98" t="inlineStr"/>
+      <c r="DJ98" t="inlineStr"/>
+      <c r="DK98" t="inlineStr"/>
+      <c r="DL98" t="inlineStr"/>
+      <c r="DM98" t="inlineStr"/>
+      <c r="DN98" t="inlineStr">
+        <is>
+          <t>t41NlDfO</t>
+        </is>
+      </c>
+      <c r="DO98" t="inlineStr">
+        <is>
+          <t>ilenikhena george</t>
+        </is>
+      </c>
+      <c r="DP98" t="inlineStr">
+        <is>
+          <t>t41NlDfO</t>
+        </is>
+      </c>
+      <c r="DQ98" t="inlineStr">
+        <is>
+          <t>ilenikhena george</t>
+        </is>
+      </c>
+      <c r="DR98" t="inlineStr">
+        <is>
+          <t>CpKkPKuP</t>
+        </is>
+      </c>
+      <c r="DS98" t="inlineStr">
+        <is>
+          <t>embolo breel</t>
+        </is>
+      </c>
+      <c r="DT98" t="inlineStr">
+        <is>
+          <t>Sbk0VFPJ</t>
+        </is>
+      </c>
+      <c r="DU98" t="inlineStr">
+        <is>
+          <t>teze jordan</t>
+        </is>
+      </c>
+      <c r="DV98" t="inlineStr">
+        <is>
+          <t>Sbk0VFPJ</t>
+        </is>
+      </c>
+      <c r="DW98" t="inlineStr">
+        <is>
+          <t>teze jordan</t>
+        </is>
+      </c>
+      <c r="DX98" t="inlineStr">
+        <is>
+          <t>OjKXB6ns</t>
+        </is>
+      </c>
+      <c r="DY98" t="inlineStr">
+        <is>
+          <t>vanderson</t>
+        </is>
+      </c>
+      <c r="DZ98" t="inlineStr">
+        <is>
+          <t>x0We5RpI</t>
+        </is>
+      </c>
+      <c r="EA98" t="inlineStr">
+        <is>
+          <t>ouattara kassoum</t>
+        </is>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>x0We5RpI</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>ouattara kassoum</t>
+        </is>
+      </c>
+      <c r="ED98" t="inlineStr">
+        <is>
+          <t>S2dMSJX1</t>
+        </is>
+      </c>
+      <c r="EE98" t="inlineStr">
+        <is>
+          <t>ben seghir eliesse</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr">
+        <is>
+          <t>zsPNUcJd</t>
+        </is>
+      </c>
+      <c r="EG98" t="inlineStr">
+        <is>
+          <t>magassa soungoutou</t>
+        </is>
+      </c>
+      <c r="EH98" t="inlineStr">
+        <is>
+          <t>zsPNUcJd</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr">
+        <is>
+          <t>magassa soungoutou</t>
+        </is>
+      </c>
+      <c r="EJ98" t="inlineStr">
+        <is>
+          <t>d23lOQrL</t>
+        </is>
+      </c>
+      <c r="EK98" t="inlineStr">
+        <is>
+          <t>zakaria denis</t>
+        </is>
+      </c>
+      <c r="EL98" t="inlineStr">
+        <is>
+          <t>Ym8dZot0</t>
+        </is>
+      </c>
+      <c r="EM98" t="inlineStr">
+        <is>
+          <t>singo wilfried</t>
+        </is>
+      </c>
+      <c r="EN98" t="inlineStr">
+        <is>
+          <t>Ym8dZot0</t>
+        </is>
+      </c>
+      <c r="EO98" t="inlineStr">
+        <is>
+          <t>singo wilfried</t>
+        </is>
+      </c>
+      <c r="EP98" t="inlineStr">
+        <is>
+          <t>hIwtloy3</t>
+        </is>
+      </c>
+      <c r="EQ98" t="inlineStr">
+        <is>
+          <t>minamino takumi</t>
+        </is>
+      </c>
+      <c r="ER98" t="inlineStr"/>
+      <c r="ES98" t="inlineStr"/>
+      <c r="ET98" t="inlineStr"/>
+      <c r="EU98" t="inlineStr"/>
+      <c r="EV98" t="inlineStr"/>
+      <c r="EW98" t="inlineStr"/>
+      <c r="EX98" t="inlineStr"/>
+      <c r="EY98" t="inlineStr"/>
+      <c r="EZ98" t="inlineStr"/>
+      <c r="FA98" t="inlineStr"/>
+      <c r="FB98" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="FC98" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="FD98" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="FE98" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="FF98" t="inlineStr"/>
+      <c r="FG98" t="inlineStr"/>
+      <c r="FH98" t="inlineStr"/>
+      <c r="FI98" t="inlineStr"/>
+      <c r="FJ98" t="inlineStr"/>
+      <c r="FK98" t="inlineStr"/>
+      <c r="FL98" t="inlineStr"/>
+      <c r="FM98" t="inlineStr"/>
+      <c r="FN98" t="inlineStr"/>
+      <c r="FO98" t="inlineStr"/>
+      <c r="FP98" t="inlineStr"/>
+      <c r="FQ98" t="inlineStr"/>
+      <c r="FR98" t="inlineStr"/>
+      <c r="FS98" t="inlineStr"/>
+      <c r="FT98" t="inlineStr"/>
+      <c r="FU98" t="inlineStr"/>
+      <c r="FV98" t="inlineStr"/>
+      <c r="FW98" t="inlineStr"/>
+      <c r="FX98" t="inlineStr"/>
+      <c r="FY98" t="inlineStr"/>
+      <c r="FZ98" t="inlineStr"/>
+      <c r="GA98" t="inlineStr"/>
+      <c r="GB98" t="inlineStr"/>
+      <c r="GC98" t="inlineStr"/>
+      <c r="GD98" t="inlineStr"/>
+      <c r="GE98" t="inlineStr"/>
+      <c r="GF98" t="inlineStr"/>
+      <c r="GG98" t="inlineStr"/>
+      <c r="GH98" t="inlineStr"/>
+      <c r="GI98" t="inlineStr"/>
+      <c r="GJ98" t="inlineStr"/>
+      <c r="GK98" t="inlineStr"/>
+      <c r="GL98" t="inlineStr"/>
+      <c r="GM98" t="inlineStr"/>
+      <c r="GN98" t="inlineStr"/>
+      <c r="GO98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>WScbdXmL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>donnarumma gianluigi</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>MqFBkBsp</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>hakimi achraf</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>UFfev8HP</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>marquinhos</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>KA5AQsy0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>pacho william</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>ne2xCTJj</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>mendes nuno</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>neJeseDL</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>zaire emery warren</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>hCbYVsXQ</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>neves joao</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sz9SH7zj</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>vitinha</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>zsMC2Ec0</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>dembele ousmane</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>GQMMQo6m</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>asensio marco</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>lhGD3RgS</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>barcola bradley</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Qe5HfcWe</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>lecomte benjamin</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>QHKswk6H</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>tchato enzo</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>hQGrDm2I</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>omeragic becir</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>pYI2rM4H</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>sagnan modibo</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>WOiB5ygg</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>sacko falaye</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>j5dSkdZI</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>ferri jordan</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>vsv6TioJ</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>savanier teji</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>A7vSQTKq</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>nordin arnaud</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>Q7VDuZr1</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>khazri wahbi</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>Y1UU1rz7</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>lucas beraldo</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>KIUWH2Jq</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>doue desire</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>WKBRZ6Y6</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>kolo muani randal</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>YTVIJfxO</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>lee kangin</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>za4zLeYc</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>mayulu senny</t>
+        </is>
+      </c>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>nkxtcGo7</t>
+        </is>
+      </c>
+      <c r="BE99" t="inlineStr">
+        <is>
+          <t>mbaye ibrahim</t>
+        </is>
+      </c>
+      <c r="BF99" t="inlineStr">
+        <is>
+          <t>l6HSH2Uo</t>
+        </is>
+      </c>
+      <c r="BG99" t="inlineStr">
+        <is>
+          <t>ruiz fabian</t>
+        </is>
+      </c>
+      <c r="BH99" t="inlineStr">
+        <is>
+          <t>zJF3W9Rq</t>
+        </is>
+      </c>
+      <c r="BI99" t="inlineStr">
+        <is>
+          <t>safonov matvey</t>
+        </is>
+      </c>
+      <c r="BJ99" t="inlineStr">
+        <is>
+          <t>S2Gd6Dq5</t>
+        </is>
+      </c>
+      <c r="BK99" t="inlineStr">
+        <is>
+          <t>zague yoram</t>
+        </is>
+      </c>
+      <c r="BL99" t="inlineStr">
+        <is>
+          <t>nks9eiQ4</t>
+        </is>
+      </c>
+      <c r="BM99" t="inlineStr">
+        <is>
+          <t>adams akor</t>
+        </is>
+      </c>
+      <c r="BN99" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="BO99" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="BP99" t="inlineStr">
+        <is>
+          <t>GUpH52h6</t>
+        </is>
+      </c>
+      <c r="BQ99" t="inlineStr">
+        <is>
+          <t>bares gabriel</t>
+        </is>
+      </c>
+      <c r="BR99" t="inlineStr">
+        <is>
+          <t>GKgj13Ht</t>
+        </is>
+      </c>
+      <c r="BS99" t="inlineStr">
+        <is>
+          <t>bertaud dimitry</t>
+        </is>
+      </c>
+      <c r="BT99" t="inlineStr">
+        <is>
+          <t>dYGOQd5o</t>
+        </is>
+      </c>
+      <c r="BU99" t="inlineStr">
+        <is>
+          <t>chennahi theo</t>
+        </is>
+      </c>
+      <c r="BV99" t="inlineStr">
+        <is>
+          <t>2qMy8CA5</t>
+        </is>
+      </c>
+      <c r="BW99" t="inlineStr">
+        <is>
+          <t>coulibaly tanguy</t>
+        </is>
+      </c>
+      <c r="BX99" t="inlineStr">
+        <is>
+          <t>S4sVF7O0</t>
+        </is>
+      </c>
+      <c r="BY99" t="inlineStr">
+        <is>
+          <t>dzodic stefan</t>
+        </is>
+      </c>
+      <c r="BZ99" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="CA99" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="CB99" t="inlineStr">
+        <is>
+          <t>OEsM5Dqs</t>
+        </is>
+      </c>
+      <c r="CC99" t="inlineStr">
+        <is>
+          <t>maamma othmane</t>
+        </is>
+      </c>
+      <c r="CD99" t="inlineStr">
+        <is>
+          <t>KIUWH2Jq</t>
+        </is>
+      </c>
+      <c r="CE99" t="inlineStr">
+        <is>
+          <t>doue desire</t>
+        </is>
+      </c>
+      <c r="CF99" t="inlineStr">
+        <is>
+          <t>KIUWH2Jq</t>
+        </is>
+      </c>
+      <c r="CG99" t="inlineStr">
+        <is>
+          <t>doue desire</t>
+        </is>
+      </c>
+      <c r="CH99" t="inlineStr">
+        <is>
+          <t>lhGD3RgS</t>
+        </is>
+      </c>
+      <c r="CI99" t="inlineStr">
+        <is>
+          <t>barcola bradley</t>
+        </is>
+      </c>
+      <c r="CJ99" t="inlineStr">
+        <is>
+          <t>YTVIJfxO</t>
+        </is>
+      </c>
+      <c r="CK99" t="inlineStr">
+        <is>
+          <t>lee kangin</t>
+        </is>
+      </c>
+      <c r="CL99" t="inlineStr">
+        <is>
+          <t>YTVIJfxO</t>
+        </is>
+      </c>
+      <c r="CM99" t="inlineStr">
+        <is>
+          <t>lee kangin</t>
+        </is>
+      </c>
+      <c r="CN99" t="inlineStr">
+        <is>
+          <t>zsMC2Ec0</t>
+        </is>
+      </c>
+      <c r="CO99" t="inlineStr">
+        <is>
+          <t>dembele ousmane</t>
+        </is>
+      </c>
+      <c r="CP99" t="inlineStr">
+        <is>
+          <t>WKBRZ6Y6</t>
+        </is>
+      </c>
+      <c r="CQ99" t="inlineStr">
+        <is>
+          <t>kolo muani randal</t>
+        </is>
+      </c>
+      <c r="CR99" t="inlineStr">
+        <is>
+          <t>WKBRZ6Y6</t>
+        </is>
+      </c>
+      <c r="CS99" t="inlineStr">
+        <is>
+          <t>kolo muani randal</t>
+        </is>
+      </c>
+      <c r="CT99" t="inlineStr">
+        <is>
+          <t>GQMMQo6m</t>
+        </is>
+      </c>
+      <c r="CU99" t="inlineStr">
+        <is>
+          <t>asensio marco</t>
+        </is>
+      </c>
+      <c r="CV99" t="inlineStr">
+        <is>
+          <t>l6HSH2Uo</t>
+        </is>
+      </c>
+      <c r="CW99" t="inlineStr">
+        <is>
+          <t>ruiz fabian</t>
+        </is>
+      </c>
+      <c r="CX99" t="inlineStr">
+        <is>
+          <t>l6HSH2Uo</t>
+        </is>
+      </c>
+      <c r="CY99" t="inlineStr">
+        <is>
+          <t>ruiz fabian</t>
+        </is>
+      </c>
+      <c r="CZ99" t="inlineStr">
+        <is>
+          <t>hCbYVsXQ</t>
+        </is>
+      </c>
+      <c r="DA99" t="inlineStr">
+        <is>
+          <t>neves joao</t>
+        </is>
+      </c>
+      <c r="DB99" t="inlineStr">
+        <is>
+          <t>nkxtcGo7</t>
+        </is>
+      </c>
+      <c r="DC99" t="inlineStr">
+        <is>
+          <t>mbaye ibrahim</t>
+        </is>
+      </c>
+      <c r="DD99" t="inlineStr">
+        <is>
+          <t>nkxtcGo7</t>
+        </is>
+      </c>
+      <c r="DE99" t="inlineStr">
+        <is>
+          <t>mbaye ibrahim</t>
+        </is>
+      </c>
+      <c r="DF99" t="inlineStr">
+        <is>
+          <t>neJeseDL</t>
+        </is>
+      </c>
+      <c r="DG99" t="inlineStr">
+        <is>
+          <t>zaire emery warren</t>
+        </is>
+      </c>
+      <c r="DH99" t="inlineStr"/>
+      <c r="DI99" t="inlineStr"/>
+      <c r="DJ99" t="inlineStr"/>
+      <c r="DK99" t="inlineStr"/>
+      <c r="DL99" t="inlineStr"/>
+      <c r="DM99" t="inlineStr"/>
+      <c r="DN99" t="inlineStr">
+        <is>
+          <t>nks9eiQ4</t>
+        </is>
+      </c>
+      <c r="DO99" t="inlineStr">
+        <is>
+          <t>adams akor</t>
+        </is>
+      </c>
+      <c r="DP99" t="inlineStr">
+        <is>
+          <t>nks9eiQ4</t>
+        </is>
+      </c>
+      <c r="DQ99" t="inlineStr">
+        <is>
+          <t>adams akor</t>
+        </is>
+      </c>
+      <c r="DR99" t="inlineStr">
+        <is>
+          <t>Q7VDuZr1</t>
+        </is>
+      </c>
+      <c r="DS99" t="inlineStr">
+        <is>
+          <t>khazri wahbi</t>
+        </is>
+      </c>
+      <c r="DT99" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="DU99" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="DV99" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="DW99" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="DX99" t="inlineStr">
+        <is>
+          <t>A7vSQTKq</t>
+        </is>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>nordin arnaud</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>j5dSkdZI</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>ferri jordan</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>GUpH52h6</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr">
+        <is>
+          <t>bares gabriel</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>GUpH52h6</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>bares gabriel</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>vsv6TioJ</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>savanier teji</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr"/>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr"/>
+      <c r="EO99" t="inlineStr"/>
+      <c r="EP99" t="inlineStr"/>
+      <c r="EQ99" t="inlineStr"/>
+      <c r="ER99" t="inlineStr"/>
+      <c r="ES99" t="inlineStr"/>
+      <c r="ET99" t="inlineStr"/>
+      <c r="EU99" t="inlineStr"/>
+      <c r="EV99" t="inlineStr"/>
+      <c r="EW99" t="inlineStr"/>
+      <c r="EX99" t="inlineStr">
+        <is>
+          <t>Cd1ieN88</t>
+        </is>
+      </c>
+      <c r="EY99" t="inlineStr">
+        <is>
+          <t>bernat juan</t>
+        </is>
+      </c>
+      <c r="EZ99" t="inlineStr">
+        <is>
+          <t>x2fvnkud</t>
+        </is>
+      </c>
+      <c r="FA99" t="inlineStr">
+        <is>
+          <t>hernandez lucas</t>
+        </is>
+      </c>
+      <c r="FB99" t="inlineStr">
+        <is>
+          <t>dSDrHenE</t>
+        </is>
+      </c>
+      <c r="FC99" t="inlineStr">
+        <is>
+          <t>gueguin axel</t>
+        </is>
+      </c>
+      <c r="FD99" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="FE99" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="FF99" t="inlineStr"/>
+      <c r="FG99" t="inlineStr"/>
+      <c r="FH99" t="inlineStr">
+        <is>
+          <t>dMyiR1D8</t>
+        </is>
+      </c>
+      <c r="FI99" t="inlineStr">
+        <is>
+          <t>kimpembe presnel</t>
+        </is>
+      </c>
+      <c r="FJ99" t="inlineStr"/>
+      <c r="FK99" t="inlineStr"/>
+      <c r="FL99" t="inlineStr"/>
+      <c r="FM99" t="inlineStr"/>
+      <c r="FN99" t="inlineStr"/>
+      <c r="FO99" t="inlineStr"/>
+      <c r="FP99" t="inlineStr">
+        <is>
+          <t>MoObMvb7</t>
+        </is>
+      </c>
+      <c r="FQ99" t="inlineStr">
+        <is>
+          <t>mukiele nordi</t>
+        </is>
+      </c>
+      <c r="FR99" t="inlineStr"/>
+      <c r="FS99" t="inlineStr"/>
+      <c r="FT99" t="inlineStr">
+        <is>
+          <t>IPvZS0u3</t>
+        </is>
+      </c>
+      <c r="FU99" t="inlineStr">
+        <is>
+          <t>pereira danilo</t>
+        </is>
+      </c>
+      <c r="FV99" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="FW99" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="FX99" t="inlineStr">
+        <is>
+          <t>EqBuG0nE</t>
+        </is>
+      </c>
+      <c r="FY99" t="inlineStr">
+        <is>
+          <t>skriniar milan</t>
+        </is>
+      </c>
+      <c r="FZ99" t="inlineStr">
+        <is>
+          <t>tSYxgDUI</t>
+        </is>
+      </c>
+      <c r="GA99" t="inlineStr">
+        <is>
+          <t>soler carlos</t>
+        </is>
+      </c>
+      <c r="GB99" t="inlineStr"/>
+      <c r="GC99" t="inlineStr"/>
+      <c r="GD99" t="inlineStr"/>
+      <c r="GE99" t="inlineStr"/>
+      <c r="GF99" t="inlineStr"/>
+      <c r="GG99" t="inlineStr"/>
+      <c r="GH99" t="inlineStr"/>
+      <c r="GI99" t="inlineStr"/>
+      <c r="GJ99" t="inlineStr"/>
+      <c r="GK99" t="inlineStr"/>
+      <c r="GL99" t="inlineStr"/>
+      <c r="GM99" t="inlineStr"/>
+      <c r="GN99" t="inlineStr"/>
+      <c r="GO99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>2yXIHV57</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>fkOg2Gqj</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>mvogo yvon</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Est8UaLc</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>igor silva</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>4nPjVrMS</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>mendy formose</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>bLU8KtEd</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>talbi montassar</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O2h5w23g</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ngameni darline zidane</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>YJhgLOwk</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>ponceau julien</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>WzrmHcCA</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>abergel laurent</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>8vMxrdie</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>mvuka joel</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>pOt3Q6yb</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>pagis pablo</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>ba2ejA41</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>dieng bamba cheikh dieng</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>zTOOlq65</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>aiyegun tosin</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>EibuOrCE</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>diop mamadou</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>OrdAwjs0</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>paquiez gaetan</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Cv3T1tX1</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>diarra mamadou</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>zeMPP8vQ</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>nestor loic</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>IXc7iymr</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>mendy arial</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>6VcKrEuM</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>valls theo</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>0K8CfONM</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>joseph lenny</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>2NKowyxS</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>sylvestre eddy</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>0ERxiKEk</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>sbai mohamed amine</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>nsRL20Ap</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>ba pape meissa</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr">
+        <is>
+          <t>z1as6ykH</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>adjei nathaniel</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>2ZLbrRiB</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>bamba muhammad</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>xrsWhgRE</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>ebong arthur</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>GjVTxPsc</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>james isaac</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="BE100" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="BF100" t="inlineStr">
+        <is>
+          <t>KAxiV8Bj</t>
+        </is>
+      </c>
+      <c r="BG100" t="inlineStr">
+        <is>
+          <t>leroy benjamin</t>
+        </is>
+      </c>
+      <c r="BH100" t="inlineStr"/>
+      <c r="BI100" t="inlineStr"/>
+      <c r="BJ100" t="inlineStr"/>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="inlineStr">
+        <is>
+          <t>tpbpYRt1</t>
+        </is>
+      </c>
+      <c r="BM100" t="inlineStr">
+        <is>
+          <t>allain bobby</t>
+        </is>
+      </c>
+      <c r="BN100" t="inlineStr">
+        <is>
+          <t>SzyvcCbe</t>
+        </is>
+      </c>
+      <c r="BO100" t="inlineStr">
+        <is>
+          <t>benet jessy</t>
+        </is>
+      </c>
+      <c r="BP100" t="inlineStr">
+        <is>
+          <t>4vlM6XrP</t>
+        </is>
+      </c>
+      <c r="BQ100" t="inlineStr">
+        <is>
+          <t>elphege nesta</t>
+        </is>
+      </c>
+      <c r="BR100" t="inlineStr">
+        <is>
+          <t>YaqgzyYt</t>
+        </is>
+      </c>
+      <c r="BS100" t="inlineStr">
+        <is>
+          <t>jeno abiezer</t>
+        </is>
+      </c>
+      <c r="BT100" t="inlineStr">
+        <is>
+          <t>ITex2UPE</t>
+        </is>
+      </c>
+      <c r="BU100" t="inlineStr">
+        <is>
+          <t>kerouedan alan</t>
+        </is>
+      </c>
+      <c r="BV100" t="inlineStr">
+        <is>
+          <t>0poPcske</t>
+        </is>
+      </c>
+      <c r="BW100" t="inlineStr">
+        <is>
+          <t>rigo dante</t>
+        </is>
+      </c>
+      <c r="BX100" t="inlineStr">
+        <is>
+          <t>Gb1d4tI6</t>
+        </is>
+      </c>
+      <c r="BY100" t="inlineStr">
+        <is>
+          <t>yameogo bachirou</t>
+        </is>
+      </c>
+      <c r="BZ100" t="inlineStr"/>
+      <c r="CA100" t="inlineStr"/>
+      <c r="CB100" t="inlineStr"/>
+      <c r="CC100" t="inlineStr"/>
+      <c r="CD100" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="CE100" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="CF100" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="CG100" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="CH100" t="inlineStr">
+        <is>
+          <t>ba2ejA41</t>
+        </is>
+      </c>
+      <c r="CI100" t="inlineStr">
+        <is>
+          <t>dieng bamba cheikh dieng</t>
+        </is>
+      </c>
+      <c r="CJ100" t="inlineStr">
+        <is>
+          <t>xrsWhgRE</t>
+        </is>
+      </c>
+      <c r="CK100" t="inlineStr">
+        <is>
+          <t>ebong arthur</t>
+        </is>
+      </c>
+      <c r="CL100" t="inlineStr">
+        <is>
+          <t>xrsWhgRE</t>
+        </is>
+      </c>
+      <c r="CM100" t="inlineStr">
+        <is>
+          <t>ebong arthur</t>
+        </is>
+      </c>
+      <c r="CN100" t="inlineStr">
+        <is>
+          <t>pOt3Q6yb</t>
+        </is>
+      </c>
+      <c r="CO100" t="inlineStr">
+        <is>
+          <t>pagis pablo</t>
+        </is>
+      </c>
+      <c r="CP100" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="CQ100" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="CR100" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="CS100" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="CT100" t="inlineStr">
+        <is>
+          <t>8vMxrdie</t>
+        </is>
+      </c>
+      <c r="CU100" t="inlineStr">
+        <is>
+          <t>mvuka joel</t>
+        </is>
+      </c>
+      <c r="CV100" t="inlineStr">
+        <is>
+          <t>GjVTxPsc</t>
+        </is>
+      </c>
+      <c r="CW100" t="inlineStr">
+        <is>
+          <t>james isaac</t>
+        </is>
+      </c>
+      <c r="CX100" t="inlineStr">
+        <is>
+          <t>GjVTxPsc</t>
+        </is>
+      </c>
+      <c r="CY100" t="inlineStr">
+        <is>
+          <t>james isaac</t>
+        </is>
+      </c>
+      <c r="CZ100" t="inlineStr">
+        <is>
+          <t>O2h5w23g</t>
+        </is>
+      </c>
+      <c r="DA100" t="inlineStr">
+        <is>
+          <t>ngameni darline zidane</t>
+        </is>
+      </c>
+      <c r="DB100" t="inlineStr">
+        <is>
+          <t>z1as6ykH</t>
+        </is>
+      </c>
+      <c r="DC100" t="inlineStr">
+        <is>
+          <t>adjei nathaniel</t>
+        </is>
+      </c>
+      <c r="DD100" t="inlineStr">
+        <is>
+          <t>z1as6ykH</t>
+        </is>
+      </c>
+      <c r="DE100" t="inlineStr">
+        <is>
+          <t>adjei nathaniel</t>
+        </is>
+      </c>
+      <c r="DF100" t="inlineStr">
+        <is>
+          <t>zTOOlq65</t>
+        </is>
+      </c>
+      <c r="DG100" t="inlineStr">
+        <is>
+          <t>aiyegun tosin</t>
+        </is>
+      </c>
+      <c r="DH100" t="inlineStr"/>
+      <c r="DI100" t="inlineStr"/>
+      <c r="DJ100" t="inlineStr"/>
+      <c r="DK100" t="inlineStr"/>
+      <c r="DL100" t="inlineStr"/>
+      <c r="DM100" t="inlineStr"/>
+      <c r="DN100" t="inlineStr">
+        <is>
+          <t>YaqgzyYt</t>
+        </is>
+      </c>
+      <c r="DO100" t="inlineStr">
+        <is>
+          <t>jeno abiezer</t>
+        </is>
+      </c>
+      <c r="DP100" t="inlineStr">
+        <is>
+          <t>YaqgzyYt</t>
+        </is>
+      </c>
+      <c r="DQ100" t="inlineStr">
+        <is>
+          <t>jeno abiezer</t>
+        </is>
+      </c>
+      <c r="DR100" t="inlineStr">
+        <is>
+          <t>2NKowyxS</t>
+        </is>
+      </c>
+      <c r="DS100" t="inlineStr">
+        <is>
+          <t>sylvestre eddy</t>
+        </is>
+      </c>
+      <c r="DT100" t="inlineStr">
+        <is>
+          <t>ITex2UPE</t>
+        </is>
+      </c>
+      <c r="DU100" t="inlineStr">
+        <is>
+          <t>kerouedan alan</t>
+        </is>
+      </c>
+      <c r="DV100" t="inlineStr">
+        <is>
+          <t>ITex2UPE</t>
+        </is>
+      </c>
+      <c r="DW100" t="inlineStr">
+        <is>
+          <t>kerouedan alan</t>
+        </is>
+      </c>
+      <c r="DX100" t="inlineStr">
+        <is>
+          <t>IXc7iymr</t>
+        </is>
+      </c>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>mendy arial</t>
+        </is>
+      </c>
+      <c r="DZ100" t="inlineStr">
+        <is>
+          <t>Gb1d4tI6</t>
+        </is>
+      </c>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>yameogo bachirou</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>Gb1d4tI6</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>yameogo bachirou</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>zeMPP8vQ</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>nestor loic</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>SzyvcCbe</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>benet jessy</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>SzyvcCbe</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>benet jessy</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="EL100" t="inlineStr">
+        <is>
+          <t>4vlM6XrP</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr">
+        <is>
+          <t>elphege nesta</t>
+        </is>
+      </c>
+      <c r="EN100" t="inlineStr">
+        <is>
+          <t>4vlM6XrP</t>
+        </is>
+      </c>
+      <c r="EO100" t="inlineStr">
+        <is>
+          <t>elphege nesta</t>
+        </is>
+      </c>
+      <c r="EP100" t="inlineStr">
+        <is>
+          <t>0ERxiKEk</t>
+        </is>
+      </c>
+      <c r="EQ100" t="inlineStr">
+        <is>
+          <t>sbai mohamed amine</t>
+        </is>
+      </c>
+      <c r="ER100" t="inlineStr"/>
+      <c r="ES100" t="inlineStr"/>
+      <c r="ET100" t="inlineStr"/>
+      <c r="EU100" t="inlineStr"/>
+      <c r="EV100" t="inlineStr"/>
+      <c r="EW100" t="inlineStr"/>
+      <c r="EX100" t="inlineStr"/>
+      <c r="EY100" t="inlineStr"/>
+      <c r="EZ100" t="inlineStr"/>
+      <c r="FA100" t="inlineStr"/>
+      <c r="FB100" t="inlineStr"/>
+      <c r="FC100" t="inlineStr"/>
+      <c r="FD100" t="inlineStr"/>
+      <c r="FE100" t="inlineStr"/>
+      <c r="FF100" t="inlineStr"/>
+      <c r="FG100" t="inlineStr"/>
+      <c r="FH100" t="inlineStr"/>
+      <c r="FI100" t="inlineStr"/>
+      <c r="FJ100" t="inlineStr"/>
+      <c r="FK100" t="inlineStr"/>
+      <c r="FL100" t="inlineStr"/>
+      <c r="FM100" t="inlineStr"/>
+      <c r="FN100" t="inlineStr"/>
+      <c r="FO100" t="inlineStr"/>
+      <c r="FP100" t="inlineStr"/>
+      <c r="FQ100" t="inlineStr"/>
+      <c r="FR100" t="inlineStr"/>
+      <c r="FS100" t="inlineStr"/>
+      <c r="FT100" t="inlineStr"/>
+      <c r="FU100" t="inlineStr"/>
+      <c r="FV100" t="inlineStr"/>
+      <c r="FW100" t="inlineStr"/>
+      <c r="FX100" t="inlineStr"/>
+      <c r="FY100" t="inlineStr"/>
+      <c r="FZ100" t="inlineStr"/>
+      <c r="GA100" t="inlineStr"/>
+      <c r="GB100" t="inlineStr"/>
+      <c r="GC100" t="inlineStr"/>
+      <c r="GD100" t="inlineStr"/>
+      <c r="GE100" t="inlineStr"/>
+      <c r="GF100" t="inlineStr"/>
+      <c r="GG100" t="inlineStr"/>
+      <c r="GH100" t="inlineStr"/>
+      <c r="GI100" t="inlineStr"/>
+      <c r="GJ100" t="inlineStr"/>
+      <c r="GK100" t="inlineStr"/>
+      <c r="GL100" t="inlineStr"/>
+      <c r="GM100" t="inlineStr"/>
+      <c r="GN100" t="inlineStr"/>
+      <c r="GO100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>GM5aU8kD</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>YkTI15a3</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>escales florian</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>xbCaEITP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>lajugie francois</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AX04y31t</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>drouhin axel</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>riY6rQKH</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>jean gaby</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>QT6THpuf</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>delphis thibault</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>SGy9pst5</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>kashi ahmed</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>dvimXsna</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>demoncy yohann</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>E7gMZtT7</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>larose antoine</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>CpDeVZbL</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>ntamack ndimba samuel</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>8SssEZCK</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>billemaz clement</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>E1h8Ff92</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>djoco kapitbafan</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>GvRRSA15</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>aymes jeremy</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>CI9LnrCi</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>saintini nathanael</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>bw41ww90</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>morante leandro</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>K6gqRt3c</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>falette simon</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>zciOF0Jn</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>amraoui ayoub</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>AuRgvOVQ</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>robin milan</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>KAGdlKQ8</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>bamba mohamed</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>hOVOETub</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>siby mahame</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>tvNblrMr</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>diawara abdoul</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr">
+        <is>
+          <t>4YOUdDQ3</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>bermont anthony</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>GW9zt9yT</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>callens thomas</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>Knpb69xQ</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>kouadio julien</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>611nUsKM</t>
+        </is>
+      </c>
+      <c r="BE101" t="inlineStr">
+        <is>
+          <t>pajot vincent</t>
+        </is>
+      </c>
+      <c r="BF101" t="inlineStr">
+        <is>
+          <t>4SgLsxFe</t>
+        </is>
+      </c>
+      <c r="BG101" t="inlineStr">
+        <is>
+          <t>tiendrebeogo wendkuuni josue</t>
+        </is>
+      </c>
+      <c r="BH101" t="inlineStr"/>
+      <c r="BI101" t="inlineStr"/>
+      <c r="BJ101" t="inlineStr"/>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="inlineStr">
+        <is>
+          <t>6c3rD50k</t>
+        </is>
+      </c>
+      <c r="BM101" t="inlineStr">
+        <is>
+          <t>djaha akim</t>
+        </is>
+      </c>
+      <c r="BN101" t="inlineStr">
+        <is>
+          <t>GM3MZsvr</t>
+        </is>
+      </c>
+      <c r="BO101" t="inlineStr">
+        <is>
+          <t>etile yannick</t>
+        </is>
+      </c>
+      <c r="BP101" t="inlineStr">
+        <is>
+          <t>QgF8WB2F</t>
+        </is>
+      </c>
+      <c r="BQ101" t="inlineStr">
+        <is>
+          <t>kembolo francis</t>
+        </is>
+      </c>
+      <c r="BR101" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="BS101" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="BT101" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="BU101" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="BV101" t="inlineStr">
+        <is>
+          <t>drXPszOh</t>
+        </is>
+      </c>
+      <c r="BW101" t="inlineStr">
+        <is>
+          <t>solvet steve</t>
+        </is>
+      </c>
+      <c r="BX101" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="BY101" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="BZ101" t="inlineStr"/>
+      <c r="CA101" t="inlineStr"/>
+      <c r="CB101" t="inlineStr"/>
+      <c r="CC101" t="inlineStr"/>
+      <c r="CD101" t="inlineStr">
+        <is>
+          <t>4YOUdDQ3</t>
+        </is>
+      </c>
+      <c r="CE101" t="inlineStr">
+        <is>
+          <t>bermont anthony</t>
+        </is>
+      </c>
+      <c r="CF101" t="inlineStr">
+        <is>
+          <t>4YOUdDQ3</t>
+        </is>
+      </c>
+      <c r="CG101" t="inlineStr">
+        <is>
+          <t>bermont anthony</t>
+        </is>
+      </c>
+      <c r="CH101" t="inlineStr">
+        <is>
+          <t>CpDeVZbL</t>
+        </is>
+      </c>
+      <c r="CI101" t="inlineStr">
+        <is>
+          <t>ntamack ndimba samuel</t>
+        </is>
+      </c>
+      <c r="CJ101" t="inlineStr">
+        <is>
+          <t>611nUsKM</t>
+        </is>
+      </c>
+      <c r="CK101" t="inlineStr">
+        <is>
+          <t>pajot vincent</t>
+        </is>
+      </c>
+      <c r="CL101" t="inlineStr">
+        <is>
+          <t>611nUsKM</t>
+        </is>
+      </c>
+      <c r="CM101" t="inlineStr">
+        <is>
+          <t>pajot vincent</t>
+        </is>
+      </c>
+      <c r="CN101" t="inlineStr">
+        <is>
+          <t>QT6THpuf</t>
+        </is>
+      </c>
+      <c r="CO101" t="inlineStr">
+        <is>
+          <t>delphis thibault</t>
+        </is>
+      </c>
+      <c r="CP101" t="inlineStr">
+        <is>
+          <t>4SgLsxFe</t>
+        </is>
+      </c>
+      <c r="CQ101" t="inlineStr">
+        <is>
+          <t>tiendrebeogo wendkuuni josue</t>
+        </is>
+      </c>
+      <c r="CR101" t="inlineStr">
+        <is>
+          <t>4SgLsxFe</t>
+        </is>
+      </c>
+      <c r="CS101" t="inlineStr">
+        <is>
+          <t>tiendrebeogo wendkuuni josue</t>
+        </is>
+      </c>
+      <c r="CT101" t="inlineStr">
+        <is>
+          <t>dvimXsna</t>
+        </is>
+      </c>
+      <c r="CU101" t="inlineStr">
+        <is>
+          <t>demoncy yohann</t>
+        </is>
+      </c>
+      <c r="CV101" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="CW101" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="CX101" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="CY101" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="CZ101" t="inlineStr">
+        <is>
+          <t>E1h8Ff92</t>
+        </is>
+      </c>
+      <c r="DA101" t="inlineStr">
+        <is>
+          <t>djoco kapitbafan</t>
+        </is>
+      </c>
+      <c r="DB101" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="DC101" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="DD101" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="DE101" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="DF101" t="inlineStr">
+        <is>
+          <t>E7gMZtT7</t>
+        </is>
+      </c>
+      <c r="DG101" t="inlineStr">
+        <is>
+          <t>larose antoine</t>
+        </is>
+      </c>
+      <c r="DH101" t="inlineStr"/>
+      <c r="DI101" t="inlineStr"/>
+      <c r="DJ101" t="inlineStr"/>
+      <c r="DK101" t="inlineStr"/>
+      <c r="DL101" t="inlineStr"/>
+      <c r="DM101" t="inlineStr"/>
+      <c r="DN101" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="DO101" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="DP101" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="DQ101" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="DR101" t="inlineStr">
+        <is>
+          <t>tvNblrMr</t>
+        </is>
+      </c>
+      <c r="DS101" t="inlineStr">
+        <is>
+          <t>diawara abdoul</t>
+        </is>
+      </c>
+      <c r="DT101" t="inlineStr">
+        <is>
+          <t>drXPszOh</t>
+        </is>
+      </c>
+      <c r="DU101" t="inlineStr">
+        <is>
+          <t>solvet steve</t>
+        </is>
+      </c>
+      <c r="DV101" t="inlineStr">
+        <is>
+          <t>drXPszOh</t>
+        </is>
+      </c>
+      <c r="DW101" t="inlineStr">
+        <is>
+          <t>solvet steve</t>
+        </is>
+      </c>
+      <c r="DX101" t="inlineStr">
+        <is>
+          <t>hOVOETub</t>
+        </is>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>siby mahame</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="ED101" t="inlineStr">
+        <is>
+          <t>KAGdlKQ8</t>
+        </is>
+      </c>
+      <c r="EE101" t="inlineStr">
+        <is>
+          <t>bamba mohamed</t>
+        </is>
+      </c>
+      <c r="EF101" t="inlineStr">
+        <is>
+          <t>6c3rD50k</t>
+        </is>
+      </c>
+      <c r="EG101" t="inlineStr">
+        <is>
+          <t>djaha akim</t>
+        </is>
+      </c>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>6c3rD50k</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
+          <t>djaha akim</t>
+        </is>
+      </c>
+      <c r="EJ101" t="inlineStr">
+        <is>
+          <t>AuRgvOVQ</t>
+        </is>
+      </c>
+      <c r="EK101" t="inlineStr">
+        <is>
+          <t>robin milan</t>
+        </is>
+      </c>
+      <c r="EL101" t="inlineStr"/>
+      <c r="EM101" t="inlineStr"/>
+      <c r="EN101" t="inlineStr"/>
+      <c r="EO101" t="inlineStr"/>
+      <c r="EP101" t="inlineStr"/>
+      <c r="EQ101" t="inlineStr"/>
+      <c r="ER101" t="inlineStr"/>
+      <c r="ES101" t="inlineStr"/>
+      <c r="ET101" t="inlineStr"/>
+      <c r="EU101" t="inlineStr"/>
+      <c r="EV101" t="inlineStr"/>
+      <c r="EW101" t="inlineStr"/>
+      <c r="EX101" t="inlineStr"/>
+      <c r="EY101" t="inlineStr"/>
+      <c r="EZ101" t="inlineStr"/>
+      <c r="FA101" t="inlineStr"/>
+      <c r="FB101" t="inlineStr"/>
+      <c r="FC101" t="inlineStr"/>
+      <c r="FD101" t="inlineStr"/>
+      <c r="FE101" t="inlineStr"/>
+      <c r="FF101" t="inlineStr"/>
+      <c r="FG101" t="inlineStr"/>
+      <c r="FH101" t="inlineStr"/>
+      <c r="FI101" t="inlineStr"/>
+      <c r="FJ101" t="inlineStr"/>
+      <c r="FK101" t="inlineStr"/>
+      <c r="FL101" t="inlineStr"/>
+      <c r="FM101" t="inlineStr"/>
+      <c r="FN101" t="inlineStr"/>
+      <c r="FO101" t="inlineStr"/>
+      <c r="FP101" t="inlineStr"/>
+      <c r="FQ101" t="inlineStr"/>
+      <c r="FR101" t="inlineStr"/>
+      <c r="FS101" t="inlineStr"/>
+      <c r="FT101" t="inlineStr"/>
+      <c r="FU101" t="inlineStr"/>
+      <c r="FV101" t="inlineStr"/>
+      <c r="FW101" t="inlineStr"/>
+      <c r="FX101" t="inlineStr"/>
+      <c r="FY101" t="inlineStr"/>
+      <c r="FZ101" t="inlineStr"/>
+      <c r="GA101" t="inlineStr"/>
+      <c r="GB101" t="inlineStr"/>
+      <c r="GC101" t="inlineStr"/>
+      <c r="GD101" t="inlineStr"/>
+      <c r="GE101" t="inlineStr"/>
+      <c r="GF101" t="inlineStr"/>
+      <c r="GG101" t="inlineStr"/>
+      <c r="GH101" t="inlineStr"/>
+      <c r="GI101" t="inlineStr"/>
+      <c r="GJ101" t="inlineStr"/>
+      <c r="GK101" t="inlineStr"/>
+      <c r="GL101" t="inlineStr"/>
+      <c r="GM101" t="inlineStr"/>
+      <c r="GN101" t="inlineStr"/>
+      <c r="GO101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>r97iWUK0</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>hz9iLSns</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>placide johnny</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>dGEFacR1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>bohnert florian</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SGS1GzV5</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>akueson gustave</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>IwWAp1LB</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>guevara juan</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>tIMjIu1I</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>ariss zakaria</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>ronEz0Iq</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>ducrocq tom</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>0hzAGETn</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>janneh jocelyn</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>vVf0mSM7</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>boutrah amine</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>2JHnrhNN</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>gurtner regis</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>buhL1Onn</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>corchia sebastien</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>6944n3Fq</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>fofana mamadou 1998</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>tthiQDjj</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>urhoghide osaze</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>4vxs1tdM</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>vita remy</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>QgfweBPT</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>gene owen</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>6w822cDk</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>leautey antoine</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>EPx2q8TS</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>boya frank</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>UBVYZus6</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>kaiboue kylian</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>zJWNDWUp</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>lutin rayan</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>MFLAEEaI</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>mafouta louis</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>vcfrwUSo</t>
+        </is>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>boumaaoui mohamed amine</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>b9dIWhMU</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>onana cyrille</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>OdiG9Lyg</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>fabri julien</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>4C2mjUxk</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>roncaglia anthony</t>
+        </is>
+      </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>x6p5H6p3</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr">
+        <is>
+          <t>tavares dylan</t>
+        </is>
+      </c>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>pfhFEyG5</t>
+        </is>
+      </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>tomi felix</t>
+        </is>
+      </c>
+      <c r="BH102" t="inlineStr"/>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="inlineStr">
+        <is>
+          <t>xQJX0yQr</t>
+        </is>
+      </c>
+      <c r="BM102" t="inlineStr">
+        <is>
+          <t>bakayoko siaka</t>
+        </is>
+      </c>
+      <c r="BN102" t="inlineStr">
+        <is>
+          <t>fsQHmhiO</t>
+        </is>
+      </c>
+      <c r="BO102" t="inlineStr">
+        <is>
+          <t>carroll andy</t>
+        </is>
+      </c>
+      <c r="BP102" t="inlineStr">
+        <is>
+          <t>UFCV4BZC</t>
+        </is>
+      </c>
+      <c r="BQ102" t="inlineStr">
+        <is>
+          <t>chabane amine</t>
+        </is>
+      </c>
+      <c r="BR102" t="inlineStr">
+        <is>
+          <t>SIEq4Qzk</t>
+        </is>
+      </c>
+      <c r="BS102" t="inlineStr">
+        <is>
+          <t>dao elyess</t>
+        </is>
+      </c>
+      <c r="BT102" t="inlineStr">
+        <is>
+          <t>hKnfwbm3</t>
+        </is>
+      </c>
+      <c r="BU102" t="inlineStr">
+        <is>
+          <t>fofana ibrahim cheick junior</t>
+        </is>
+      </c>
+      <c r="BV102" t="inlineStr">
+        <is>
+          <t>pWfVw1vj</t>
+        </is>
+      </c>
+      <c r="BW102" t="inlineStr">
+        <is>
+          <t>sauvage alexis</t>
+        </is>
+      </c>
+      <c r="BX102" t="inlineStr">
+        <is>
+          <t>CWFxV8dL</t>
+        </is>
+      </c>
+      <c r="BY102" t="inlineStr">
+        <is>
+          <t>touho mathis</t>
+        </is>
+      </c>
+      <c r="BZ102" t="inlineStr"/>
+      <c r="CA102" t="inlineStr"/>
+      <c r="CB102" t="inlineStr"/>
+      <c r="CC102" t="inlineStr"/>
+      <c r="CD102" t="inlineStr">
+        <is>
+          <t>b9dIWhMU</t>
+        </is>
+      </c>
+      <c r="CE102" t="inlineStr">
+        <is>
+          <t>onana cyrille</t>
+        </is>
+      </c>
+      <c r="CF102" t="inlineStr">
+        <is>
+          <t>b9dIWhMU</t>
+        </is>
+      </c>
+      <c r="CG102" t="inlineStr">
+        <is>
+          <t>onana cyrille</t>
+        </is>
+      </c>
+      <c r="CH102" t="inlineStr">
+        <is>
+          <t>0hzAGETn</t>
+        </is>
+      </c>
+      <c r="CI102" t="inlineStr">
+        <is>
+          <t>janneh jocelyn</t>
+        </is>
+      </c>
+      <c r="CJ102" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="CK102" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="CL102" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="CM102" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="CN102" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="CO102" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="CP102" t="inlineStr">
+        <is>
+          <t>4C2mjUxk</t>
+        </is>
+      </c>
+      <c r="CQ102" t="inlineStr">
+        <is>
+          <t>roncaglia anthony</t>
+        </is>
+      </c>
+      <c r="CR102" t="inlineStr">
+        <is>
+          <t>4C2mjUxk</t>
+        </is>
+      </c>
+      <c r="CS102" t="inlineStr">
+        <is>
+          <t>roncaglia anthony</t>
+        </is>
+      </c>
+      <c r="CT102" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="CU102" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="CV102" t="inlineStr">
+        <is>
+          <t>pfhFEyG5</t>
+        </is>
+      </c>
+      <c r="CW102" t="inlineStr">
+        <is>
+          <t>tomi felix</t>
+        </is>
+      </c>
+      <c r="CX102" t="inlineStr">
+        <is>
+          <t>pfhFEyG5</t>
+        </is>
+      </c>
+      <c r="CY102" t="inlineStr">
+        <is>
+          <t>tomi felix</t>
+        </is>
+      </c>
+      <c r="CZ102" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="DA102" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="DB102" t="inlineStr"/>
+      <c r="DC102" t="inlineStr"/>
+      <c r="DD102" t="inlineStr"/>
+      <c r="DE102" t="inlineStr"/>
+      <c r="DF102" t="inlineStr"/>
+      <c r="DG102" t="inlineStr"/>
+      <c r="DH102" t="inlineStr"/>
+      <c r="DI102" t="inlineStr"/>
+      <c r="DJ102" t="inlineStr"/>
+      <c r="DK102" t="inlineStr"/>
+      <c r="DL102" t="inlineStr"/>
+      <c r="DM102" t="inlineStr"/>
+      <c r="DN102" t="inlineStr">
+        <is>
+          <t>CWFxV8dL</t>
+        </is>
+      </c>
+      <c r="DO102" t="inlineStr">
+        <is>
+          <t>touho mathis</t>
+        </is>
+      </c>
+      <c r="DP102" t="inlineStr">
+        <is>
+          <t>CWFxV8dL</t>
+        </is>
+      </c>
+      <c r="DQ102" t="inlineStr">
+        <is>
+          <t>touho mathis</t>
+        </is>
+      </c>
+      <c r="DR102" t="inlineStr">
+        <is>
+          <t>zJWNDWUp</t>
+        </is>
+      </c>
+      <c r="DS102" t="inlineStr">
+        <is>
+          <t>lutin rayan</t>
+        </is>
+      </c>
+      <c r="DT102" t="inlineStr">
+        <is>
+          <t>fsQHmhiO</t>
+        </is>
+      </c>
+      <c r="DU102" t="inlineStr">
+        <is>
+          <t>carroll andy</t>
+        </is>
+      </c>
+      <c r="DV102" t="inlineStr">
+        <is>
+          <t>fsQHmhiO</t>
+        </is>
+      </c>
+      <c r="DW102" t="inlineStr">
+        <is>
+          <t>carroll andy</t>
+        </is>
+      </c>
+      <c r="DX102" t="inlineStr">
+        <is>
+          <t>EPx2q8TS</t>
+        </is>
+      </c>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>boya frank</t>
+        </is>
+      </c>
+      <c r="DZ102" t="inlineStr">
+        <is>
+          <t>hKnfwbm3</t>
+        </is>
+      </c>
+      <c r="EA102" t="inlineStr">
+        <is>
+          <t>fofana ibrahim cheick junior</t>
+        </is>
+      </c>
+      <c r="EB102" t="inlineStr">
+        <is>
+          <t>hKnfwbm3</t>
+        </is>
+      </c>
+      <c r="EC102" t="inlineStr">
+        <is>
+          <t>fofana ibrahim cheick junior</t>
+        </is>
+      </c>
+      <c r="ED102" t="inlineStr">
+        <is>
+          <t>UBVYZus6</t>
+        </is>
+      </c>
+      <c r="EE102" t="inlineStr">
+        <is>
+          <t>kaiboue kylian</t>
+        </is>
+      </c>
+      <c r="EF102" t="inlineStr">
+        <is>
+          <t>SIEq4Qzk</t>
+        </is>
+      </c>
+      <c r="EG102" t="inlineStr">
+        <is>
+          <t>dao elyess</t>
+        </is>
+      </c>
+      <c r="EH102" t="inlineStr">
+        <is>
+          <t>SIEq4Qzk</t>
+        </is>
+      </c>
+      <c r="EI102" t="inlineStr">
+        <is>
+          <t>dao elyess</t>
+        </is>
+      </c>
+      <c r="EJ102" t="inlineStr">
+        <is>
+          <t>6w822cDk</t>
+        </is>
+      </c>
+      <c r="EK102" t="inlineStr">
+        <is>
+          <t>leautey antoine</t>
+        </is>
+      </c>
+      <c r="EL102" t="inlineStr"/>
+      <c r="EM102" t="inlineStr"/>
+      <c r="EN102" t="inlineStr"/>
+      <c r="EO102" t="inlineStr"/>
+      <c r="EP102" t="inlineStr"/>
+      <c r="EQ102" t="inlineStr"/>
+      <c r="ER102" t="inlineStr"/>
+      <c r="ES102" t="inlineStr"/>
+      <c r="ET102" t="inlineStr"/>
+      <c r="EU102" t="inlineStr"/>
+      <c r="EV102" t="inlineStr"/>
+      <c r="EW102" t="inlineStr"/>
+      <c r="EX102" t="inlineStr"/>
+      <c r="EY102" t="inlineStr"/>
+      <c r="EZ102" t="inlineStr"/>
+      <c r="FA102" t="inlineStr"/>
+      <c r="FB102" t="inlineStr"/>
+      <c r="FC102" t="inlineStr"/>
+      <c r="FD102" t="inlineStr"/>
+      <c r="FE102" t="inlineStr"/>
+      <c r="FF102" t="inlineStr"/>
+      <c r="FG102" t="inlineStr"/>
+      <c r="FH102" t="inlineStr"/>
+      <c r="FI102" t="inlineStr"/>
+      <c r="FJ102" t="inlineStr"/>
+      <c r="FK102" t="inlineStr"/>
+      <c r="FL102" t="inlineStr"/>
+      <c r="FM102" t="inlineStr"/>
+      <c r="FN102" t="inlineStr"/>
+      <c r="FO102" t="inlineStr"/>
+      <c r="FP102" t="inlineStr"/>
+      <c r="FQ102" t="inlineStr"/>
+      <c r="FR102" t="inlineStr"/>
+      <c r="FS102" t="inlineStr"/>
+      <c r="FT102" t="inlineStr"/>
+      <c r="FU102" t="inlineStr"/>
+      <c r="FV102" t="inlineStr"/>
+      <c r="FW102" t="inlineStr"/>
+      <c r="FX102" t="inlineStr"/>
+      <c r="FY102" t="inlineStr"/>
+      <c r="FZ102" t="inlineStr"/>
+      <c r="GA102" t="inlineStr"/>
+      <c r="GB102" t="inlineStr"/>
+      <c r="GC102" t="inlineStr"/>
+      <c r="GD102" t="inlineStr"/>
+      <c r="GE102" t="inlineStr"/>
+      <c r="GF102" t="inlineStr"/>
+      <c r="GG102" t="inlineStr"/>
+      <c r="GH102" t="inlineStr"/>
+      <c r="GI102" t="inlineStr"/>
+      <c r="GJ102" t="inlineStr"/>
+      <c r="GK102" t="inlineStr"/>
+      <c r="GL102" t="inlineStr"/>
+      <c r="GM102" t="inlineStr"/>
+      <c r="GN102" t="inlineStr"/>
+      <c r="GO102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>MaSQpUZg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Whzw3G5K</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>samassa mamadou</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>KbXo1rjj</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>vargas thibault</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Amfeubd3</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>adilehou moise</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Wh6NlULE</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>tavares yohan</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>QyXR4UTq</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>kouassi christ owen</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>h2wDEAtM</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>cherni amine</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>UBp43Hs9</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>roye jimmy</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>0IAHPMVG</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>thomas titouan</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>xjWxEtds</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>sanna sam</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>8S3SWHBn</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>tchokounte malik</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>8Y0L4o9I</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>kadile junior</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>A9ux8Ef8</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>basilio enzo</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>4tt9cPfg</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>sissoko alpha</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>fsOSS7y0</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>riou mathis</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>KAGBPuyQ</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>nair sohaib</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>QPweXact</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>vallier lenny</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>McCSZuxs</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>sagna amadou</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>pC1OCXV4</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>louiserre dylan</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>29krq31i</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>sidibe kalidou</t>
+        </is>
+      </c>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>GxfU6qGd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>picard hugo</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>27PxWKIj</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>hemia amine</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>GxWPthlH</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>siwe jacques</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>OpjMuJEk</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>goncalves anthony</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>zXm9ns79</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>hautbois maxime</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>0K3veiZ5</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>kokolo williams</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>h0KBtgkc</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>martins lois</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>lIDA7uHl</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>ouaneh peter</t>
+        </is>
+      </c>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>2JZ0HH6Q</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr">
+        <is>
+          <t>sellouki malik</t>
+        </is>
+      </c>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>W2tc6ZMa</t>
+        </is>
+      </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>zohi kevin</t>
+        </is>
+      </c>
+      <c r="BH103" t="inlineStr"/>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="inlineStr">
+        <is>
+          <t>Odr6gL7i</t>
+        </is>
+      </c>
+      <c r="BM103" t="inlineStr">
+        <is>
+          <t>guendouz sabri</t>
+        </is>
+      </c>
+      <c r="BN103" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="BO103" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="BP103" t="inlineStr">
+        <is>
+          <t>8IfBwmXp</t>
+        </is>
+      </c>
+      <c r="BQ103" t="inlineStr">
+        <is>
+          <t>maronnier lucas</t>
+        </is>
+      </c>
+      <c r="BR103" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="BS103" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="BT103" t="inlineStr">
+        <is>
+          <t>EFZ6icqq</t>
+        </is>
+      </c>
+      <c r="BU103" t="inlineStr">
+        <is>
+          <t>mbaye babacar</t>
+        </is>
+      </c>
+      <c r="BV103" t="inlineStr">
+        <is>
+          <t>GttDZAgH</t>
+        </is>
+      </c>
+      <c r="BW103" t="inlineStr">
+        <is>
+          <t>planeix idriss</t>
+        </is>
+      </c>
+      <c r="BX103" t="inlineStr">
+        <is>
+          <t>t8ya9KXl</t>
+        </is>
+      </c>
+      <c r="BY103" t="inlineStr">
+        <is>
+          <t>touzghar rayan</t>
+        </is>
+      </c>
+      <c r="BZ103" t="inlineStr"/>
+      <c r="CA103" t="inlineStr"/>
+      <c r="CB103" t="inlineStr"/>
+      <c r="CC103" t="inlineStr"/>
+      <c r="CD103" t="inlineStr">
+        <is>
+          <t>W2tc6ZMa</t>
+        </is>
+      </c>
+      <c r="CE103" t="inlineStr">
+        <is>
+          <t>zohi kevin</t>
+        </is>
+      </c>
+      <c r="CF103" t="inlineStr">
+        <is>
+          <t>W2tc6ZMa</t>
+        </is>
+      </c>
+      <c r="CG103" t="inlineStr">
+        <is>
+          <t>zohi kevin</t>
+        </is>
+      </c>
+      <c r="CH103" t="inlineStr">
+        <is>
+          <t>Amfeubd3</t>
+        </is>
+      </c>
+      <c r="CI103" t="inlineStr">
+        <is>
+          <t>adilehou moise</t>
+        </is>
+      </c>
+      <c r="CJ103" t="inlineStr">
+        <is>
+          <t>2JZ0HH6Q</t>
+        </is>
+      </c>
+      <c r="CK103" t="inlineStr">
+        <is>
+          <t>sellouki malik</t>
+        </is>
+      </c>
+      <c r="CL103" t="inlineStr">
+        <is>
+          <t>2JZ0HH6Q</t>
+        </is>
+      </c>
+      <c r="CM103" t="inlineStr">
+        <is>
+          <t>sellouki malik</t>
+        </is>
+      </c>
+      <c r="CN103" t="inlineStr">
+        <is>
+          <t>UBp43Hs9</t>
+        </is>
+      </c>
+      <c r="CO103" t="inlineStr">
+        <is>
+          <t>roye jimmy</t>
+        </is>
+      </c>
+      <c r="CP103" t="inlineStr">
+        <is>
+          <t>0K3veiZ5</t>
+        </is>
+      </c>
+      <c r="CQ103" t="inlineStr">
+        <is>
+          <t>kokolo williams</t>
+        </is>
+      </c>
+      <c r="CR103" t="inlineStr">
+        <is>
+          <t>0K3veiZ5</t>
+        </is>
+      </c>
+      <c r="CS103" t="inlineStr">
+        <is>
+          <t>kokolo williams</t>
+        </is>
+      </c>
+      <c r="CT103" t="inlineStr">
+        <is>
+          <t>h2wDEAtM</t>
+        </is>
+      </c>
+      <c r="CU103" t="inlineStr">
+        <is>
+          <t>cherni amine</t>
+        </is>
+      </c>
+      <c r="CV103" t="inlineStr">
+        <is>
+          <t>OpjMuJEk</t>
+        </is>
+      </c>
+      <c r="CW103" t="inlineStr">
+        <is>
+          <t>goncalves anthony</t>
+        </is>
+      </c>
+      <c r="CX103" t="inlineStr">
+        <is>
+          <t>OpjMuJEk</t>
+        </is>
+      </c>
+      <c r="CY103" t="inlineStr">
+        <is>
+          <t>goncalves anthony</t>
+        </is>
+      </c>
+      <c r="CZ103" t="inlineStr">
+        <is>
+          <t>KbXo1rjj</t>
+        </is>
+      </c>
+      <c r="DA103" t="inlineStr">
+        <is>
+          <t>vargas thibault</t>
+        </is>
+      </c>
+      <c r="DB103" t="inlineStr">
+        <is>
+          <t>h0KBtgkc</t>
+        </is>
+      </c>
+      <c r="DC103" t="inlineStr">
+        <is>
+          <t>martins lois</t>
+        </is>
+      </c>
+      <c r="DD103" t="inlineStr">
+        <is>
+          <t>h0KBtgkc</t>
+        </is>
+      </c>
+      <c r="DE103" t="inlineStr">
+        <is>
+          <t>martins lois</t>
+        </is>
+      </c>
+      <c r="DF103" t="inlineStr">
+        <is>
+          <t>xjWxEtds</t>
+        </is>
+      </c>
+      <c r="DG103" t="inlineStr">
+        <is>
+          <t>sanna sam</t>
+        </is>
+      </c>
+      <c r="DH103" t="inlineStr"/>
+      <c r="DI103" t="inlineStr"/>
+      <c r="DJ103" t="inlineStr"/>
+      <c r="DK103" t="inlineStr"/>
+      <c r="DL103" t="inlineStr"/>
+      <c r="DM103" t="inlineStr"/>
+      <c r="DN103" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="DO103" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="DP103" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="DQ103" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="DR103" t="inlineStr">
+        <is>
+          <t>McCSZuxs</t>
+        </is>
+      </c>
+      <c r="DS103" t="inlineStr">
+        <is>
+          <t>sagna amadou</t>
+        </is>
+      </c>
+      <c r="DT103" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="DU103" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="DV103" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="DW103" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="DX103" t="inlineStr">
+        <is>
+          <t>GxWPthlH</t>
+        </is>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>siwe jacques</t>
+        </is>
+      </c>
+      <c r="DZ103" t="inlineStr">
+        <is>
+          <t>Odr6gL7i</t>
+        </is>
+      </c>
+      <c r="EA103" t="inlineStr">
+        <is>
+          <t>guendouz sabri</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>Odr6gL7i</t>
+        </is>
+      </c>
+      <c r="EC103" t="inlineStr">
+        <is>
+          <t>guendouz sabri</t>
+        </is>
+      </c>
+      <c r="ED103" t="inlineStr">
+        <is>
+          <t>27PxWKIj</t>
+        </is>
+      </c>
+      <c r="EE103" t="inlineStr">
+        <is>
+          <t>hemia amine</t>
+        </is>
+      </c>
+      <c r="EF103" t="inlineStr"/>
+      <c r="EG103" t="inlineStr"/>
+      <c r="EH103" t="inlineStr"/>
+      <c r="EI103" t="inlineStr"/>
+      <c r="EJ103" t="inlineStr"/>
+      <c r="EK103" t="inlineStr"/>
+      <c r="EL103" t="inlineStr"/>
+      <c r="EM103" t="inlineStr"/>
+      <c r="EN103" t="inlineStr"/>
+      <c r="EO103" t="inlineStr"/>
+      <c r="EP103" t="inlineStr"/>
+      <c r="EQ103" t="inlineStr"/>
+      <c r="ER103" t="inlineStr"/>
+      <c r="ES103" t="inlineStr"/>
+      <c r="ET103" t="inlineStr"/>
+      <c r="EU103" t="inlineStr"/>
+      <c r="EV103" t="inlineStr"/>
+      <c r="EW103" t="inlineStr"/>
+      <c r="EX103" t="inlineStr"/>
+      <c r="EY103" t="inlineStr"/>
+      <c r="EZ103" t="inlineStr"/>
+      <c r="FA103" t="inlineStr"/>
+      <c r="FB103" t="inlineStr"/>
+      <c r="FC103" t="inlineStr"/>
+      <c r="FD103" t="inlineStr"/>
+      <c r="FE103" t="inlineStr"/>
+      <c r="FF103" t="inlineStr"/>
+      <c r="FG103" t="inlineStr"/>
+      <c r="FH103" t="inlineStr"/>
+      <c r="FI103" t="inlineStr"/>
+      <c r="FJ103" t="inlineStr"/>
+      <c r="FK103" t="inlineStr"/>
+      <c r="FL103" t="inlineStr"/>
+      <c r="FM103" t="inlineStr"/>
+      <c r="FN103" t="inlineStr"/>
+      <c r="FO103" t="inlineStr"/>
+      <c r="FP103" t="inlineStr"/>
+      <c r="FQ103" t="inlineStr"/>
+      <c r="FR103" t="inlineStr"/>
+      <c r="FS103" t="inlineStr"/>
+      <c r="FT103" t="inlineStr"/>
+      <c r="FU103" t="inlineStr"/>
+      <c r="FV103" t="inlineStr"/>
+      <c r="FW103" t="inlineStr"/>
+      <c r="FX103" t="inlineStr"/>
+      <c r="FY103" t="inlineStr"/>
+      <c r="FZ103" t="inlineStr"/>
+      <c r="GA103" t="inlineStr"/>
+      <c r="GB103" t="inlineStr"/>
+      <c r="GC103" t="inlineStr"/>
+      <c r="GD103" t="inlineStr"/>
+      <c r="GE103" t="inlineStr"/>
+      <c r="GF103" t="inlineStr"/>
+      <c r="GG103" t="inlineStr"/>
+      <c r="GH103" t="inlineStr"/>
+      <c r="GI103" t="inlineStr"/>
+      <c r="GJ103" t="inlineStr"/>
+      <c r="GK103" t="inlineStr"/>
+      <c r="GL103" t="inlineStr"/>
+      <c r="GM103" t="inlineStr"/>
+      <c r="GN103" t="inlineStr"/>
+      <c r="GO103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>WUmnhCsK</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Uc1khkvm</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>nkambadio obed</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>jcMPmwUo</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>tourraine mathys</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>8UK1HbMC</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>mbow mamadou</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>6Nrp053I</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>kolodziejczak timothee</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>t2wVToOG</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>ollila tuomas</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>dvCqyKNu</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>doucet lohann</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>6Ze5jFyJ</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>marchetti vincent</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>zZWv9QAr</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>camara adama</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>8zzd9I9p</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>kebbal ilan</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>MDGk7mZd</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>krasso jean philippe</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>jyzyc1pE</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>jaouen ewen</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>GOqK3T14</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>youssouf benjaloud</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>CSpt7BMu</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>sangante opa</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>UZzd4sDM</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>sasso vincent</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>EagFLcyg</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>abner</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>8zK6oP8a</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>georgen alec</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>WSXgQK56</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>bardeli enzo</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>6RvNumuL</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>sekongo anto</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>OrSsAkI5</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>tehan kaj</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>KQnM7QoO</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>courtet gaetan</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>Kh3fmMhH</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>rivera maxence</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>pzIqHPOJ</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>dicko nouha</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>EyOk88TC</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>himeur thomas</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>nq2AGvHL</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>lukembila josias</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>niLz9KKj</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>soumahoro aboubaka</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr"/>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="BM104" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="BN104" t="inlineStr">
+        <is>
+          <t>K6JcFKeq</t>
+        </is>
+      </c>
+      <c r="BO104" t="inlineStr">
+        <is>
+          <t>bessile loic</t>
+        </is>
+      </c>
+      <c r="BP104" t="inlineStr">
+        <is>
+          <t>O8JvUz1C</t>
+        </is>
+      </c>
+      <c r="BQ104" t="inlineStr">
+        <is>
+          <t>essimi marco</t>
+        </is>
+      </c>
+      <c r="BR104" t="inlineStr">
+        <is>
+          <t>OnyqUWvJ</t>
+        </is>
+      </c>
+      <c r="BS104" t="inlineStr">
+        <is>
+          <t>fernandez nehemiah</t>
+        </is>
+      </c>
+      <c r="BT104" t="inlineStr">
+        <is>
+          <t>numxuYP2</t>
+        </is>
+      </c>
+      <c r="BU104" t="inlineStr">
+        <is>
+          <t>kondo geoffrey</t>
+        </is>
+      </c>
+      <c r="BV104" t="inlineStr">
+        <is>
+          <t>6utqVfCd</t>
+        </is>
+      </c>
+      <c r="BW104" t="inlineStr">
+        <is>
+          <t>kone ibrahim</t>
+        </is>
+      </c>
+      <c r="BX104" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="BY104" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="BZ104" t="inlineStr"/>
+      <c r="CA104" t="inlineStr"/>
+      <c r="CB104" t="inlineStr"/>
+      <c r="CC104" t="inlineStr"/>
+      <c r="CD104" t="inlineStr">
+        <is>
+          <t>pzIqHPOJ</t>
+        </is>
+      </c>
+      <c r="CE104" t="inlineStr">
+        <is>
+          <t>dicko nouha</t>
+        </is>
+      </c>
+      <c r="CF104" t="inlineStr">
+        <is>
+          <t>pzIqHPOJ</t>
+        </is>
+      </c>
+      <c r="CG104" t="inlineStr">
+        <is>
+          <t>dicko nouha</t>
+        </is>
+      </c>
+      <c r="CH104" t="inlineStr">
+        <is>
+          <t>zZWv9QAr</t>
+        </is>
+      </c>
+      <c r="CI104" t="inlineStr">
+        <is>
+          <t>camara adama</t>
+        </is>
+      </c>
+      <c r="CJ104" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="CK104" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="CL104" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="CM104" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="CN104" t="inlineStr">
+        <is>
+          <t>8zzd9I9p</t>
+        </is>
+      </c>
+      <c r="CO104" t="inlineStr">
+        <is>
+          <t>kebbal ilan</t>
+        </is>
+      </c>
+      <c r="CP104" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="CQ104" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="CR104" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="CS104" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="CT104" t="inlineStr">
+        <is>
+          <t>t2wVToOG</t>
+        </is>
+      </c>
+      <c r="CU104" t="inlineStr">
+        <is>
+          <t>ollila tuomas</t>
+        </is>
+      </c>
+      <c r="CV104" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="CW104" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="CX104" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="CY104" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="CZ104" t="inlineStr">
+        <is>
+          <t>MDGk7mZd</t>
+        </is>
+      </c>
+      <c r="DA104" t="inlineStr">
+        <is>
+          <t>krasso jean philippe</t>
+        </is>
+      </c>
+      <c r="DB104" t="inlineStr">
+        <is>
+          <t>nq2AGvHL</t>
+        </is>
+      </c>
+      <c r="DC104" t="inlineStr">
+        <is>
+          <t>lukembila josias</t>
+        </is>
+      </c>
+      <c r="DD104" t="inlineStr">
+        <is>
+          <t>nq2AGvHL</t>
+        </is>
+      </c>
+      <c r="DE104" t="inlineStr">
+        <is>
+          <t>lukembila josias</t>
+        </is>
+      </c>
+      <c r="DF104" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="DG104" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="DH104" t="inlineStr"/>
+      <c r="DI104" t="inlineStr"/>
+      <c r="DJ104" t="inlineStr"/>
+      <c r="DK104" t="inlineStr"/>
+      <c r="DL104" t="inlineStr"/>
+      <c r="DM104" t="inlineStr"/>
+      <c r="DN104" t="inlineStr">
+        <is>
+          <t>numxuYP2</t>
+        </is>
+      </c>
+      <c r="DO104" t="inlineStr">
+        <is>
+          <t>kondo geoffrey</t>
+        </is>
+      </c>
+      <c r="DP104" t="inlineStr">
+        <is>
+          <t>numxuYP2</t>
+        </is>
+      </c>
+      <c r="DQ104" t="inlineStr">
+        <is>
+          <t>kondo geoffrey</t>
+        </is>
+      </c>
+      <c r="DR104" t="inlineStr">
+        <is>
+          <t>EagFLcyg</t>
+        </is>
+      </c>
+      <c r="DS104" t="inlineStr">
+        <is>
+          <t>abner</t>
+        </is>
+      </c>
+      <c r="DT104" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="DU104" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="DV104" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="DW104" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="DX104" t="inlineStr">
+        <is>
+          <t>OrSsAkI5</t>
+        </is>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>tehan kaj</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>OnyqUWvJ</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>fernandez nehemiah</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>OnyqUWvJ</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr">
+        <is>
+          <t>fernandez nehemiah</t>
+        </is>
+      </c>
+      <c r="ED104" t="inlineStr">
+        <is>
+          <t>8zK6oP8a</t>
+        </is>
+      </c>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>georgen alec</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr">
+        <is>
+          <t>Kh3fmMhH</t>
+        </is>
+      </c>
+      <c r="EK104" t="inlineStr">
+        <is>
+          <t>rivera maxence</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr"/>
+      <c r="EM104" t="inlineStr"/>
+      <c r="EN104" t="inlineStr"/>
+      <c r="EO104" t="inlineStr"/>
+      <c r="EP104" t="inlineStr"/>
+      <c r="EQ104" t="inlineStr"/>
+      <c r="ER104" t="inlineStr"/>
+      <c r="ES104" t="inlineStr"/>
+      <c r="ET104" t="inlineStr"/>
+      <c r="EU104" t="inlineStr"/>
+      <c r="EV104" t="inlineStr"/>
+      <c r="EW104" t="inlineStr"/>
+      <c r="EX104" t="inlineStr"/>
+      <c r="EY104" t="inlineStr"/>
+      <c r="EZ104" t="inlineStr"/>
+      <c r="FA104" t="inlineStr"/>
+      <c r="FB104" t="inlineStr"/>
+      <c r="FC104" t="inlineStr"/>
+      <c r="FD104" t="inlineStr"/>
+      <c r="FE104" t="inlineStr"/>
+      <c r="FF104" t="inlineStr"/>
+      <c r="FG104" t="inlineStr"/>
+      <c r="FH104" t="inlineStr"/>
+      <c r="FI104" t="inlineStr"/>
+      <c r="FJ104" t="inlineStr"/>
+      <c r="FK104" t="inlineStr"/>
+      <c r="FL104" t="inlineStr"/>
+      <c r="FM104" t="inlineStr"/>
+      <c r="FN104" t="inlineStr"/>
+      <c r="FO104" t="inlineStr"/>
+      <c r="FP104" t="inlineStr"/>
+      <c r="FQ104" t="inlineStr"/>
+      <c r="FR104" t="inlineStr"/>
+      <c r="FS104" t="inlineStr"/>
+      <c r="FT104" t="inlineStr"/>
+      <c r="FU104" t="inlineStr"/>
+      <c r="FV104" t="inlineStr"/>
+      <c r="FW104" t="inlineStr"/>
+      <c r="FX104" t="inlineStr"/>
+      <c r="FY104" t="inlineStr"/>
+      <c r="FZ104" t="inlineStr"/>
+      <c r="GA104" t="inlineStr"/>
+      <c r="GB104" t="inlineStr"/>
+      <c r="GC104" t="inlineStr"/>
+      <c r="GD104" t="inlineStr"/>
+      <c r="GE104" t="inlineStr"/>
+      <c r="GF104" t="inlineStr"/>
+      <c r="GG104" t="inlineStr"/>
+      <c r="GH104" t="inlineStr"/>
+      <c r="GI104" t="inlineStr"/>
+      <c r="GJ104" t="inlineStr"/>
+      <c r="GK104" t="inlineStr"/>
+      <c r="GL104" t="inlineStr"/>
+      <c r="GM104" t="inlineStr"/>
+      <c r="GN104" t="inlineStr"/>
+      <c r="GO104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>nsErYjjl</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UqwxErXc</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>kamara bingourou</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>UVcaeNxh</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>gaspar jordy</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>f77lo10C</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ahoussou kouadio guy ange</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>A1JE6XmB</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ruiz jean</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>xUaIYbZa</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>koudou therence</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>UTeVGQBo</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>ngom oumar</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>K0sjhCJO</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>mohamed iyad</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>ManhCoID</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>arconte tairyk</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>GjoN5Ete</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>mille antoine</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>CrYHlkps</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>mboup pathe</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>GUQFSOu2</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>boutaib khalid</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>0QluvG6s</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>mandrea anthony</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>Ojlo3DFG</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>vandermersch hugo</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>YaDc8KUo</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>diedounne debohi</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>v1nbamR8</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>thomas romain</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>h4HteEDA</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>abdi ali</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>GOdGE1cn</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>m vila yann</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>6qDAkr52</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>keyremeh godson</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>nTSAxkMK</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>lebreton noe</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>OnEUHb2t</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>rajot lorenzo</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>YLpVZgK4</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>le bihan mickael</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>As2skget</t>
+        </is>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>bongelo fidele maolcolm</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>EVE3oJPN</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>gomes tom</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>AXCqL4Qp</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>jeannin mehdi</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>EZQeQxef</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>kalulu joseph</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>EJuazaLT</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>kante ousmane</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>Ollmu17h</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>njoh yonis</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr"/>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="inlineStr">
+        <is>
+          <t>EuWckL8D</t>
+        </is>
+      </c>
+      <c r="BM105" t="inlineStr">
+        <is>
+          <t>bagbema zoumana</t>
+        </is>
+      </c>
+      <c r="BN105" t="inlineStr">
+        <is>
+          <t>zRkxtbt5</t>
+        </is>
+      </c>
+      <c r="BO105" t="inlineStr">
+        <is>
+          <t>clementia yannis</t>
+        </is>
+      </c>
+      <c r="BP105" t="inlineStr">
+        <is>
+          <t>byAFdWP0</t>
+        </is>
+      </c>
+      <c r="BQ105" t="inlineStr">
+        <is>
+          <t>gomis tidiam</t>
+        </is>
+      </c>
+      <c r="BR105" t="inlineStr">
+        <is>
+          <t>r5ZrGvqR</t>
+        </is>
+      </c>
+      <c r="BS105" t="inlineStr">
+        <is>
+          <t>hafid mohamed</t>
+        </is>
+      </c>
+      <c r="BT105" t="inlineStr">
+        <is>
+          <t>487CQIYM</t>
+        </is>
+      </c>
+      <c r="BU105" t="inlineStr">
+        <is>
+          <t>meddah daylam</t>
+        </is>
+      </c>
+      <c r="BV105" t="inlineStr">
+        <is>
+          <t>fikV9v0s</t>
+        </is>
+      </c>
+      <c r="BW105" t="inlineStr">
+        <is>
+          <t>milliner leo</t>
+        </is>
+      </c>
+      <c r="BX105" t="inlineStr">
+        <is>
+          <t>KIfK6TkH</t>
+        </is>
+      </c>
+      <c r="BY105" t="inlineStr">
+        <is>
+          <t>verhaeghe robin</t>
+        </is>
+      </c>
+      <c r="BZ105" t="inlineStr"/>
+      <c r="CA105" t="inlineStr"/>
+      <c r="CB105" t="inlineStr"/>
+      <c r="CC105" t="inlineStr"/>
+      <c r="CD105" t="inlineStr">
+        <is>
+          <t>EJuazaLT</t>
+        </is>
+      </c>
+      <c r="CE105" t="inlineStr">
+        <is>
+          <t>kante ousmane</t>
+        </is>
+      </c>
+      <c r="CF105" t="inlineStr">
+        <is>
+          <t>EJuazaLT</t>
+        </is>
+      </c>
+      <c r="CG105" t="inlineStr">
+        <is>
+          <t>kante ousmane</t>
+        </is>
+      </c>
+      <c r="CH105" t="inlineStr">
+        <is>
+          <t>ManhCoID</t>
+        </is>
+      </c>
+      <c r="CI105" t="inlineStr">
+        <is>
+          <t>arconte tairyk</t>
+        </is>
+      </c>
+      <c r="CJ105" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="CK105" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="CL105" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="CM105" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="CN105" t="inlineStr">
+        <is>
+          <t>GjoN5Ete</t>
+        </is>
+      </c>
+      <c r="CO105" t="inlineStr">
+        <is>
+          <t>mille antoine</t>
+        </is>
+      </c>
+      <c r="CP105" t="inlineStr">
+        <is>
+          <t>Ollmu17h</t>
+        </is>
+      </c>
+      <c r="CQ105" t="inlineStr">
+        <is>
+          <t>njoh yonis</t>
+        </is>
+      </c>
+      <c r="CR105" t="inlineStr">
+        <is>
+          <t>Ollmu17h</t>
+        </is>
+      </c>
+      <c r="CS105" t="inlineStr">
+        <is>
+          <t>njoh yonis</t>
+        </is>
+      </c>
+      <c r="CT105" t="inlineStr">
+        <is>
+          <t>CrYHlkps</t>
+        </is>
+      </c>
+      <c r="CU105" t="inlineStr">
+        <is>
+          <t>mboup pathe</t>
+        </is>
+      </c>
+      <c r="CV105" t="inlineStr">
+        <is>
+          <t>EZQeQxef</t>
+        </is>
+      </c>
+      <c r="CW105" t="inlineStr">
+        <is>
+          <t>kalulu joseph</t>
+        </is>
+      </c>
+      <c r="CX105" t="inlineStr">
+        <is>
+          <t>EZQeQxef</t>
+        </is>
+      </c>
+      <c r="CY105" t="inlineStr">
+        <is>
+          <t>kalulu joseph</t>
+        </is>
+      </c>
+      <c r="CZ105" t="inlineStr">
+        <is>
+          <t>xUaIYbZa</t>
+        </is>
+      </c>
+      <c r="DA105" t="inlineStr">
+        <is>
+          <t>koudou therence</t>
+        </is>
+      </c>
+      <c r="DB105" t="inlineStr">
+        <is>
+          <t>EVE3oJPN</t>
+        </is>
+      </c>
+      <c r="DC105" t="inlineStr">
+        <is>
+          <t>gomes tom</t>
+        </is>
+      </c>
+      <c r="DD105" t="inlineStr">
+        <is>
+          <t>EVE3oJPN</t>
+        </is>
+      </c>
+      <c r="DE105" t="inlineStr">
+        <is>
+          <t>gomes tom</t>
+        </is>
+      </c>
+      <c r="DF105" t="inlineStr">
+        <is>
+          <t>A1JE6XmB</t>
+        </is>
+      </c>
+      <c r="DG105" t="inlineStr">
+        <is>
+          <t>ruiz jean</t>
+        </is>
+      </c>
+      <c r="DH105" t="inlineStr"/>
+      <c r="DI105" t="inlineStr"/>
+      <c r="DJ105" t="inlineStr"/>
+      <c r="DK105" t="inlineStr"/>
+      <c r="DL105" t="inlineStr"/>
+      <c r="DM105" t="inlineStr"/>
+      <c r="DN105" t="inlineStr">
+        <is>
+          <t>byAFdWP0</t>
+        </is>
+      </c>
+      <c r="DO105" t="inlineStr">
+        <is>
+          <t>gomis tidiam</t>
+        </is>
+      </c>
+      <c r="DP105" t="inlineStr">
+        <is>
+          <t>byAFdWP0</t>
+        </is>
+      </c>
+      <c r="DQ105" t="inlineStr">
+        <is>
+          <t>gomis tidiam</t>
+        </is>
+      </c>
+      <c r="DR105" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="DS105" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="DT105" t="inlineStr">
+        <is>
+          <t>487CQIYM</t>
+        </is>
+      </c>
+      <c r="DU105" t="inlineStr">
+        <is>
+          <t>meddah daylam</t>
+        </is>
+      </c>
+      <c r="DV105" t="inlineStr">
+        <is>
+          <t>487CQIYM</t>
+        </is>
+      </c>
+      <c r="DW105" t="inlineStr">
+        <is>
+          <t>meddah daylam</t>
+        </is>
+      </c>
+      <c r="DX105" t="inlineStr">
+        <is>
+          <t>YaDc8KUo</t>
+        </is>
+      </c>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>diedounne debohi</t>
+        </is>
+      </c>
+      <c r="DZ105" t="inlineStr">
+        <is>
+          <t>fikV9v0s</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr">
+        <is>
+          <t>milliner leo</t>
+        </is>
+      </c>
+      <c r="EB105" t="inlineStr">
+        <is>
+          <t>fikV9v0s</t>
+        </is>
+      </c>
+      <c r="EC105" t="inlineStr">
+        <is>
+          <t>milliner leo</t>
+        </is>
+      </c>
+      <c r="ED105" t="inlineStr">
+        <is>
+          <t>OnEUHb2t</t>
+        </is>
+      </c>
+      <c r="EE105" t="inlineStr">
+        <is>
+          <t>rajot lorenzo</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr">
+        <is>
+          <t>r5ZrGvqR</t>
+        </is>
+      </c>
+      <c r="EG105" t="inlineStr">
+        <is>
+          <t>hafid mohamed</t>
+        </is>
+      </c>
+      <c r="EH105" t="inlineStr">
+        <is>
+          <t>r5ZrGvqR</t>
+        </is>
+      </c>
+      <c r="EI105" t="inlineStr">
+        <is>
+          <t>hafid mohamed</t>
+        </is>
+      </c>
+      <c r="EJ105" t="inlineStr">
+        <is>
+          <t>nTSAxkMK</t>
+        </is>
+      </c>
+      <c r="EK105" t="inlineStr">
+        <is>
+          <t>lebreton noe</t>
+        </is>
+      </c>
+      <c r="EL105" t="inlineStr"/>
+      <c r="EM105" t="inlineStr"/>
+      <c r="EN105" t="inlineStr"/>
+      <c r="EO105" t="inlineStr"/>
+      <c r="EP105" t="inlineStr"/>
+      <c r="EQ105" t="inlineStr"/>
+      <c r="ER105" t="inlineStr"/>
+      <c r="ES105" t="inlineStr"/>
+      <c r="ET105" t="inlineStr"/>
+      <c r="EU105" t="inlineStr"/>
+      <c r="EV105" t="inlineStr"/>
+      <c r="EW105" t="inlineStr"/>
+      <c r="EX105" t="inlineStr"/>
+      <c r="EY105" t="inlineStr"/>
+      <c r="EZ105" t="inlineStr"/>
+      <c r="FA105" t="inlineStr"/>
+      <c r="FB105" t="inlineStr"/>
+      <c r="FC105" t="inlineStr"/>
+      <c r="FD105" t="inlineStr"/>
+      <c r="FE105" t="inlineStr"/>
+      <c r="FF105" t="inlineStr"/>
+      <c r="FG105" t="inlineStr"/>
+      <c r="FH105" t="inlineStr"/>
+      <c r="FI105" t="inlineStr"/>
+      <c r="FJ105" t="inlineStr"/>
+      <c r="FK105" t="inlineStr"/>
+      <c r="FL105" t="inlineStr"/>
+      <c r="FM105" t="inlineStr"/>
+      <c r="FN105" t="inlineStr"/>
+      <c r="FO105" t="inlineStr"/>
+      <c r="FP105" t="inlineStr"/>
+      <c r="FQ105" t="inlineStr"/>
+      <c r="FR105" t="inlineStr"/>
+      <c r="FS105" t="inlineStr"/>
+      <c r="FT105" t="inlineStr"/>
+      <c r="FU105" t="inlineStr"/>
+      <c r="FV105" t="inlineStr"/>
+      <c r="FW105" t="inlineStr"/>
+      <c r="FX105" t="inlineStr"/>
+      <c r="FY105" t="inlineStr"/>
+      <c r="FZ105" t="inlineStr"/>
+      <c r="GA105" t="inlineStr"/>
+      <c r="GB105" t="inlineStr"/>
+      <c r="GC105" t="inlineStr"/>
+      <c r="GD105" t="inlineStr"/>
+      <c r="GE105" t="inlineStr"/>
+      <c r="GF105" t="inlineStr"/>
+      <c r="GG105" t="inlineStr"/>
+      <c r="GH105" t="inlineStr"/>
+      <c r="GI105" t="inlineStr"/>
+      <c r="GJ105" t="inlineStr"/>
+      <c r="GK105" t="inlineStr"/>
+      <c r="GL105" t="inlineStr"/>
+      <c r="GM105" t="inlineStr"/>
+      <c r="GN105" t="inlineStr"/>
+      <c r="GO105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>UsP4uZcE</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>6kl4UZvQ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>cibois sebastien</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>p2nsMSal</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ngouyamsa ahmad</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>6Vz9xZIb</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>quenabio loni</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>AmGWfem4</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>mambo muzalijoma stone</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>QBWpvgXg</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>bouchouari mohamed</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>b9VtHGuL</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>younoussa wilitty</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>6i5Z1XL8</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>haag giovanni</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>INSa57F7</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>taibi waniss</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Iqjtansb</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>abdallah abdel hakim</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>nZIb4fy3</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>jean dany</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>OhP1S4nf</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>nkada timothee</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>tCw122Zu</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>oukidja alexandre</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>jZhhxxLu</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>traore ismael</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>AuzyopRB</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>udol matthieu</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>ncoSpPJ3</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>kouao koffi</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>GlPxp8Ek</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>deminguet jessy</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>06rZTKMc</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>hein gauthier</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>21NXX0AU</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>cande fali</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>OKRPP19G</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>jallow ablie</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>E5Ot0kk3</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>sabaly cheikh tidiane</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>v9UFU7UB</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>sane ibou</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>46NuxuYs</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>chougrani joris</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>dfjU302n</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>mazou sacko derek</t>
+        </is>
+      </c>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>pzX674k0</t>
+        </is>
+      </c>
+      <c r="BE106" t="inlineStr">
+        <is>
+          <t>mpasi nzau lionel</t>
+        </is>
+      </c>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="BG106" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="BH106" t="inlineStr"/>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="BM106" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="BN106" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="BO106" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="BP106" t="inlineStr">
+        <is>
+          <t>xdl3kAtK</t>
+        </is>
+      </c>
+      <c r="BQ106" t="inlineStr">
+        <is>
+          <t>diallo papa amadou</t>
+        </is>
+      </c>
+      <c r="BR106" t="inlineStr">
+        <is>
+          <t>W6Zv9LTG</t>
+        </is>
+      </c>
+      <c r="BS106" t="inlineStr">
+        <is>
+          <t>abou lo</t>
+        </is>
+      </c>
+      <c r="BT106" t="inlineStr">
+        <is>
+          <t>tE85H9db</t>
+        </is>
+      </c>
+      <c r="BU106" t="inlineStr">
+        <is>
+          <t>nduquidi joseph</t>
+        </is>
+      </c>
+      <c r="BV106" t="inlineStr">
+        <is>
+          <t>O8reaWmD</t>
+        </is>
+      </c>
+      <c r="BW106" t="inlineStr">
+        <is>
+          <t>sane sadibou</t>
+        </is>
+      </c>
+      <c r="BX106" t="inlineStr">
+        <is>
+          <t>OADbJzj2</t>
+        </is>
+      </c>
+      <c r="BY106" t="inlineStr">
+        <is>
+          <t>sy pape</t>
+        </is>
+      </c>
+      <c r="BZ106" t="inlineStr"/>
+      <c r="CA106" t="inlineStr"/>
+      <c r="CB106" t="inlineStr"/>
+      <c r="CC106" t="inlineStr"/>
+      <c r="CD106" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="CE106" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="CF106" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="CG106" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="CH106" t="inlineStr">
+        <is>
+          <t>OhP1S4nf</t>
+        </is>
+      </c>
+      <c r="CI106" t="inlineStr">
+        <is>
+          <t>nkada timothee</t>
+        </is>
+      </c>
+      <c r="CJ106" t="inlineStr">
+        <is>
+          <t>dfjU302n</t>
+        </is>
+      </c>
+      <c r="CK106" t="inlineStr">
+        <is>
+          <t>mazou sacko derek</t>
+        </is>
+      </c>
+      <c r="CL106" t="inlineStr">
+        <is>
+          <t>dfjU302n</t>
+        </is>
+      </c>
+      <c r="CM106" t="inlineStr">
+        <is>
+          <t>mazou sacko derek</t>
+        </is>
+      </c>
+      <c r="CN106" t="inlineStr">
+        <is>
+          <t>INSa57F7</t>
+        </is>
+      </c>
+      <c r="CO106" t="inlineStr">
+        <is>
+          <t>taibi waniss</t>
+        </is>
+      </c>
+      <c r="CP106" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="CQ106" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="CR106" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="CS106" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="CT106" t="inlineStr">
+        <is>
+          <t>QBWpvgXg</t>
+        </is>
+      </c>
+      <c r="CU106" t="inlineStr">
+        <is>
+          <t>bouchouari mohamed</t>
+        </is>
+      </c>
+      <c r="CV106" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="CW106" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="CX106" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="CY106" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="CZ106" t="inlineStr">
+        <is>
+          <t>Iqjtansb</t>
+        </is>
+      </c>
+      <c r="DA106" t="inlineStr">
+        <is>
+          <t>abdallah abdel hakim</t>
+        </is>
+      </c>
+      <c r="DB106" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="DC106" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="DD106" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="DE106" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="DF106" t="inlineStr">
+        <is>
+          <t>6i5Z1XL8</t>
+        </is>
+      </c>
+      <c r="DG106" t="inlineStr">
+        <is>
+          <t>haag giovanni</t>
+        </is>
+      </c>
+      <c r="DH106" t="inlineStr"/>
+      <c r="DI106" t="inlineStr"/>
+      <c r="DJ106" t="inlineStr"/>
+      <c r="DK106" t="inlineStr"/>
+      <c r="DL106" t="inlineStr"/>
+      <c r="DM106" t="inlineStr"/>
+      <c r="DN106" t="inlineStr">
+        <is>
+          <t>xdl3kAtK</t>
+        </is>
+      </c>
+      <c r="DO106" t="inlineStr">
+        <is>
+          <t>diallo papa amadou</t>
+        </is>
+      </c>
+      <c r="DP106" t="inlineStr">
+        <is>
+          <t>xdl3kAtK</t>
+        </is>
+      </c>
+      <c r="DQ106" t="inlineStr">
+        <is>
+          <t>diallo papa amadou</t>
+        </is>
+      </c>
+      <c r="DR106" t="inlineStr">
+        <is>
+          <t>E5Ot0kk3</t>
+        </is>
+      </c>
+      <c r="DS106" t="inlineStr">
+        <is>
+          <t>sabaly cheikh tidiane</t>
+        </is>
+      </c>
+      <c r="DT106" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="DU106" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="DV106" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="DW106" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="DX106" t="inlineStr">
+        <is>
+          <t>OKRPP19G</t>
+        </is>
+      </c>
+      <c r="DY106" t="inlineStr">
+        <is>
+          <t>jallow ablie</t>
+        </is>
+      </c>
+      <c r="DZ106" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="EA106" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="EB106" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="EC106" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="ED106" t="inlineStr">
+        <is>
+          <t>v9UFU7UB</t>
+        </is>
+      </c>
+      <c r="EE106" t="inlineStr">
+        <is>
+          <t>sane ibou</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr"/>
+      <c r="EG106" t="inlineStr"/>
+      <c r="EH106" t="inlineStr"/>
+      <c r="EI106" t="inlineStr"/>
+      <c r="EJ106" t="inlineStr"/>
+      <c r="EK106" t="inlineStr"/>
+      <c r="EL106" t="inlineStr"/>
+      <c r="EM106" t="inlineStr"/>
+      <c r="EN106" t="inlineStr"/>
+      <c r="EO106" t="inlineStr"/>
+      <c r="EP106" t="inlineStr"/>
+      <c r="EQ106" t="inlineStr"/>
+      <c r="ER106" t="inlineStr"/>
+      <c r="ES106" t="inlineStr"/>
+      <c r="ET106" t="inlineStr"/>
+      <c r="EU106" t="inlineStr"/>
+      <c r="EV106" t="inlineStr"/>
+      <c r="EW106" t="inlineStr"/>
+      <c r="EX106" t="inlineStr"/>
+      <c r="EY106" t="inlineStr"/>
+      <c r="EZ106" t="inlineStr"/>
+      <c r="FA106" t="inlineStr"/>
+      <c r="FB106" t="inlineStr"/>
+      <c r="FC106" t="inlineStr"/>
+      <c r="FD106" t="inlineStr"/>
+      <c r="FE106" t="inlineStr"/>
+      <c r="FF106" t="inlineStr"/>
+      <c r="FG106" t="inlineStr"/>
+      <c r="FH106" t="inlineStr"/>
+      <c r="FI106" t="inlineStr"/>
+      <c r="FJ106" t="inlineStr"/>
+      <c r="FK106" t="inlineStr"/>
+      <c r="FL106" t="inlineStr"/>
+      <c r="FM106" t="inlineStr"/>
+      <c r="FN106" t="inlineStr"/>
+      <c r="FO106" t="inlineStr"/>
+      <c r="FP106" t="inlineStr"/>
+      <c r="FQ106" t="inlineStr"/>
+      <c r="FR106" t="inlineStr"/>
+      <c r="FS106" t="inlineStr"/>
+      <c r="FT106" t="inlineStr"/>
+      <c r="FU106" t="inlineStr"/>
+      <c r="FV106" t="inlineStr"/>
+      <c r="FW106" t="inlineStr"/>
+      <c r="FX106" t="inlineStr"/>
+      <c r="FY106" t="inlineStr"/>
+      <c r="FZ106" t="inlineStr"/>
+      <c r="GA106" t="inlineStr"/>
+      <c r="GB106" t="inlineStr"/>
+      <c r="GC106" t="inlineStr"/>
+      <c r="GD106" t="inlineStr"/>
+      <c r="GE106" t="inlineStr"/>
+      <c r="GF106" t="inlineStr"/>
+      <c r="GG106" t="inlineStr"/>
+      <c r="GH106" t="inlineStr"/>
+      <c r="GI106" t="inlineStr"/>
+      <c r="GJ106" t="inlineStr"/>
+      <c r="GK106" t="inlineStr"/>
+      <c r="GL106" t="inlineStr"/>
+      <c r="GM106" t="inlineStr"/>
+      <c r="GN106" t="inlineStr"/>
+      <c r="GO106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>4rrRVcF7</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Qg47cicT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>boucher zacharie</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>nkt4zHnF</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>boura ismael</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>jTCO0CRG</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>monfray adrien</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>UmQAaj9U</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>diaz michel</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>dEUlUsYE</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>hamdi mathis</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Ao6LMYLE</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>kante abdoulaye</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>AZyV3xma</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>diop mouhamed</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>jqI1zNGn</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>irie cyriaque</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>xQzrR2fm</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>m changama youssouf</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>QaynB0J3</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>said rafiki</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>dzY8Gcno</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>assoumou kouadou jaures</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>8xrw5lBb</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>ndiaye massamba</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>2eNPn89c</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>konate cheick oumar</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>Ygx5oNQb</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>da silva damien</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>h0WK6DL4</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>jacquet jeremy</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>zJeiPqkr</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>armougom yoel</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>nae24Rc4</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>gastien johan</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>4fUfKBcN</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>ackra allan</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>25nL64OI</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>keita habib</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>8SNLp9tO</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>bassouamina mons</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>6BUWSZeH</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>saivet henri</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>8K0T20C6</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>akpakoun tom</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>AytHd0Cs</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>bruus andreas</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>l0bJ7sac</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>chavalerin xavier</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>6c7NpWon</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>de preville nicolas</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>fyAli38M</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>michel corentin</t>
+        </is>
+      </c>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="BE107" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="BG107" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="BH107" t="inlineStr"/>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="inlineStr">
+        <is>
+          <t>fy3e4VyR</t>
+        </is>
+      </c>
+      <c r="BM107" t="inlineStr">
+        <is>
+          <t>bouchenna mohamed amine</t>
+        </is>
+      </c>
+      <c r="BN107" t="inlineStr">
+        <is>
+          <t>I3ygvfy8</t>
+        </is>
+      </c>
+      <c r="BO107" t="inlineStr">
+        <is>
+          <t>diop ousmane</t>
+        </is>
+      </c>
+      <c r="BP107" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="BQ107" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="BR107" t="inlineStr">
+        <is>
+          <t>pQlD4dwJ</t>
+        </is>
+      </c>
+      <c r="BS107" t="inlineStr">
+        <is>
+          <t>guivarch theo</t>
+        </is>
+      </c>
+      <c r="BT107" t="inlineStr">
+        <is>
+          <t>ziL9G1en</t>
+        </is>
+      </c>
+      <c r="BU107" t="inlineStr">
+        <is>
+          <t>magnin yohan</t>
+        </is>
+      </c>
+      <c r="BV107" t="inlineStr">
+        <is>
+          <t>xrVxB738</t>
+        </is>
+      </c>
+      <c r="BW107" t="inlineStr">
+        <is>
+          <t>mwimba josue</t>
+        </is>
+      </c>
+      <c r="BX107" t="inlineStr">
+        <is>
+          <t>Igzz1rIl</t>
+        </is>
+      </c>
+      <c r="BY107" t="inlineStr">
+        <is>
+          <t>said amine</t>
+        </is>
+      </c>
+      <c r="BZ107" t="inlineStr"/>
+      <c r="CA107" t="inlineStr"/>
+      <c r="CB107" t="inlineStr"/>
+      <c r="CC107" t="inlineStr"/>
+      <c r="CD107" t="inlineStr">
+        <is>
+          <t>AytHd0Cs</t>
+        </is>
+      </c>
+      <c r="CE107" t="inlineStr">
+        <is>
+          <t>bruus andreas</t>
+        </is>
+      </c>
+      <c r="CF107" t="inlineStr">
+        <is>
+          <t>AytHd0Cs</t>
+        </is>
+      </c>
+      <c r="CG107" t="inlineStr">
+        <is>
+          <t>bruus andreas</t>
+        </is>
+      </c>
+      <c r="CH107" t="inlineStr">
+        <is>
+          <t>dEUlUsYE</t>
+        </is>
+      </c>
+      <c r="CI107" t="inlineStr">
+        <is>
+          <t>hamdi mathis</t>
+        </is>
+      </c>
+      <c r="CJ107" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="CK107" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="CL107" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="CM107" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="CN107" t="inlineStr">
+        <is>
+          <t>jqI1zNGn</t>
+        </is>
+      </c>
+      <c r="CO107" t="inlineStr">
+        <is>
+          <t>irie cyriaque</t>
+        </is>
+      </c>
+      <c r="CP107" t="inlineStr">
+        <is>
+          <t>6c7NpWon</t>
+        </is>
+      </c>
+      <c r="CQ107" t="inlineStr">
+        <is>
+          <t>de preville nicolas</t>
+        </is>
+      </c>
+      <c r="CR107" t="inlineStr">
+        <is>
+          <t>6c7NpWon</t>
+        </is>
+      </c>
+      <c r="CS107" t="inlineStr">
+        <is>
+          <t>de preville nicolas</t>
+        </is>
+      </c>
+      <c r="CT107" t="inlineStr">
+        <is>
+          <t>AZyV3xma</t>
+        </is>
+      </c>
+      <c r="CU107" t="inlineStr">
+        <is>
+          <t>diop mouhamed</t>
+        </is>
+      </c>
+      <c r="CV107" t="inlineStr">
+        <is>
+          <t>l0bJ7sac</t>
+        </is>
+      </c>
+      <c r="CW107" t="inlineStr">
+        <is>
+          <t>chavalerin xavier</t>
+        </is>
+      </c>
+      <c r="CX107" t="inlineStr">
+        <is>
+          <t>l0bJ7sac</t>
+        </is>
+      </c>
+      <c r="CY107" t="inlineStr">
+        <is>
+          <t>chavalerin xavier</t>
+        </is>
+      </c>
+      <c r="CZ107" t="inlineStr">
+        <is>
+          <t>dzY8Gcno</t>
+        </is>
+      </c>
+      <c r="DA107" t="inlineStr">
+        <is>
+          <t>assoumou kouadou jaures</t>
+        </is>
+      </c>
+      <c r="DB107" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="DC107" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="DD107" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="DE107" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="DF107" t="inlineStr">
+        <is>
+          <t>nkt4zHnF</t>
+        </is>
+      </c>
+      <c r="DG107" t="inlineStr">
+        <is>
+          <t>boura ismael</t>
+        </is>
+      </c>
+      <c r="DH107" t="inlineStr"/>
+      <c r="DI107" t="inlineStr"/>
+      <c r="DJ107" t="inlineStr"/>
+      <c r="DK107" t="inlineStr"/>
+      <c r="DL107" t="inlineStr"/>
+      <c r="DM107" t="inlineStr"/>
+      <c r="DN107" t="inlineStr">
+        <is>
+          <t>xrVxB738</t>
+        </is>
+      </c>
+      <c r="DO107" t="inlineStr">
+        <is>
+          <t>mwimba josue</t>
+        </is>
+      </c>
+      <c r="DP107" t="inlineStr">
+        <is>
+          <t>xrVxB738</t>
+        </is>
+      </c>
+      <c r="DQ107" t="inlineStr">
+        <is>
+          <t>mwimba josue</t>
+        </is>
+      </c>
+      <c r="DR107" t="inlineStr">
+        <is>
+          <t>Ygx5oNQb</t>
+        </is>
+      </c>
+      <c r="DS107" t="inlineStr">
+        <is>
+          <t>da silva damien</t>
+        </is>
+      </c>
+      <c r="DT107" t="inlineStr">
+        <is>
+          <t>ziL9G1en</t>
+        </is>
+      </c>
+      <c r="DU107" t="inlineStr">
+        <is>
+          <t>magnin yohan</t>
+        </is>
+      </c>
+      <c r="DV107" t="inlineStr">
+        <is>
+          <t>ziL9G1en</t>
+        </is>
+      </c>
+      <c r="DW107" t="inlineStr">
+        <is>
+          <t>magnin yohan</t>
+        </is>
+      </c>
+      <c r="DX107" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="DY107" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="DZ107" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="EA107" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="EB107" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr">
+        <is>
+          <t>8SNLp9tO</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr">
+        <is>
+          <t>bassouamina mons</t>
+        </is>
+      </c>
+      <c r="EF107" t="inlineStr">
+        <is>
+          <t>Igzz1rIl</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>said amine</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
+          <t>Igzz1rIl</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr">
+        <is>
+          <t>said amine</t>
+        </is>
+      </c>
+      <c r="EJ107" t="inlineStr">
+        <is>
+          <t>25nL64OI</t>
+        </is>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>keita habib</t>
+        </is>
+      </c>
+      <c r="EL107" t="inlineStr"/>
+      <c r="EM107" t="inlineStr"/>
+      <c r="EN107" t="inlineStr"/>
+      <c r="EO107" t="inlineStr"/>
+      <c r="EP107" t="inlineStr"/>
+      <c r="EQ107" t="inlineStr"/>
+      <c r="ER107" t="inlineStr"/>
+      <c r="ES107" t="inlineStr"/>
+      <c r="ET107" t="inlineStr"/>
+      <c r="EU107" t="inlineStr"/>
+      <c r="EV107" t="inlineStr"/>
+      <c r="EW107" t="inlineStr"/>
+      <c r="EX107" t="inlineStr"/>
+      <c r="EY107" t="inlineStr"/>
+      <c r="EZ107" t="inlineStr"/>
+      <c r="FA107" t="inlineStr"/>
+      <c r="FB107" t="inlineStr"/>
+      <c r="FC107" t="inlineStr"/>
+      <c r="FD107" t="inlineStr"/>
+      <c r="FE107" t="inlineStr"/>
+      <c r="FF107" t="inlineStr"/>
+      <c r="FG107" t="inlineStr"/>
+      <c r="FH107" t="inlineStr"/>
+      <c r="FI107" t="inlineStr"/>
+      <c r="FJ107" t="inlineStr"/>
+      <c r="FK107" t="inlineStr"/>
+      <c r="FL107" t="inlineStr"/>
+      <c r="FM107" t="inlineStr"/>
+      <c r="FN107" t="inlineStr"/>
+      <c r="FO107" t="inlineStr"/>
+      <c r="FP107" t="inlineStr"/>
+      <c r="FQ107" t="inlineStr"/>
+      <c r="FR107" t="inlineStr"/>
+      <c r="FS107" t="inlineStr"/>
+      <c r="FT107" t="inlineStr"/>
+      <c r="FU107" t="inlineStr"/>
+      <c r="FV107" t="inlineStr"/>
+      <c r="FW107" t="inlineStr"/>
+      <c r="FX107" t="inlineStr"/>
+      <c r="FY107" t="inlineStr"/>
+      <c r="FZ107" t="inlineStr"/>
+      <c r="GA107" t="inlineStr"/>
+      <c r="GB107" t="inlineStr"/>
+      <c r="GC107" t="inlineStr"/>
+      <c r="GD107" t="inlineStr"/>
+      <c r="GE107" t="inlineStr"/>
+      <c r="GF107" t="inlineStr"/>
+      <c r="GG107" t="inlineStr"/>
+      <c r="GH107" t="inlineStr"/>
+      <c r="GI107" t="inlineStr"/>
+      <c r="GJ107" t="inlineStr"/>
+      <c r="GK107" t="inlineStr"/>
+      <c r="GL107" t="inlineStr"/>
+      <c r="GM107" t="inlineStr"/>
+      <c r="GN107" t="inlineStr"/>
+      <c r="GO107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GO112"/>
+  <dimension ref="A1:GO114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85055,6 +85055,1444 @@
       <c r="GN112" t="inlineStr"/>
       <c r="GO112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>rcbM0Dd8</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>rulli geronimo</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>rNLU0jIl</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>murillo michael</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>OYrb8EBS</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>balerdi leonardo</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>8YhWSbAS</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>brassier lilian</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>tvuaMWgc</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>nZs03zT2</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>kondogbia geoffrey</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ITwS8wMo</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>hojbjerg pierre emile</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>hxe108Jl</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>greenwood mason</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>lxSgSRDd</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>harit amine</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>dU3VTnID</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>luis henrique</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>8jdHWf50</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>wahi sepe elye</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>xCg7OFVE</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>diouf yehvann</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>W2ZQhrQI</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>sangui nhoa</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>zBgW9dak</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>okumu joseph</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>fRbu2Opo</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>agbadou emmanuel</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>4nBZRS2T</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>akieme sergio</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>2LonY10K</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>munetsi nyasha</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>MskdO4tG</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>atangana edoa valentin</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>Yg2zH6de</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>fofana yaya kader</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>j9vuLu2S</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>junya ito</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>jeOb1FYh</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>diakite oumar</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>ttEUhyfq</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>nakamura keito</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr">
+        <is>
+          <t>6whb8Ahe</t>
+        </is>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>seghir salim</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Wvb8v5p5</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>cornelius derek</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>GGTSMhui</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>de lange jeffrey</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>dYFeVggU</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>lirola pol</t>
+        </is>
+      </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>xbLpmH22</t>
+        </is>
+      </c>
+      <c r="BE113" t="inlineStr">
+        <is>
+          <t>meite abdoul</t>
+        </is>
+      </c>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>pQEvn0aK</t>
+        </is>
+      </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>rongier valentin</t>
+        </is>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="BI113" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="BJ113" t="inlineStr">
+        <is>
+          <t>YZTn9sgp</t>
+        </is>
+      </c>
+      <c r="BK113" t="inlineStr">
+        <is>
+          <t>sternal enzo</t>
+        </is>
+      </c>
+      <c r="BL113" t="inlineStr">
+        <is>
+          <t>42xsAKpa</t>
+        </is>
+      </c>
+      <c r="BM113" t="inlineStr">
+        <is>
+          <t>adeline martin</t>
+        </is>
+      </c>
+      <c r="BN113" t="inlineStr">
+        <is>
+          <t>vBVl3fPN</t>
+        </is>
+      </c>
+      <c r="BO113" t="inlineStr">
+        <is>
+          <t>bojang adama</t>
+        </is>
+      </c>
+      <c r="BP113" t="inlineStr">
+        <is>
+          <t>WfOJXqJA</t>
+        </is>
+      </c>
+      <c r="BQ113" t="inlineStr">
+        <is>
+          <t>de smet thibault</t>
+        </is>
+      </c>
+      <c r="BR113" t="inlineStr">
+        <is>
+          <t>hhMsOIeH</t>
+        </is>
+      </c>
+      <c r="BS113" t="inlineStr">
+        <is>
+          <t>diakhon mamadou</t>
+        </is>
+      </c>
+      <c r="BT113" t="inlineStr">
+        <is>
+          <t>YywLL7YO</t>
+        </is>
+      </c>
+      <c r="BU113" t="inlineStr">
+        <is>
+          <t>gabriel moscardo</t>
+        </is>
+      </c>
+      <c r="BV113" t="inlineStr">
+        <is>
+          <t>tSf0YZjE</t>
+        </is>
+      </c>
+      <c r="BW113" t="inlineStr">
+        <is>
+          <t>khadra reda</t>
+        </is>
+      </c>
+      <c r="BX113" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="BY113" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="BZ113" t="inlineStr">
+        <is>
+          <t>EyJTU6I9</t>
+        </is>
+      </c>
+      <c r="CA113" t="inlineStr">
+        <is>
+          <t>olliero alexandre</t>
+        </is>
+      </c>
+      <c r="CB113" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="CC113" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="CD113" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="CE113" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="CF113" t="inlineStr">
+        <is>
+          <t>8jdHWf50</t>
+        </is>
+      </c>
+      <c r="CG113" t="inlineStr">
+        <is>
+          <t>wahi sepe elye</t>
+        </is>
+      </c>
+      <c r="CH113" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="CI113" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="CJ113" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="CK113" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="CL113" t="inlineStr">
+        <is>
+          <t>lxSgSRDd</t>
+        </is>
+      </c>
+      <c r="CM113" t="inlineStr">
+        <is>
+          <t>harit amine</t>
+        </is>
+      </c>
+      <c r="CN113" t="inlineStr"/>
+      <c r="CO113" t="inlineStr"/>
+      <c r="CP113" t="inlineStr"/>
+      <c r="CQ113" t="inlineStr"/>
+      <c r="CR113" t="inlineStr"/>
+      <c r="CS113" t="inlineStr"/>
+      <c r="CT113" t="inlineStr"/>
+      <c r="CU113" t="inlineStr"/>
+      <c r="CV113" t="inlineStr"/>
+      <c r="CW113" t="inlineStr"/>
+      <c r="CX113" t="inlineStr"/>
+      <c r="CY113" t="inlineStr"/>
+      <c r="CZ113" t="inlineStr">
+        <is>
+          <t>42xsAKpa</t>
+        </is>
+      </c>
+      <c r="DA113" t="inlineStr">
+        <is>
+          <t>adeline martin</t>
+        </is>
+      </c>
+      <c r="DB113" t="inlineStr">
+        <is>
+          <t>42xsAKpa</t>
+        </is>
+      </c>
+      <c r="DC113" t="inlineStr">
+        <is>
+          <t>adeline martin</t>
+        </is>
+      </c>
+      <c r="DD113" t="inlineStr">
+        <is>
+          <t>Yg2zH6de</t>
+        </is>
+      </c>
+      <c r="DE113" t="inlineStr">
+        <is>
+          <t>fofana yaya kader</t>
+        </is>
+      </c>
+      <c r="DF113" t="inlineStr">
+        <is>
+          <t>8fTnn97m</t>
+        </is>
+      </c>
+      <c r="DG113" t="inlineStr">
+        <is>
+          <t>salama amine</t>
+        </is>
+      </c>
+      <c r="DH113" t="inlineStr">
+        <is>
+          <t>8fTnn97m</t>
+        </is>
+      </c>
+      <c r="DI113" t="inlineStr">
+        <is>
+          <t>salama amine</t>
+        </is>
+      </c>
+      <c r="DJ113" t="inlineStr">
+        <is>
+          <t>jeOb1FYh</t>
+        </is>
+      </c>
+      <c r="DK113" t="inlineStr">
+        <is>
+          <t>diakite oumar</t>
+        </is>
+      </c>
+      <c r="DL113" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="DM113" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="DN113" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="DO113" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="DP113" t="inlineStr">
+        <is>
+          <t>ttEUhyfq</t>
+        </is>
+      </c>
+      <c r="DQ113" t="inlineStr">
+        <is>
+          <t>nakamura keito</t>
+        </is>
+      </c>
+      <c r="DR113" t="inlineStr">
+        <is>
+          <t>hhMsOIeH</t>
+        </is>
+      </c>
+      <c r="DS113" t="inlineStr">
+        <is>
+          <t>diakhon mamadou</t>
+        </is>
+      </c>
+      <c r="DT113" t="inlineStr">
+        <is>
+          <t>hhMsOIeH</t>
+        </is>
+      </c>
+      <c r="DU113" t="inlineStr">
+        <is>
+          <t>diakhon mamadou</t>
+        </is>
+      </c>
+      <c r="DV113" t="inlineStr">
+        <is>
+          <t>j9vuLu2S</t>
+        </is>
+      </c>
+      <c r="DW113" t="inlineStr">
+        <is>
+          <t>junya ito</t>
+        </is>
+      </c>
+      <c r="DX113" t="inlineStr">
+        <is>
+          <t>MkgjOoBG</t>
+        </is>
+      </c>
+      <c r="DY113" t="inlineStr">
+        <is>
+          <t>kone ismael</t>
+        </is>
+      </c>
+      <c r="DZ113" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="EA113" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="EB113" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="EC113" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="ED113" t="inlineStr"/>
+      <c r="EE113" t="inlineStr"/>
+      <c r="EF113" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="EG113" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="EH113" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="EI113" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="EJ113" t="inlineStr"/>
+      <c r="EK113" t="inlineStr"/>
+      <c r="EL113" t="inlineStr"/>
+      <c r="EM113" t="inlineStr"/>
+      <c r="EN113" t="inlineStr"/>
+      <c r="EO113" t="inlineStr"/>
+      <c r="EP113" t="inlineStr">
+        <is>
+          <t>8fTnn97m</t>
+        </is>
+      </c>
+      <c r="EQ113" t="inlineStr">
+        <is>
+          <t>salama amine</t>
+        </is>
+      </c>
+      <c r="ER113" t="inlineStr"/>
+      <c r="ES113" t="inlineStr"/>
+      <c r="ET113" t="inlineStr"/>
+      <c r="EU113" t="inlineStr"/>
+      <c r="EV113" t="inlineStr"/>
+      <c r="EW113" t="inlineStr"/>
+      <c r="EX113" t="inlineStr"/>
+      <c r="EY113" t="inlineStr"/>
+      <c r="EZ113" t="inlineStr"/>
+      <c r="FA113" t="inlineStr"/>
+      <c r="FB113" t="inlineStr"/>
+      <c r="FC113" t="inlineStr"/>
+      <c r="FD113" t="inlineStr"/>
+      <c r="FE113" t="inlineStr"/>
+      <c r="FF113" t="inlineStr"/>
+      <c r="FG113" t="inlineStr"/>
+      <c r="FH113" t="inlineStr"/>
+      <c r="FI113" t="inlineStr"/>
+      <c r="FJ113" t="inlineStr"/>
+      <c r="FK113" t="inlineStr"/>
+      <c r="FL113" t="inlineStr"/>
+      <c r="FM113" t="inlineStr"/>
+      <c r="FN113" t="inlineStr"/>
+      <c r="FO113" t="inlineStr"/>
+      <c r="FP113" t="inlineStr"/>
+      <c r="FQ113" t="inlineStr"/>
+      <c r="FR113" t="inlineStr"/>
+      <c r="FS113" t="inlineStr"/>
+      <c r="FT113" t="inlineStr"/>
+      <c r="FU113" t="inlineStr"/>
+      <c r="FV113" t="inlineStr"/>
+      <c r="FW113" t="inlineStr"/>
+      <c r="FX113" t="inlineStr"/>
+      <c r="FY113" t="inlineStr"/>
+      <c r="FZ113" t="inlineStr"/>
+      <c r="GA113" t="inlineStr"/>
+      <c r="GB113" t="inlineStr"/>
+      <c r="GC113" t="inlineStr"/>
+      <c r="GD113" t="inlineStr"/>
+      <c r="GE113" t="inlineStr"/>
+      <c r="GF113" t="inlineStr"/>
+      <c r="GG113" t="inlineStr"/>
+      <c r="GH113" t="inlineStr"/>
+      <c r="GI113" t="inlineStr"/>
+      <c r="GJ113" t="inlineStr"/>
+      <c r="GK113" t="inlineStr"/>
+      <c r="GL113" t="inlineStr"/>
+      <c r="GM113" t="inlineStr"/>
+      <c r="GN113" t="inlineStr"/>
+      <c r="GO113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>0pvInj5s</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>dl7hEyx3</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>beunardeau quentin</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>bD4oBeZu</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>danger bradlay</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>WEf5zAtn</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>mendy bissenty</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CjerQdJC</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>kouagba loic</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>zkh2UjHb</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>eickmayer joachim</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>xbSVpTij</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>renel samuel</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Cf8ju4GK</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>hachem ryad</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>lUS5czaO</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>ifnaoui merwan</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>tYd2ZZ4l</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>durand damien</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>4nR8LCCp</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>sollacaro francois</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>j1uZ9TzE</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>ayessa jesah</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>xtTKOiHO</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>jacob valentin</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>EeeUoqnD</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>bonet pepe</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Eqg3ERA3</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>botella ivann</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="BE114" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr"/>
+      <c r="BI114" t="inlineStr"/>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="BM114" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="BN114" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="BO114" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="BP114" t="inlineStr">
+        <is>
+          <t>trRNdJLg</t>
+        </is>
+      </c>
+      <c r="BQ114" t="inlineStr">
+        <is>
+          <t>quemper stephen</t>
+        </is>
+      </c>
+      <c r="BR114" t="inlineStr">
+        <is>
+          <t>25CTGXNp</t>
+        </is>
+      </c>
+      <c r="BS114" t="inlineStr">
+        <is>
+          <t>quilichini ghjuvanni</t>
+        </is>
+      </c>
+      <c r="BT114" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="BU114" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="BV114" t="inlineStr">
+        <is>
+          <t>ptT4ile8</t>
+        </is>
+      </c>
+      <c r="BW114" t="inlineStr">
+        <is>
+          <t>toure al hassan</t>
+        </is>
+      </c>
+      <c r="BX114" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="BY114" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="BZ114" t="inlineStr"/>
+      <c r="CA114" t="inlineStr"/>
+      <c r="CB114" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="CC114" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="CD114" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="CE114" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="CF114" t="inlineStr">
+        <is>
+          <t>zkh2UjHb</t>
+        </is>
+      </c>
+      <c r="CG114" t="inlineStr">
+        <is>
+          <t>eickmayer joachim</t>
+        </is>
+      </c>
+      <c r="CH114" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="CI114" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="CJ114" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="CK114" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="CL114" t="inlineStr">
+        <is>
+          <t>tYd2ZZ4l</t>
+        </is>
+      </c>
+      <c r="CM114" t="inlineStr">
+        <is>
+          <t>durand damien</t>
+        </is>
+      </c>
+      <c r="CN114" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="CO114" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="CP114" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="CQ114" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="CR114" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="CS114" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="CT114" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="CU114" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="CV114" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="CW114" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="CX114" t="inlineStr">
+        <is>
+          <t>xbSVpTij</t>
+        </is>
+      </c>
+      <c r="CY114" t="inlineStr">
+        <is>
+          <t>renel samuel</t>
+        </is>
+      </c>
+      <c r="CZ114" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="DA114" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="DB114" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="DC114" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="DD114" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="DE114" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="DF114" t="inlineStr">
+        <is>
+          <t>ptT4ile8</t>
+        </is>
+      </c>
+      <c r="DG114" t="inlineStr">
+        <is>
+          <t>toure al hassan</t>
+        </is>
+      </c>
+      <c r="DH114" t="inlineStr">
+        <is>
+          <t>ptT4ile8</t>
+        </is>
+      </c>
+      <c r="DI114" t="inlineStr">
+        <is>
+          <t>toure al hassan</t>
+        </is>
+      </c>
+      <c r="DJ114" t="inlineStr">
+        <is>
+          <t>xtTKOiHO</t>
+        </is>
+      </c>
+      <c r="DK114" t="inlineStr">
+        <is>
+          <t>jacob valentin</t>
+        </is>
+      </c>
+      <c r="DL114" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="DM114" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="DN114" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="DO114" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="DP114" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="DQ114" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="DR114" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="DS114" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="DT114" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="DU114" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="DV114" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="DW114" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="DX114" t="inlineStr"/>
+      <c r="DY114" t="inlineStr"/>
+      <c r="DZ114" t="inlineStr"/>
+      <c r="EA114" t="inlineStr"/>
+      <c r="EB114" t="inlineStr"/>
+      <c r="EC114" t="inlineStr"/>
+      <c r="ED114" t="inlineStr"/>
+      <c r="EE114" t="inlineStr"/>
+      <c r="EF114" t="inlineStr"/>
+      <c r="EG114" t="inlineStr"/>
+      <c r="EH114" t="inlineStr"/>
+      <c r="EI114" t="inlineStr"/>
+      <c r="EJ114" t="inlineStr"/>
+      <c r="EK114" t="inlineStr"/>
+      <c r="EL114" t="inlineStr"/>
+      <c r="EM114" t="inlineStr"/>
+      <c r="EN114" t="inlineStr"/>
+      <c r="EO114" t="inlineStr"/>
+      <c r="EP114" t="inlineStr"/>
+      <c r="EQ114" t="inlineStr"/>
+      <c r="ER114" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="ES114" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="ET114" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="EU114" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="EV114" t="inlineStr">
+        <is>
+          <t>WEf5zAtn</t>
+        </is>
+      </c>
+      <c r="EW114" t="inlineStr">
+        <is>
+          <t>mendy bissenty</t>
+        </is>
+      </c>
+      <c r="EX114" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="EY114" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="EZ114" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="FA114" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="FB114" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="FC114" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="FD114" t="inlineStr"/>
+      <c r="FE114" t="inlineStr"/>
+      <c r="FF114" t="inlineStr"/>
+      <c r="FG114" t="inlineStr"/>
+      <c r="FH114" t="inlineStr"/>
+      <c r="FI114" t="inlineStr"/>
+      <c r="FJ114" t="inlineStr"/>
+      <c r="FK114" t="inlineStr"/>
+      <c r="FL114" t="inlineStr"/>
+      <c r="FM114" t="inlineStr"/>
+      <c r="FN114" t="inlineStr"/>
+      <c r="FO114" t="inlineStr"/>
+      <c r="FP114" t="inlineStr"/>
+      <c r="FQ114" t="inlineStr"/>
+      <c r="FR114" t="inlineStr"/>
+      <c r="FS114" t="inlineStr"/>
+      <c r="FT114" t="inlineStr"/>
+      <c r="FU114" t="inlineStr"/>
+      <c r="FV114" t="inlineStr"/>
+      <c r="FW114" t="inlineStr"/>
+      <c r="FX114" t="inlineStr"/>
+      <c r="FY114" t="inlineStr"/>
+      <c r="FZ114" t="inlineStr"/>
+      <c r="GA114" t="inlineStr"/>
+      <c r="GB114" t="inlineStr"/>
+      <c r="GC114" t="inlineStr"/>
+      <c r="GD114" t="inlineStr"/>
+      <c r="GE114" t="inlineStr"/>
+      <c r="GF114" t="inlineStr"/>
+      <c r="GG114" t="inlineStr"/>
+      <c r="GH114" t="inlineStr"/>
+      <c r="GI114" t="inlineStr"/>
+      <c r="GJ114" t="inlineStr"/>
+      <c r="GK114" t="inlineStr"/>
+      <c r="GL114" t="inlineStr"/>
+      <c r="GM114" t="inlineStr"/>
+      <c r="GN114" t="inlineStr"/>
+      <c r="GO114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GO114"/>
+  <dimension ref="A1:GO122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86493,6 +86493,5670 @@
       <c r="GN114" t="inlineStr"/>
       <c r="GO114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2qYBqH5q</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>lucas perri</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>6PvHspma</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>clinton mata</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>K44QNA2A</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>caleta car duje</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>tdnibGHH</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>niakhate moussa</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>0U8JJaVd</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>caqueret maxence</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>hQOIoFOs</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>tolisso corentin</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>CnBQp2sj</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>maitland niles ainsley</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>CCz5z9Ug</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>abner</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>QgN9t9CH</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>mikautadze georges</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>YegtWFr9</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>lacazette alexandre</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>4zY3gbw3</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>johnsson karl johan</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>vg3drc4E</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>doue guela</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>GIuyQQam</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>sow saidou</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>lOBSekrn</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>sylla abakar</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>x4JfNzq1</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>bakwa dilane</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>vDrVnIrd</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>andrey santos</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>nHtBqog0</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>doukoure ismael</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>dIkk2y21</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>nanasi sebastian</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>bPoOcxvJ</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>lemarechal felix</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>nFakLd1E</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>diarra habib</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>by8Xcffd</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>emegha emanuel</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr">
+        <is>
+          <t>Qc9B0Q23</t>
+        </is>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>adryelson</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>Qyrn555R</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>benrahma said</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>0IG1JXBr</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>descamps remy</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>WG2O5tgf</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>diawara mahamadou</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>6N65iDOI</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>fofana malick</t>
+        </is>
+      </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>vaX5DmSc</t>
+        </is>
+      </c>
+      <c r="BE115" t="inlineStr">
+        <is>
+          <t>kumbedi sael</t>
+        </is>
+      </c>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>I3i2lcHS</t>
+        </is>
+      </c>
+      <c r="BG115" t="inlineStr">
+        <is>
+          <t>molebe enzo</t>
+        </is>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>K8mhV4Es</t>
+        </is>
+      </c>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>gift emmanuel</t>
+        </is>
+      </c>
+      <c r="BJ115" t="inlineStr">
+        <is>
+          <t>WjEvCrvs</t>
+        </is>
+      </c>
+      <c r="BK115" t="inlineStr">
+        <is>
+          <t>tessmann tanner</t>
+        </is>
+      </c>
+      <c r="BL115" t="inlineStr">
+        <is>
+          <t>AV5YKO71</t>
+        </is>
+      </c>
+      <c r="BM115" t="inlineStr">
+        <is>
+          <t>diongu daouda</t>
+        </is>
+      </c>
+      <c r="BN115" t="inlineStr">
+        <is>
+          <t>M1dogGtP</t>
+        </is>
+      </c>
+      <c r="BO115" t="inlineStr">
+        <is>
+          <t>fila karol</t>
+        </is>
+      </c>
+      <c r="BP115" t="inlineStr">
+        <is>
+          <t>WUXGmxoa</t>
+        </is>
+      </c>
+      <c r="BQ115" t="inlineStr">
+        <is>
+          <t>mara sekou</t>
+        </is>
+      </c>
+      <c r="BR115" t="inlineStr">
+        <is>
+          <t>0QNoKs1B</t>
+        </is>
+      </c>
+      <c r="BS115" t="inlineStr">
+        <is>
+          <t>moreira diego</t>
+        </is>
+      </c>
+      <c r="BT115" t="inlineStr">
+        <is>
+          <t>dta4FB8P</t>
+        </is>
+      </c>
+      <c r="BU115" t="inlineStr">
+        <is>
+          <t>mwanga junior</t>
+        </is>
+      </c>
+      <c r="BV115" t="inlineStr">
+        <is>
+          <t>zHRwZwXF</t>
+        </is>
+      </c>
+      <c r="BW115" t="inlineStr">
+        <is>
+          <t>risser robin</t>
+        </is>
+      </c>
+      <c r="BX115" t="inlineStr">
+        <is>
+          <t>Op4InIJ1</t>
+        </is>
+      </c>
+      <c r="BY115" t="inlineStr">
+        <is>
+          <t>sebas jeremy</t>
+        </is>
+      </c>
+      <c r="BZ115" t="inlineStr">
+        <is>
+          <t>YFqLAlLI</t>
+        </is>
+      </c>
+      <c r="CA115" t="inlineStr">
+        <is>
+          <t>senaya marvin</t>
+        </is>
+      </c>
+      <c r="CB115" t="inlineStr">
+        <is>
+          <t>6N65iDOI</t>
+        </is>
+      </c>
+      <c r="CC115" t="inlineStr">
+        <is>
+          <t>fofana malick</t>
+        </is>
+      </c>
+      <c r="CD115" t="inlineStr">
+        <is>
+          <t>6N65iDOI</t>
+        </is>
+      </c>
+      <c r="CE115" t="inlineStr">
+        <is>
+          <t>fofana malick</t>
+        </is>
+      </c>
+      <c r="CF115" t="inlineStr">
+        <is>
+          <t>QgN9t9CH</t>
+        </is>
+      </c>
+      <c r="CG115" t="inlineStr">
+        <is>
+          <t>mikautadze georges</t>
+        </is>
+      </c>
+      <c r="CH115" t="inlineStr">
+        <is>
+          <t>K8mhV4Es</t>
+        </is>
+      </c>
+      <c r="CI115" t="inlineStr">
+        <is>
+          <t>gift emmanuel</t>
+        </is>
+      </c>
+      <c r="CJ115" t="inlineStr">
+        <is>
+          <t>K8mhV4Es</t>
+        </is>
+      </c>
+      <c r="CK115" t="inlineStr">
+        <is>
+          <t>gift emmanuel</t>
+        </is>
+      </c>
+      <c r="CL115" t="inlineStr">
+        <is>
+          <t>CCz5z9Ug</t>
+        </is>
+      </c>
+      <c r="CM115" t="inlineStr">
+        <is>
+          <t>abner</t>
+        </is>
+      </c>
+      <c r="CN115" t="inlineStr">
+        <is>
+          <t>WjEvCrvs</t>
+        </is>
+      </c>
+      <c r="CO115" t="inlineStr">
+        <is>
+          <t>tessmann tanner</t>
+        </is>
+      </c>
+      <c r="CP115" t="inlineStr">
+        <is>
+          <t>WjEvCrvs</t>
+        </is>
+      </c>
+      <c r="CQ115" t="inlineStr">
+        <is>
+          <t>tessmann tanner</t>
+        </is>
+      </c>
+      <c r="CR115" t="inlineStr">
+        <is>
+          <t>Kty10JVG</t>
+        </is>
+      </c>
+      <c r="CS115" t="inlineStr">
+        <is>
+          <t>matic nemanja</t>
+        </is>
+      </c>
+      <c r="CT115" t="inlineStr">
+        <is>
+          <t>Qc9B0Q23</t>
+        </is>
+      </c>
+      <c r="CU115" t="inlineStr">
+        <is>
+          <t>adryelson</t>
+        </is>
+      </c>
+      <c r="CV115" t="inlineStr">
+        <is>
+          <t>Qc9B0Q23</t>
+        </is>
+      </c>
+      <c r="CW115" t="inlineStr">
+        <is>
+          <t>adryelson</t>
+        </is>
+      </c>
+      <c r="CX115" t="inlineStr">
+        <is>
+          <t>K44QNA2A</t>
+        </is>
+      </c>
+      <c r="CY115" t="inlineStr">
+        <is>
+          <t>caleta car duje</t>
+        </is>
+      </c>
+      <c r="CZ115" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="DA115" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
+        </is>
+      </c>
+      <c r="DB115" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="DC115" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
+        </is>
+      </c>
+      <c r="DD115" t="inlineStr">
+        <is>
+          <t>bPoOcxvJ</t>
+        </is>
+      </c>
+      <c r="DE115" t="inlineStr">
+        <is>
+          <t>lemarechal felix</t>
+        </is>
+      </c>
+      <c r="DF115" t="inlineStr">
+        <is>
+          <t>WUXGmxoa</t>
+        </is>
+      </c>
+      <c r="DG115" t="inlineStr">
+        <is>
+          <t>mara sekou</t>
+        </is>
+      </c>
+      <c r="DH115" t="inlineStr">
+        <is>
+          <t>WUXGmxoa</t>
+        </is>
+      </c>
+      <c r="DI115" t="inlineStr">
+        <is>
+          <t>mara sekou</t>
+        </is>
+      </c>
+      <c r="DJ115" t="inlineStr">
+        <is>
+          <t>dIkk2y21</t>
+        </is>
+      </c>
+      <c r="DK115" t="inlineStr">
+        <is>
+          <t>nanasi sebastian</t>
+        </is>
+      </c>
+      <c r="DL115" t="inlineStr">
+        <is>
+          <t>YFqLAlLI</t>
+        </is>
+      </c>
+      <c r="DM115" t="inlineStr">
+        <is>
+          <t>senaya marvin</t>
+        </is>
+      </c>
+      <c r="DN115" t="inlineStr">
+        <is>
+          <t>YFqLAlLI</t>
+        </is>
+      </c>
+      <c r="DO115" t="inlineStr">
+        <is>
+          <t>senaya marvin</t>
+        </is>
+      </c>
+      <c r="DP115" t="inlineStr">
+        <is>
+          <t>nFakLd1E</t>
+        </is>
+      </c>
+      <c r="DQ115" t="inlineStr">
+        <is>
+          <t>diarra habib</t>
+        </is>
+      </c>
+      <c r="DR115" t="inlineStr">
+        <is>
+          <t>0QNoKs1B</t>
+        </is>
+      </c>
+      <c r="DS115" t="inlineStr">
+        <is>
+          <t>moreira diego</t>
+        </is>
+      </c>
+      <c r="DT115" t="inlineStr">
+        <is>
+          <t>0QNoKs1B</t>
+        </is>
+      </c>
+      <c r="DU115" t="inlineStr">
+        <is>
+          <t>moreira diego</t>
+        </is>
+      </c>
+      <c r="DV115" t="inlineStr">
+        <is>
+          <t>GIuyQQam</t>
+        </is>
+      </c>
+      <c r="DW115" t="inlineStr">
+        <is>
+          <t>sow saidou</t>
+        </is>
+      </c>
+      <c r="DX115" t="inlineStr">
+        <is>
+          <t>rsiloRPO</t>
+        </is>
+      </c>
+      <c r="DY115" t="inlineStr">
+        <is>
+          <t>nuamah ernest</t>
+        </is>
+      </c>
+      <c r="DZ115" t="inlineStr">
+        <is>
+          <t>jgaGiVOl</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>tagliafico nicolas</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr"/>
+      <c r="EC115" t="inlineStr"/>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="EH115" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr"/>
+      <c r="EM115" t="inlineStr"/>
+      <c r="EN115" t="inlineStr"/>
+      <c r="EO115" t="inlineStr"/>
+      <c r="EP115" t="inlineStr">
+        <is>
+          <t>ARPvetaS</t>
+        </is>
+      </c>
+      <c r="EQ115" t="inlineStr">
+        <is>
+          <t>wiley caleb</t>
+        </is>
+      </c>
+      <c r="ER115" t="inlineStr"/>
+      <c r="ES115" t="inlineStr"/>
+      <c r="ET115" t="inlineStr"/>
+      <c r="EU115" t="inlineStr"/>
+      <c r="EV115" t="inlineStr"/>
+      <c r="EW115" t="inlineStr"/>
+      <c r="EX115" t="inlineStr">
+        <is>
+          <t>Op4InIJ1</t>
+        </is>
+      </c>
+      <c r="EY115" t="inlineStr">
+        <is>
+          <t>sebas jeremy</t>
+        </is>
+      </c>
+      <c r="EZ115" t="inlineStr">
+        <is>
+          <t>Op4InIJ1</t>
+        </is>
+      </c>
+      <c r="FA115" t="inlineStr">
+        <is>
+          <t>sebas jeremy</t>
+        </is>
+      </c>
+      <c r="FB115" t="inlineStr">
+        <is>
+          <t>by8Xcffd</t>
+        </is>
+      </c>
+      <c r="FC115" t="inlineStr">
+        <is>
+          <t>emegha emanuel</t>
+        </is>
+      </c>
+      <c r="FD115" t="inlineStr"/>
+      <c r="FE115" t="inlineStr"/>
+      <c r="FF115" t="inlineStr"/>
+      <c r="FG115" t="inlineStr"/>
+      <c r="FH115" t="inlineStr"/>
+      <c r="FI115" t="inlineStr"/>
+      <c r="FJ115" t="inlineStr"/>
+      <c r="FK115" t="inlineStr"/>
+      <c r="FL115" t="inlineStr"/>
+      <c r="FM115" t="inlineStr"/>
+      <c r="FN115" t="inlineStr"/>
+      <c r="FO115" t="inlineStr"/>
+      <c r="FP115" t="inlineStr"/>
+      <c r="FQ115" t="inlineStr"/>
+      <c r="FR115" t="inlineStr"/>
+      <c r="FS115" t="inlineStr"/>
+      <c r="FT115" t="inlineStr"/>
+      <c r="FU115" t="inlineStr"/>
+      <c r="FV115" t="inlineStr"/>
+      <c r="FW115" t="inlineStr"/>
+      <c r="FX115" t="inlineStr"/>
+      <c r="FY115" t="inlineStr"/>
+      <c r="FZ115" t="inlineStr"/>
+      <c r="GA115" t="inlineStr"/>
+      <c r="GB115" t="inlineStr"/>
+      <c r="GC115" t="inlineStr"/>
+      <c r="GD115" t="inlineStr"/>
+      <c r="GE115" t="inlineStr"/>
+      <c r="GF115" t="inlineStr"/>
+      <c r="GG115" t="inlineStr"/>
+      <c r="GH115" t="inlineStr"/>
+      <c r="GI115" t="inlineStr"/>
+      <c r="GJ115" t="inlineStr"/>
+      <c r="GK115" t="inlineStr"/>
+      <c r="GL115" t="inlineStr"/>
+      <c r="GM115" t="inlineStr"/>
+      <c r="GN115" t="inlineStr"/>
+      <c r="GO115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>WlzDg17E</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>25CTGXNp</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>quilichini ghjuvanni</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>j1uZ9TzE</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ayessa jesah</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>trRNdJLg</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>quemper stephen</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Qg47cicT</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>boucher zacharie</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>nkt4zHnF</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>boura ismael</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>63DHUXLG</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>mendes houboulang</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>UmQAaj9U</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>diaz michel</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>dEUlUsYE</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>hamdi mathis</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Ao6LMYLE</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>kante abdoulaye</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>l0bJ7sac</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>chavalerin xavier</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>jqI1zNGn</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>irie cyriaque</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>xQzrR2fm</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>m changama youssouf</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>QaynB0J3</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>said rafiki</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>dzY8Gcno</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>assoumou kouadou jaures</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>fTn87CcD</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>khelifa anthony</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>WCC14cm0</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>kouassi arsene</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>drNgaEBH</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>michel mathieu</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="BE116" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="BH116" t="inlineStr"/>
+      <c r="BI116" t="inlineStr"/>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="inlineStr">
+        <is>
+          <t>zuiN9zaU</t>
+        </is>
+      </c>
+      <c r="BM116" t="inlineStr">
+        <is>
+          <t>ba pape ibnou</t>
+        </is>
+      </c>
+      <c r="BN116" t="inlineStr">
+        <is>
+          <t>AZyV3xma</t>
+        </is>
+      </c>
+      <c r="BO116" t="inlineStr">
+        <is>
+          <t>diop mouhamed</t>
+        </is>
+      </c>
+      <c r="BP116" t="inlineStr">
+        <is>
+          <t>tdNIZmPm</t>
+        </is>
+      </c>
+      <c r="BQ116" t="inlineStr">
+        <is>
+          <t>fage ryan</t>
+        </is>
+      </c>
+      <c r="BR116" t="inlineStr">
+        <is>
+          <t>fyAli38M</t>
+        </is>
+      </c>
+      <c r="BS116" t="inlineStr">
+        <is>
+          <t>michel corentin</t>
+        </is>
+      </c>
+      <c r="BT116" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="BU116" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="BV116" t="inlineStr">
+        <is>
+          <t>A7Ucux61</t>
+        </is>
+      </c>
+      <c r="BW116" t="inlineStr">
+        <is>
+          <t>jean tahrat mehdi</t>
+        </is>
+      </c>
+      <c r="BX116" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="BY116" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="BZ116" t="inlineStr"/>
+      <c r="CA116" t="inlineStr"/>
+      <c r="CB116" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="CC116" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="CD116" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="CE116" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="CF116" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="CG116" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="CH116" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="CI116" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="CJ116" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="CK116" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="CL116" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="CM116" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="CN116" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="CO116" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="CP116" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="CQ116" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="CR116" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="CS116" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="CT116" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="CU116" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="CV116" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="CW116" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="CX116" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="CY116" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="CZ116" t="inlineStr">
+        <is>
+          <t>AZyV3xma</t>
+        </is>
+      </c>
+      <c r="DA116" t="inlineStr">
+        <is>
+          <t>diop mouhamed</t>
+        </is>
+      </c>
+      <c r="DB116" t="inlineStr">
+        <is>
+          <t>AZyV3xma</t>
+        </is>
+      </c>
+      <c r="DC116" t="inlineStr">
+        <is>
+          <t>diop mouhamed</t>
+        </is>
+      </c>
+      <c r="DD116" t="inlineStr">
+        <is>
+          <t>dzY8Gcno</t>
+        </is>
+      </c>
+      <c r="DE116" t="inlineStr">
+        <is>
+          <t>assoumou kouadou jaures</t>
+        </is>
+      </c>
+      <c r="DF116" t="inlineStr">
+        <is>
+          <t>A7Ucux61</t>
+        </is>
+      </c>
+      <c r="DG116" t="inlineStr">
+        <is>
+          <t>jean tahrat mehdi</t>
+        </is>
+      </c>
+      <c r="DH116" t="inlineStr">
+        <is>
+          <t>A7Ucux61</t>
+        </is>
+      </c>
+      <c r="DI116" t="inlineStr">
+        <is>
+          <t>jean tahrat mehdi</t>
+        </is>
+      </c>
+      <c r="DJ116" t="inlineStr">
+        <is>
+          <t>jqI1zNGn</t>
+        </is>
+      </c>
+      <c r="DK116" t="inlineStr">
+        <is>
+          <t>irie cyriaque</t>
+        </is>
+      </c>
+      <c r="DL116" t="inlineStr">
+        <is>
+          <t>zuiN9zaU</t>
+        </is>
+      </c>
+      <c r="DM116" t="inlineStr">
+        <is>
+          <t>ba pape ibnou</t>
+        </is>
+      </c>
+      <c r="DN116" t="inlineStr">
+        <is>
+          <t>zuiN9zaU</t>
+        </is>
+      </c>
+      <c r="DO116" t="inlineStr">
+        <is>
+          <t>ba pape ibnou</t>
+        </is>
+      </c>
+      <c r="DP116" t="inlineStr">
+        <is>
+          <t>QaynB0J3</t>
+        </is>
+      </c>
+      <c r="DQ116" t="inlineStr">
+        <is>
+          <t>said rafiki</t>
+        </is>
+      </c>
+      <c r="DR116" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="DS116" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="DT116" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="DU116" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="DV116" t="inlineStr">
+        <is>
+          <t>l0bJ7sac</t>
+        </is>
+      </c>
+      <c r="DW116" t="inlineStr">
+        <is>
+          <t>chavalerin xavier</t>
+        </is>
+      </c>
+      <c r="DX116" t="inlineStr"/>
+      <c r="DY116" t="inlineStr"/>
+      <c r="DZ116" t="inlineStr"/>
+      <c r="EA116" t="inlineStr"/>
+      <c r="EB116" t="inlineStr"/>
+      <c r="EC116" t="inlineStr"/>
+      <c r="ED116" t="inlineStr"/>
+      <c r="EE116" t="inlineStr"/>
+      <c r="EF116" t="inlineStr"/>
+      <c r="EG116" t="inlineStr"/>
+      <c r="EH116" t="inlineStr"/>
+      <c r="EI116" t="inlineStr"/>
+      <c r="EJ116" t="inlineStr"/>
+      <c r="EK116" t="inlineStr"/>
+      <c r="EL116" t="inlineStr"/>
+      <c r="EM116" t="inlineStr"/>
+      <c r="EN116" t="inlineStr"/>
+      <c r="EO116" t="inlineStr"/>
+      <c r="EP116" t="inlineStr"/>
+      <c r="EQ116" t="inlineStr"/>
+      <c r="ER116" t="inlineStr"/>
+      <c r="ES116" t="inlineStr"/>
+      <c r="ET116" t="inlineStr"/>
+      <c r="EU116" t="inlineStr"/>
+      <c r="EV116" t="inlineStr"/>
+      <c r="EW116" t="inlineStr"/>
+      <c r="EX116" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="EY116" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="EZ116" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="FA116" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="FB116" t="inlineStr">
+        <is>
+          <t>UmQAaj9U</t>
+        </is>
+      </c>
+      <c r="FC116" t="inlineStr">
+        <is>
+          <t>diaz michel</t>
+        </is>
+      </c>
+      <c r="FD116" t="inlineStr"/>
+      <c r="FE116" t="inlineStr"/>
+      <c r="FF116" t="inlineStr"/>
+      <c r="FG116" t="inlineStr"/>
+      <c r="FH116" t="inlineStr"/>
+      <c r="FI116" t="inlineStr"/>
+      <c r="FJ116" t="inlineStr"/>
+      <c r="FK116" t="inlineStr"/>
+      <c r="FL116" t="inlineStr"/>
+      <c r="FM116" t="inlineStr"/>
+      <c r="FN116" t="inlineStr"/>
+      <c r="FO116" t="inlineStr"/>
+      <c r="FP116" t="inlineStr"/>
+      <c r="FQ116" t="inlineStr"/>
+      <c r="FR116" t="inlineStr"/>
+      <c r="FS116" t="inlineStr"/>
+      <c r="FT116" t="inlineStr"/>
+      <c r="FU116" t="inlineStr"/>
+      <c r="FV116" t="inlineStr"/>
+      <c r="FW116" t="inlineStr"/>
+      <c r="FX116" t="inlineStr"/>
+      <c r="FY116" t="inlineStr"/>
+      <c r="FZ116" t="inlineStr"/>
+      <c r="GA116" t="inlineStr"/>
+      <c r="GB116" t="inlineStr"/>
+      <c r="GC116" t="inlineStr"/>
+      <c r="GD116" t="inlineStr"/>
+      <c r="GE116" t="inlineStr"/>
+      <c r="GF116" t="inlineStr"/>
+      <c r="GG116" t="inlineStr"/>
+      <c r="GH116" t="inlineStr"/>
+      <c r="GI116" t="inlineStr"/>
+      <c r="GJ116" t="inlineStr"/>
+      <c r="GK116" t="inlineStr"/>
+      <c r="GL116" t="inlineStr"/>
+      <c r="GM116" t="inlineStr"/>
+      <c r="GN116" t="inlineStr"/>
+      <c r="GO116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>IoCT4kRP</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0QluvG6s</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>mandrea anthony</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Ojlo3DFG</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>vandermersch hugo</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>YaDc8KUo</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>diedounne debohi</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>v1nbamR8</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>thomas romain</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>487CQIYM</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>meddah daylam</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>GOdGE1cn</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>m vila yann</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>6qDAkr52</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>keyremeh godson</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>nTSAxkMK</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>lebreton noe</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>OnEUHb2t</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>rajot lorenzo</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>byAFdWP0</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>gomis tidiam</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>YLpVZgK4</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>le bihan mickael</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>YkTI15a3</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>escales florian</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>Knpb69xQ</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>kouadio julien</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>xbCaEITP</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>lajugie francois</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>AX04y31t</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>drouhin axel</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>QT6THpuf</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>delphis thibault</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>SGy9pst5</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>kashi ahmed</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>611nUsKM</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>pajot vincent</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>E7gMZtT7</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>larose antoine</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>4SgLsxFe</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>tiendrebeogo wendkuuni josue</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>4YOUdDQ3</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>bermont anthony</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>E1h8Ff92</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>djoco kapitbafan</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>W6JaBPra</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>brahimi bilal</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>zRkxtbt5</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>clementia yannis</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>QoV6Ei8J</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>coulibaly kalifa</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>MN5RvsXp</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>mendy alexandre</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>fikV9v0s</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>milliner leo</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>IZetE3Oq</t>
+        </is>
+      </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>tavares heliohdino</t>
+        </is>
+      </c>
+      <c r="BH117" t="inlineStr"/>
+      <c r="BI117" t="inlineStr"/>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="inlineStr">
+        <is>
+          <t>GW9zt9yT</t>
+        </is>
+      </c>
+      <c r="BM117" t="inlineStr">
+        <is>
+          <t>callens thomas</t>
+        </is>
+      </c>
+      <c r="BN117" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="BO117" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="BP117" t="inlineStr">
+        <is>
+          <t>dGm01L6K</t>
+        </is>
+      </c>
+      <c r="BQ117" t="inlineStr">
+        <is>
+          <t>debbiche wael</t>
+        </is>
+      </c>
+      <c r="BR117" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="BS117" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="BT117" t="inlineStr">
+        <is>
+          <t>GIatFrPC</t>
+        </is>
+      </c>
+      <c r="BU117" t="inlineStr">
+        <is>
+          <t>mahop moise</t>
+        </is>
+      </c>
+      <c r="BV117" t="inlineStr">
+        <is>
+          <t>U7tAfTbA</t>
+        </is>
+      </c>
+      <c r="BW117" t="inlineStr">
+        <is>
+          <t>ntignee goteh</t>
+        </is>
+      </c>
+      <c r="BX117" t="inlineStr">
+        <is>
+          <t>rcTbvUIa</t>
+        </is>
+      </c>
+      <c r="BY117" t="inlineStr">
+        <is>
+          <t>paris quentin</t>
+        </is>
+      </c>
+      <c r="BZ117" t="inlineStr"/>
+      <c r="CA117" t="inlineStr"/>
+      <c r="CB117" t="inlineStr">
+        <is>
+          <t>W6JaBPra</t>
+        </is>
+      </c>
+      <c r="CC117" t="inlineStr">
+        <is>
+          <t>brahimi bilal</t>
+        </is>
+      </c>
+      <c r="CD117" t="inlineStr">
+        <is>
+          <t>W6JaBPra</t>
+        </is>
+      </c>
+      <c r="CE117" t="inlineStr">
+        <is>
+          <t>brahimi bilal</t>
+        </is>
+      </c>
+      <c r="CF117" t="inlineStr">
+        <is>
+          <t>byAFdWP0</t>
+        </is>
+      </c>
+      <c r="CG117" t="inlineStr">
+        <is>
+          <t>gomis tidiam</t>
+        </is>
+      </c>
+      <c r="CH117" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="CI117" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="CJ117" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="CK117" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="CL117" t="inlineStr">
+        <is>
+          <t>nTSAxkMK</t>
+        </is>
+      </c>
+      <c r="CM117" t="inlineStr">
+        <is>
+          <t>lebreton noe</t>
+        </is>
+      </c>
+      <c r="CN117" t="inlineStr">
+        <is>
+          <t>MN5RvsXp</t>
+        </is>
+      </c>
+      <c r="CO117" t="inlineStr">
+        <is>
+          <t>mendy alexandre</t>
+        </is>
+      </c>
+      <c r="CP117" t="inlineStr">
+        <is>
+          <t>MN5RvsXp</t>
+        </is>
+      </c>
+      <c r="CQ117" t="inlineStr">
+        <is>
+          <t>mendy alexandre</t>
+        </is>
+      </c>
+      <c r="CR117" t="inlineStr">
+        <is>
+          <t>YLpVZgK4</t>
+        </is>
+      </c>
+      <c r="CS117" t="inlineStr">
+        <is>
+          <t>le bihan mickael</t>
+        </is>
+      </c>
+      <c r="CT117" t="inlineStr">
+        <is>
+          <t>IZetE3Oq</t>
+        </is>
+      </c>
+      <c r="CU117" t="inlineStr">
+        <is>
+          <t>tavares heliohdino</t>
+        </is>
+      </c>
+      <c r="CV117" t="inlineStr">
+        <is>
+          <t>IZetE3Oq</t>
+        </is>
+      </c>
+      <c r="CW117" t="inlineStr">
+        <is>
+          <t>tavares heliohdino</t>
+        </is>
+      </c>
+      <c r="CX117" t="inlineStr">
+        <is>
+          <t>487CQIYM</t>
+        </is>
+      </c>
+      <c r="CY117" t="inlineStr">
+        <is>
+          <t>meddah daylam</t>
+        </is>
+      </c>
+      <c r="CZ117" t="inlineStr">
+        <is>
+          <t>GIatFrPC</t>
+        </is>
+      </c>
+      <c r="DA117" t="inlineStr">
+        <is>
+          <t>mahop moise</t>
+        </is>
+      </c>
+      <c r="DB117" t="inlineStr">
+        <is>
+          <t>GIatFrPC</t>
+        </is>
+      </c>
+      <c r="DC117" t="inlineStr">
+        <is>
+          <t>mahop moise</t>
+        </is>
+      </c>
+      <c r="DD117" t="inlineStr">
+        <is>
+          <t>4YOUdDQ3</t>
+        </is>
+      </c>
+      <c r="DE117" t="inlineStr">
+        <is>
+          <t>bermont anthony</t>
+        </is>
+      </c>
+      <c r="DF117" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="DG117" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="DH117" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="DI117" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="DJ117" t="inlineStr">
+        <is>
+          <t>4SgLsxFe</t>
+        </is>
+      </c>
+      <c r="DK117" t="inlineStr">
+        <is>
+          <t>tiendrebeogo wendkuuni josue</t>
+        </is>
+      </c>
+      <c r="DL117" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="DM117" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="DN117" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="DO117" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="DP117" t="inlineStr">
+        <is>
+          <t>E1h8Ff92</t>
+        </is>
+      </c>
+      <c r="DQ117" t="inlineStr">
+        <is>
+          <t>djoco kapitbafan</t>
+        </is>
+      </c>
+      <c r="DR117" t="inlineStr">
+        <is>
+          <t>U7tAfTbA</t>
+        </is>
+      </c>
+      <c r="DS117" t="inlineStr">
+        <is>
+          <t>ntignee goteh</t>
+        </is>
+      </c>
+      <c r="DT117" t="inlineStr">
+        <is>
+          <t>U7tAfTbA</t>
+        </is>
+      </c>
+      <c r="DU117" t="inlineStr">
+        <is>
+          <t>ntignee goteh</t>
+        </is>
+      </c>
+      <c r="DV117" t="inlineStr">
+        <is>
+          <t>Knpb69xQ</t>
+        </is>
+      </c>
+      <c r="DW117" t="inlineStr">
+        <is>
+          <t>kouadio julien</t>
+        </is>
+      </c>
+      <c r="DX117" t="inlineStr"/>
+      <c r="DY117" t="inlineStr"/>
+      <c r="DZ117" t="inlineStr"/>
+      <c r="EA117" t="inlineStr"/>
+      <c r="EB117" t="inlineStr"/>
+      <c r="EC117" t="inlineStr"/>
+      <c r="ED117" t="inlineStr"/>
+      <c r="EE117" t="inlineStr"/>
+      <c r="EF117" t="inlineStr"/>
+      <c r="EG117" t="inlineStr"/>
+      <c r="EH117" t="inlineStr"/>
+      <c r="EI117" t="inlineStr"/>
+      <c r="EJ117" t="inlineStr"/>
+      <c r="EK117" t="inlineStr"/>
+      <c r="EL117" t="inlineStr"/>
+      <c r="EM117" t="inlineStr"/>
+      <c r="EN117" t="inlineStr"/>
+      <c r="EO117" t="inlineStr"/>
+      <c r="EP117" t="inlineStr"/>
+      <c r="EQ117" t="inlineStr"/>
+      <c r="ER117" t="inlineStr">
+        <is>
+          <t>QoV6Ei8J</t>
+        </is>
+      </c>
+      <c r="ES117" t="inlineStr">
+        <is>
+          <t>coulibaly kalifa</t>
+        </is>
+      </c>
+      <c r="ET117" t="inlineStr">
+        <is>
+          <t>QoV6Ei8J</t>
+        </is>
+      </c>
+      <c r="EU117" t="inlineStr">
+        <is>
+          <t>coulibaly kalifa</t>
+        </is>
+      </c>
+      <c r="EV117" t="inlineStr">
+        <is>
+          <t>6qDAkr52</t>
+        </is>
+      </c>
+      <c r="EW117" t="inlineStr">
+        <is>
+          <t>keyremeh godson</t>
+        </is>
+      </c>
+      <c r="EX117" t="inlineStr"/>
+      <c r="EY117" t="inlineStr"/>
+      <c r="EZ117" t="inlineStr"/>
+      <c r="FA117" t="inlineStr"/>
+      <c r="FB117" t="inlineStr"/>
+      <c r="FC117" t="inlineStr"/>
+      <c r="FD117" t="inlineStr"/>
+      <c r="FE117" t="inlineStr"/>
+      <c r="FF117" t="inlineStr"/>
+      <c r="FG117" t="inlineStr"/>
+      <c r="FH117" t="inlineStr"/>
+      <c r="FI117" t="inlineStr"/>
+      <c r="FJ117" t="inlineStr"/>
+      <c r="FK117" t="inlineStr"/>
+      <c r="FL117" t="inlineStr"/>
+      <c r="FM117" t="inlineStr"/>
+      <c r="FN117" t="inlineStr"/>
+      <c r="FO117" t="inlineStr"/>
+      <c r="FP117" t="inlineStr"/>
+      <c r="FQ117" t="inlineStr"/>
+      <c r="FR117" t="inlineStr"/>
+      <c r="FS117" t="inlineStr"/>
+      <c r="FT117" t="inlineStr"/>
+      <c r="FU117" t="inlineStr"/>
+      <c r="FV117" t="inlineStr"/>
+      <c r="FW117" t="inlineStr"/>
+      <c r="FX117" t="inlineStr"/>
+      <c r="FY117" t="inlineStr"/>
+      <c r="FZ117" t="inlineStr"/>
+      <c r="GA117" t="inlineStr"/>
+      <c r="GB117" t="inlineStr"/>
+      <c r="GC117" t="inlineStr"/>
+      <c r="GD117" t="inlineStr"/>
+      <c r="GE117" t="inlineStr"/>
+      <c r="GF117" t="inlineStr"/>
+      <c r="GG117" t="inlineStr"/>
+      <c r="GH117" t="inlineStr"/>
+      <c r="GI117" t="inlineStr"/>
+      <c r="GJ117" t="inlineStr"/>
+      <c r="GK117" t="inlineStr"/>
+      <c r="GL117" t="inlineStr"/>
+      <c r="GM117" t="inlineStr"/>
+      <c r="GN117" t="inlineStr"/>
+      <c r="GO117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>zyWS0tQi</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>8xrw5lBb</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ndiaye massamba</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ziL9G1en</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>magnin yohan</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ygx5oNQb</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>da silva damien</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>h0WK6DL4</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>jacquet jeremy</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>zev04vcl</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>kabeya ethan</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2eNPn89c</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>konate cheick oumar</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>4fUfKBcN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>ackra allan</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>nae24Rc4</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>gastien johan</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>25nL64OI</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>keita habib</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>8SNLp9tO</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>bassouamina mons</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>6BUWSZeH</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>saivet henri</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Uc1khkvm</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>nkambadio obed</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>jcMPmwUo</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>tourraine mathys</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>8UK1HbMC</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>mbow mamadou</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>6Nrp053I</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>kolodziejczak timothee</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>t2wVToOG</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>ollila tuomas</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>dvCqyKNu</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>doucet lohann</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>6Ze5jFyJ</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>marchetti vincent</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>zZWv9QAr</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>camara adama</t>
+        </is>
+      </c>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>8zzd9I9p</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>kebbal ilan</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>MDGk7mZd</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>krasso jean philippe</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>pzIqHPOJ</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>dicko nouha</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr">
+        <is>
+          <t>zJeiPqkr</t>
+        </is>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>armougom yoel</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>xpUN168t</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>diallo baila</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>I3ygvfy8</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>diop ousmane</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>pQlD4dwJ</t>
+        </is>
+      </c>
+      <c r="BE118" t="inlineStr">
+        <is>
+          <t>guivarch theo</t>
+        </is>
+      </c>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>hhhzfVW1</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>m bahia ivan</t>
+        </is>
+      </c>
+      <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="BM118" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="BN118" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="BO118" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="BP118" t="inlineStr">
+        <is>
+          <t>YF5m5ItO</t>
+        </is>
+      </c>
+      <c r="BQ118" t="inlineStr">
+        <is>
+          <t>kante mohamadou</t>
+        </is>
+      </c>
+      <c r="BR118" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="BS118" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="BT118" t="inlineStr">
+        <is>
+          <t>6Nb8GjF8</t>
+        </is>
+      </c>
+      <c r="BU118" t="inlineStr">
+        <is>
+          <t>riou remy</t>
+        </is>
+      </c>
+      <c r="BV118" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="BW118" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="BX118" t="inlineStr">
+        <is>
+          <t>niLz9KKj</t>
+        </is>
+      </c>
+      <c r="BY118" t="inlineStr">
+        <is>
+          <t>soumahoro aboubaka</t>
+        </is>
+      </c>
+      <c r="BZ118" t="inlineStr"/>
+      <c r="CA118" t="inlineStr"/>
+      <c r="CB118" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="CC118" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="CD118" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="CE118" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="CF118" t="inlineStr">
+        <is>
+          <t>zev04vcl</t>
+        </is>
+      </c>
+      <c r="CG118" t="inlineStr">
+        <is>
+          <t>kabeya ethan</t>
+        </is>
+      </c>
+      <c r="CH118" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="CI118" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="CJ118" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="CK118" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="CL118" t="inlineStr">
+        <is>
+          <t>25nL64OI</t>
+        </is>
+      </c>
+      <c r="CM118" t="inlineStr">
+        <is>
+          <t>keita habib</t>
+        </is>
+      </c>
+      <c r="CN118" t="inlineStr">
+        <is>
+          <t>xpUN168t</t>
+        </is>
+      </c>
+      <c r="CO118" t="inlineStr">
+        <is>
+          <t>diallo baila</t>
+        </is>
+      </c>
+      <c r="CP118" t="inlineStr">
+        <is>
+          <t>xpUN168t</t>
+        </is>
+      </c>
+      <c r="CQ118" t="inlineStr">
+        <is>
+          <t>diallo baila</t>
+        </is>
+      </c>
+      <c r="CR118" t="inlineStr">
+        <is>
+          <t>ziL9G1en</t>
+        </is>
+      </c>
+      <c r="CS118" t="inlineStr">
+        <is>
+          <t>magnin yohan</t>
+        </is>
+      </c>
+      <c r="CT118" t="inlineStr">
+        <is>
+          <t>I3ygvfy8</t>
+        </is>
+      </c>
+      <c r="CU118" t="inlineStr">
+        <is>
+          <t>diop ousmane</t>
+        </is>
+      </c>
+      <c r="CV118" t="inlineStr">
+        <is>
+          <t>I3ygvfy8</t>
+        </is>
+      </c>
+      <c r="CW118" t="inlineStr">
+        <is>
+          <t>diop ousmane</t>
+        </is>
+      </c>
+      <c r="CX118" t="inlineStr">
+        <is>
+          <t>8SNLp9tO</t>
+        </is>
+      </c>
+      <c r="CY118" t="inlineStr">
+        <is>
+          <t>bassouamina mons</t>
+        </is>
+      </c>
+      <c r="CZ118" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="DA118" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="DB118" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="DC118" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="DD118" t="inlineStr">
+        <is>
+          <t>MDGk7mZd</t>
+        </is>
+      </c>
+      <c r="DE118" t="inlineStr">
+        <is>
+          <t>krasso jean philippe</t>
+        </is>
+      </c>
+      <c r="DF118" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="DG118" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="DH118" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="DI118" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="DJ118" t="inlineStr">
+        <is>
+          <t>pzIqHPOJ</t>
+        </is>
+      </c>
+      <c r="DK118" t="inlineStr">
+        <is>
+          <t>dicko nouha</t>
+        </is>
+      </c>
+      <c r="DL118" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="DM118" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="DN118" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="DO118" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="DP118" t="inlineStr">
+        <is>
+          <t>dvCqyKNu</t>
+        </is>
+      </c>
+      <c r="DQ118" t="inlineStr">
+        <is>
+          <t>doucet lohann</t>
+        </is>
+      </c>
+      <c r="DR118" t="inlineStr">
+        <is>
+          <t>niLz9KKj</t>
+        </is>
+      </c>
+      <c r="DS118" t="inlineStr">
+        <is>
+          <t>soumahoro aboubaka</t>
+        </is>
+      </c>
+      <c r="DT118" t="inlineStr">
+        <is>
+          <t>niLz9KKj</t>
+        </is>
+      </c>
+      <c r="DU118" t="inlineStr">
+        <is>
+          <t>soumahoro aboubaka</t>
+        </is>
+      </c>
+      <c r="DV118" t="inlineStr">
+        <is>
+          <t>8zzd9I9p</t>
+        </is>
+      </c>
+      <c r="DW118" t="inlineStr">
+        <is>
+          <t>kebbal ilan</t>
+        </is>
+      </c>
+      <c r="DX118" t="inlineStr"/>
+      <c r="DY118" t="inlineStr"/>
+      <c r="DZ118" t="inlineStr"/>
+      <c r="EA118" t="inlineStr"/>
+      <c r="EB118" t="inlineStr"/>
+      <c r="EC118" t="inlineStr"/>
+      <c r="ED118" t="inlineStr"/>
+      <c r="EE118" t="inlineStr"/>
+      <c r="EF118" t="inlineStr"/>
+      <c r="EG118" t="inlineStr"/>
+      <c r="EH118" t="inlineStr"/>
+      <c r="EI118" t="inlineStr"/>
+      <c r="EJ118" t="inlineStr"/>
+      <c r="EK118" t="inlineStr"/>
+      <c r="EL118" t="inlineStr"/>
+      <c r="EM118" t="inlineStr"/>
+      <c r="EN118" t="inlineStr"/>
+      <c r="EO118" t="inlineStr"/>
+      <c r="EP118" t="inlineStr"/>
+      <c r="EQ118" t="inlineStr"/>
+      <c r="ER118" t="inlineStr">
+        <is>
+          <t>hhhzfVW1</t>
+        </is>
+      </c>
+      <c r="ES118" t="inlineStr">
+        <is>
+          <t>m bahia ivan</t>
+        </is>
+      </c>
+      <c r="ET118" t="inlineStr">
+        <is>
+          <t>hhhzfVW1</t>
+        </is>
+      </c>
+      <c r="EU118" t="inlineStr">
+        <is>
+          <t>m bahia ivan</t>
+        </is>
+      </c>
+      <c r="EV118" t="inlineStr">
+        <is>
+          <t>2eNPn89c</t>
+        </is>
+      </c>
+      <c r="EW118" t="inlineStr">
+        <is>
+          <t>konate cheick oumar</t>
+        </is>
+      </c>
+      <c r="EX118" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="EY118" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="EZ118" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="FA118" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="FB118" t="inlineStr">
+        <is>
+          <t>t2wVToOG</t>
+        </is>
+      </c>
+      <c r="FC118" t="inlineStr">
+        <is>
+          <t>ollila tuomas</t>
+        </is>
+      </c>
+      <c r="FD118" t="inlineStr"/>
+      <c r="FE118" t="inlineStr"/>
+      <c r="FF118" t="inlineStr"/>
+      <c r="FG118" t="inlineStr"/>
+      <c r="FH118" t="inlineStr"/>
+      <c r="FI118" t="inlineStr"/>
+      <c r="FJ118" t="inlineStr"/>
+      <c r="FK118" t="inlineStr"/>
+      <c r="FL118" t="inlineStr"/>
+      <c r="FM118" t="inlineStr"/>
+      <c r="FN118" t="inlineStr"/>
+      <c r="FO118" t="inlineStr"/>
+      <c r="FP118" t="inlineStr"/>
+      <c r="FQ118" t="inlineStr"/>
+      <c r="FR118" t="inlineStr"/>
+      <c r="FS118" t="inlineStr"/>
+      <c r="FT118" t="inlineStr"/>
+      <c r="FU118" t="inlineStr"/>
+      <c r="FV118" t="inlineStr"/>
+      <c r="FW118" t="inlineStr"/>
+      <c r="FX118" t="inlineStr"/>
+      <c r="FY118" t="inlineStr"/>
+      <c r="FZ118" t="inlineStr"/>
+      <c r="GA118" t="inlineStr"/>
+      <c r="GB118" t="inlineStr"/>
+      <c r="GC118" t="inlineStr"/>
+      <c r="GD118" t="inlineStr"/>
+      <c r="GE118" t="inlineStr"/>
+      <c r="GF118" t="inlineStr"/>
+      <c r="GG118" t="inlineStr"/>
+      <c r="GH118" t="inlineStr"/>
+      <c r="GI118" t="inlineStr"/>
+      <c r="GJ118" t="inlineStr"/>
+      <c r="GK118" t="inlineStr"/>
+      <c r="GL118" t="inlineStr"/>
+      <c r="GM118" t="inlineStr"/>
+      <c r="GN118" t="inlineStr"/>
+      <c r="GO118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>06FhaTlm</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>jyzyc1pE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jaouen ewen</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>GOqK3T14</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>youssouf benjaloud</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>CSpt7BMu</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>sangante opa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>UZzd4sDM</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>sasso vincent</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>8zK6oP8a</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>georgen alec</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>WSXgQK56</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>bardeli enzo</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>UayiGBFq</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>queiros diogo</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>6RvNumuL</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>sekongo anto</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>OrSsAkI5</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>tehan kaj</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>KQnM7QoO</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>courtet gaetan</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Kh3fmMhH</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>rivera maxence</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>pzX674k0</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>mpasi nzau lionel</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>p2nsMSal</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>ngouyamsa ahmad</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>6Vz9xZIb</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>quenabio loni</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>AmGWfem4</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>mambo muzalijoma stone</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>QBWpvgXg</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>bouchouari mohamed</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>b9VtHGuL</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>younoussa wilitty</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>dfjU302n</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>mazou sacko derek</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>INSa57F7</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>taibi waniss</t>
+        </is>
+      </c>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>Iqjtansb</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>abdallah abdel hakim</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>QqlDIsGM</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>bentayeb tawfik</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>OhP1S4nf</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>nkada timothee</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>K6JcFKeq</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>bessile loic</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>6utqVfCd</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>kone ibrahim</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>Wd8BDKWs</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>raghouber ugo</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>Ue1A5pGE</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>senneville christian</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>jusUrXEa</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
+          <t>skytta naatan</t>
+        </is>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="BM119" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="BN119" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="BO119" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="BP119" t="inlineStr">
+        <is>
+          <t>46NuxuYs</t>
+        </is>
+      </c>
+      <c r="BQ119" t="inlineStr">
+        <is>
+          <t>chougrani joris</t>
+        </is>
+      </c>
+      <c r="BR119" t="inlineStr">
+        <is>
+          <t>6kl4UZvQ</t>
+        </is>
+      </c>
+      <c r="BS119" t="inlineStr">
+        <is>
+          <t>cibois sebastien</t>
+        </is>
+      </c>
+      <c r="BT119" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="BU119" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="BV119" t="inlineStr">
+        <is>
+          <t>tASVC4IR</t>
+        </is>
+      </c>
+      <c r="BW119" t="inlineStr">
+        <is>
+          <t>pelon aurelien</t>
+        </is>
+      </c>
+      <c r="BX119" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="BY119" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="BZ119" t="inlineStr"/>
+      <c r="CA119" t="inlineStr"/>
+      <c r="CB119" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="CC119" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="CD119" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="CE119" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="CF119" t="inlineStr">
+        <is>
+          <t>OrSsAkI5</t>
+        </is>
+      </c>
+      <c r="CG119" t="inlineStr">
+        <is>
+          <t>tehan kaj</t>
+        </is>
+      </c>
+      <c r="CH119" t="inlineStr">
+        <is>
+          <t>Wd8BDKWs</t>
+        </is>
+      </c>
+      <c r="CI119" t="inlineStr">
+        <is>
+          <t>raghouber ugo</t>
+        </is>
+      </c>
+      <c r="CJ119" t="inlineStr">
+        <is>
+          <t>Wd8BDKWs</t>
+        </is>
+      </c>
+      <c r="CK119" t="inlineStr">
+        <is>
+          <t>raghouber ugo</t>
+        </is>
+      </c>
+      <c r="CL119" t="inlineStr">
+        <is>
+          <t>6RvNumuL</t>
+        </is>
+      </c>
+      <c r="CM119" t="inlineStr">
+        <is>
+          <t>sekongo anto</t>
+        </is>
+      </c>
+      <c r="CN119" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="CO119" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="CP119" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="CQ119" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="CR119" t="inlineStr">
+        <is>
+          <t>Kh3fmMhH</t>
+        </is>
+      </c>
+      <c r="CS119" t="inlineStr">
+        <is>
+          <t>rivera maxence</t>
+        </is>
+      </c>
+      <c r="CT119" t="inlineStr">
+        <is>
+          <t>Ue1A5pGE</t>
+        </is>
+      </c>
+      <c r="CU119" t="inlineStr">
+        <is>
+          <t>senneville christian</t>
+        </is>
+      </c>
+      <c r="CV119" t="inlineStr">
+        <is>
+          <t>Ue1A5pGE</t>
+        </is>
+      </c>
+      <c r="CW119" t="inlineStr">
+        <is>
+          <t>senneville christian</t>
+        </is>
+      </c>
+      <c r="CX119" t="inlineStr">
+        <is>
+          <t>8zK6oP8a</t>
+        </is>
+      </c>
+      <c r="CY119" t="inlineStr">
+        <is>
+          <t>georgen alec</t>
+        </is>
+      </c>
+      <c r="CZ119" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="DA119" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="DB119" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="DC119" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="DD119" t="inlineStr">
+        <is>
+          <t>dfjU302n</t>
+        </is>
+      </c>
+      <c r="DE119" t="inlineStr">
+        <is>
+          <t>mazou sacko derek</t>
+        </is>
+      </c>
+      <c r="DF119" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="DG119" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="DH119" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="DI119" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="DJ119" t="inlineStr">
+        <is>
+          <t>QqlDIsGM</t>
+        </is>
+      </c>
+      <c r="DK119" t="inlineStr">
+        <is>
+          <t>bentayeb tawfik</t>
+        </is>
+      </c>
+      <c r="DL119" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="DM119" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="DN119" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="DO119" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="DP119" t="inlineStr">
+        <is>
+          <t>p2nsMSal</t>
+        </is>
+      </c>
+      <c r="DQ119" t="inlineStr">
+        <is>
+          <t>ngouyamsa ahmad</t>
+        </is>
+      </c>
+      <c r="DR119" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="DS119" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="DT119" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="DU119" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="DV119" t="inlineStr">
+        <is>
+          <t>QBWpvgXg</t>
+        </is>
+      </c>
+      <c r="DW119" t="inlineStr">
+        <is>
+          <t>bouchouari mohamed</t>
+        </is>
+      </c>
+      <c r="DX119" t="inlineStr"/>
+      <c r="DY119" t="inlineStr"/>
+      <c r="DZ119" t="inlineStr"/>
+      <c r="EA119" t="inlineStr"/>
+      <c r="EB119" t="inlineStr"/>
+      <c r="EC119" t="inlineStr"/>
+      <c r="ED119" t="inlineStr"/>
+      <c r="EE119" t="inlineStr"/>
+      <c r="EF119" t="inlineStr"/>
+      <c r="EG119" t="inlineStr"/>
+      <c r="EH119" t="inlineStr"/>
+      <c r="EI119" t="inlineStr"/>
+      <c r="EJ119" t="inlineStr"/>
+      <c r="EK119" t="inlineStr"/>
+      <c r="EL119" t="inlineStr"/>
+      <c r="EM119" t="inlineStr"/>
+      <c r="EN119" t="inlineStr"/>
+      <c r="EO119" t="inlineStr"/>
+      <c r="EP119" t="inlineStr"/>
+      <c r="EQ119" t="inlineStr"/>
+      <c r="ER119" t="inlineStr">
+        <is>
+          <t>jusUrXEa</t>
+        </is>
+      </c>
+      <c r="ES119" t="inlineStr">
+        <is>
+          <t>skytta naatan</t>
+        </is>
+      </c>
+      <c r="ET119" t="inlineStr">
+        <is>
+          <t>jusUrXEa</t>
+        </is>
+      </c>
+      <c r="EU119" t="inlineStr">
+        <is>
+          <t>skytta naatan</t>
+        </is>
+      </c>
+      <c r="EV119" t="inlineStr">
+        <is>
+          <t>WSXgQK56</t>
+        </is>
+      </c>
+      <c r="EW119" t="inlineStr">
+        <is>
+          <t>bardeli enzo</t>
+        </is>
+      </c>
+      <c r="EX119" t="inlineStr"/>
+      <c r="EY119" t="inlineStr"/>
+      <c r="EZ119" t="inlineStr"/>
+      <c r="FA119" t="inlineStr"/>
+      <c r="FB119" t="inlineStr"/>
+      <c r="FC119" t="inlineStr"/>
+      <c r="FD119" t="inlineStr"/>
+      <c r="FE119" t="inlineStr"/>
+      <c r="FF119" t="inlineStr"/>
+      <c r="FG119" t="inlineStr"/>
+      <c r="FH119" t="inlineStr"/>
+      <c r="FI119" t="inlineStr"/>
+      <c r="FJ119" t="inlineStr"/>
+      <c r="FK119" t="inlineStr"/>
+      <c r="FL119" t="inlineStr"/>
+      <c r="FM119" t="inlineStr"/>
+      <c r="FN119" t="inlineStr"/>
+      <c r="FO119" t="inlineStr"/>
+      <c r="FP119" t="inlineStr"/>
+      <c r="FQ119" t="inlineStr"/>
+      <c r="FR119" t="inlineStr"/>
+      <c r="FS119" t="inlineStr"/>
+      <c r="FT119" t="inlineStr"/>
+      <c r="FU119" t="inlineStr"/>
+      <c r="FV119" t="inlineStr"/>
+      <c r="FW119" t="inlineStr"/>
+      <c r="FX119" t="inlineStr"/>
+      <c r="FY119" t="inlineStr"/>
+      <c r="FZ119" t="inlineStr"/>
+      <c r="GA119" t="inlineStr"/>
+      <c r="GB119" t="inlineStr"/>
+      <c r="GC119" t="inlineStr"/>
+      <c r="GD119" t="inlineStr"/>
+      <c r="GE119" t="inlineStr"/>
+      <c r="GF119" t="inlineStr"/>
+      <c r="GG119" t="inlineStr"/>
+      <c r="GH119" t="inlineStr"/>
+      <c r="GI119" t="inlineStr"/>
+      <c r="GJ119" t="inlineStr"/>
+      <c r="GK119" t="inlineStr"/>
+      <c r="GL119" t="inlineStr"/>
+      <c r="GM119" t="inlineStr"/>
+      <c r="GN119" t="inlineStr"/>
+      <c r="GO119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>UPVYr846</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EibuOrCE</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>diop mamadou</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>OrdAwjs0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>paquiez gaetan</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Cv3T1tX1</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>diarra mamadou</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>QeC1pQvn</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>tchaptchet allan</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>IXc7iymr</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>mendy arial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>0poPcske</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>rigo dante</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>6VcKrEuM</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>valls theo</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>2NKowyxS</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>sylvestre eddy</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>SzyvcCbe</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>benet jessy</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>ITex2UPE</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>kerouedan alan</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>nsRL20Ap</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>ba pape meissa</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>AXCqL4Qp</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>jeannin mehdi</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>UVcaeNxh</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>gaspar jordy</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>f77lo10C</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>ahoussou kouadio guy ange</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>A1JE6XmB</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>ruiz jean</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>xUaIYbZa</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>koudou therence</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>ImnpF5je</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>beusnard steeve</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>K0sjhCJO</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>mohamed iyad</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>CrYHlkps</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>mboup pathe</t>
+        </is>
+      </c>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>GjoN5Ete</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>mille antoine</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>Ollmu17h</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>njoh yonis</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>ManhCoID</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>arconte tairyk</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>tpbpYRt1</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>allain bobby</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>QBRg7SrJ</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>bangre mamady</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>4vlM6XrP</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>elphege nesta</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>0K8CfONM</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>joseph lenny</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>rqvBoQyG</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>mouyokolo loris</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>hKS4A5nd</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>zahui nesta</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr"/>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr">
+        <is>
+          <t>nHFb8AML</t>
+        </is>
+      </c>
+      <c r="BM120" t="inlineStr">
+        <is>
+          <t>diawara kandet</t>
+        </is>
+      </c>
+      <c r="BN120" t="inlineStr">
+        <is>
+          <t>ERwj7fzC</t>
+        </is>
+      </c>
+      <c r="BO120" t="inlineStr">
+        <is>
+          <t>evans jean</t>
+        </is>
+      </c>
+      <c r="BP120" t="inlineStr">
+        <is>
+          <t>bqTyyFdl</t>
+        </is>
+      </c>
+      <c r="BQ120" t="inlineStr">
+        <is>
+          <t>gasnier kyllian</t>
+        </is>
+      </c>
+      <c r="BR120" t="inlineStr">
+        <is>
+          <t>EZQeQxef</t>
+        </is>
+      </c>
+      <c r="BS120" t="inlineStr">
+        <is>
+          <t>kalulu joseph</t>
+        </is>
+      </c>
+      <c r="BT120" t="inlineStr">
+        <is>
+          <t>EJuazaLT</t>
+        </is>
+      </c>
+      <c r="BU120" t="inlineStr">
+        <is>
+          <t>kante ousmane</t>
+        </is>
+      </c>
+      <c r="BV120" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="BW120" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="BX120" t="inlineStr">
+        <is>
+          <t>0ID2g08S</t>
+        </is>
+      </c>
+      <c r="BY120" t="inlineStr">
+        <is>
+          <t>paradowski tao</t>
+        </is>
+      </c>
+      <c r="BZ120" t="inlineStr"/>
+      <c r="CA120" t="inlineStr"/>
+      <c r="CB120" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="CC120" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="CD120" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="CE120" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="CF120" t="inlineStr">
+        <is>
+          <t>2NKowyxS</t>
+        </is>
+      </c>
+      <c r="CG120" t="inlineStr">
+        <is>
+          <t>sylvestre eddy</t>
+        </is>
+      </c>
+      <c r="CH120" t="inlineStr">
+        <is>
+          <t>0K8CfONM</t>
+        </is>
+      </c>
+      <c r="CI120" t="inlineStr">
+        <is>
+          <t>joseph lenny</t>
+        </is>
+      </c>
+      <c r="CJ120" t="inlineStr">
+        <is>
+          <t>0K8CfONM</t>
+        </is>
+      </c>
+      <c r="CK120" t="inlineStr">
+        <is>
+          <t>joseph lenny</t>
+        </is>
+      </c>
+      <c r="CL120" t="inlineStr">
+        <is>
+          <t>0poPcske</t>
+        </is>
+      </c>
+      <c r="CM120" t="inlineStr">
+        <is>
+          <t>rigo dante</t>
+        </is>
+      </c>
+      <c r="CN120" t="inlineStr">
+        <is>
+          <t>QBRg7SrJ</t>
+        </is>
+      </c>
+      <c r="CO120" t="inlineStr">
+        <is>
+          <t>bangre mamady</t>
+        </is>
+      </c>
+      <c r="CP120" t="inlineStr">
+        <is>
+          <t>QBRg7SrJ</t>
+        </is>
+      </c>
+      <c r="CQ120" t="inlineStr">
+        <is>
+          <t>bangre mamady</t>
+        </is>
+      </c>
+      <c r="CR120" t="inlineStr">
+        <is>
+          <t>ITex2UPE</t>
+        </is>
+      </c>
+      <c r="CS120" t="inlineStr">
+        <is>
+          <t>kerouedan alan</t>
+        </is>
+      </c>
+      <c r="CT120" t="inlineStr">
+        <is>
+          <t>hKS4A5nd</t>
+        </is>
+      </c>
+      <c r="CU120" t="inlineStr">
+        <is>
+          <t>zahui nesta</t>
+        </is>
+      </c>
+      <c r="CV120" t="inlineStr">
+        <is>
+          <t>hKS4A5nd</t>
+        </is>
+      </c>
+      <c r="CW120" t="inlineStr">
+        <is>
+          <t>zahui nesta</t>
+        </is>
+      </c>
+      <c r="CX120" t="inlineStr">
+        <is>
+          <t>SzyvcCbe</t>
+        </is>
+      </c>
+      <c r="CY120" t="inlineStr">
+        <is>
+          <t>benet jessy</t>
+        </is>
+      </c>
+      <c r="CZ120" t="inlineStr">
+        <is>
+          <t>nHFb8AML</t>
+        </is>
+      </c>
+      <c r="DA120" t="inlineStr">
+        <is>
+          <t>diawara kandet</t>
+        </is>
+      </c>
+      <c r="DB120" t="inlineStr">
+        <is>
+          <t>nHFb8AML</t>
+        </is>
+      </c>
+      <c r="DC120" t="inlineStr">
+        <is>
+          <t>diawara kandet</t>
+        </is>
+      </c>
+      <c r="DD120" t="inlineStr">
+        <is>
+          <t>Ollmu17h</t>
+        </is>
+      </c>
+      <c r="DE120" t="inlineStr">
+        <is>
+          <t>njoh yonis</t>
+        </is>
+      </c>
+      <c r="DF120" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="DG120" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="DH120" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="DI120" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="DJ120" t="inlineStr">
+        <is>
+          <t>ImnpF5je</t>
+        </is>
+      </c>
+      <c r="DK120" t="inlineStr">
+        <is>
+          <t>beusnard steeve</t>
+        </is>
+      </c>
+      <c r="DL120" t="inlineStr">
+        <is>
+          <t>bqTyyFdl</t>
+        </is>
+      </c>
+      <c r="DM120" t="inlineStr">
+        <is>
+          <t>gasnier kyllian</t>
+        </is>
+      </c>
+      <c r="DN120" t="inlineStr">
+        <is>
+          <t>bqTyyFdl</t>
+        </is>
+      </c>
+      <c r="DO120" t="inlineStr">
+        <is>
+          <t>gasnier kyllian</t>
+        </is>
+      </c>
+      <c r="DP120" t="inlineStr">
+        <is>
+          <t>GjoN5Ete</t>
+        </is>
+      </c>
+      <c r="DQ120" t="inlineStr">
+        <is>
+          <t>mille antoine</t>
+        </is>
+      </c>
+      <c r="DR120" t="inlineStr"/>
+      <c r="DS120" t="inlineStr"/>
+      <c r="DT120" t="inlineStr"/>
+      <c r="DU120" t="inlineStr"/>
+      <c r="DV120" t="inlineStr"/>
+      <c r="DW120" t="inlineStr"/>
+      <c r="DX120" t="inlineStr"/>
+      <c r="DY120" t="inlineStr"/>
+      <c r="DZ120" t="inlineStr"/>
+      <c r="EA120" t="inlineStr"/>
+      <c r="EB120" t="inlineStr"/>
+      <c r="EC120" t="inlineStr"/>
+      <c r="ED120" t="inlineStr"/>
+      <c r="EE120" t="inlineStr"/>
+      <c r="EF120" t="inlineStr"/>
+      <c r="EG120" t="inlineStr"/>
+      <c r="EH120" t="inlineStr"/>
+      <c r="EI120" t="inlineStr"/>
+      <c r="EJ120" t="inlineStr"/>
+      <c r="EK120" t="inlineStr"/>
+      <c r="EL120" t="inlineStr"/>
+      <c r="EM120" t="inlineStr"/>
+      <c r="EN120" t="inlineStr"/>
+      <c r="EO120" t="inlineStr"/>
+      <c r="EP120" t="inlineStr"/>
+      <c r="EQ120" t="inlineStr"/>
+      <c r="ER120" t="inlineStr"/>
+      <c r="ES120" t="inlineStr"/>
+      <c r="ET120" t="inlineStr"/>
+      <c r="EU120" t="inlineStr"/>
+      <c r="EV120" t="inlineStr"/>
+      <c r="EW120" t="inlineStr"/>
+      <c r="EX120" t="inlineStr"/>
+      <c r="EY120" t="inlineStr"/>
+      <c r="EZ120" t="inlineStr"/>
+      <c r="FA120" t="inlineStr"/>
+      <c r="FB120" t="inlineStr"/>
+      <c r="FC120" t="inlineStr"/>
+      <c r="FD120" t="inlineStr"/>
+      <c r="FE120" t="inlineStr"/>
+      <c r="FF120" t="inlineStr"/>
+      <c r="FG120" t="inlineStr"/>
+      <c r="FH120" t="inlineStr"/>
+      <c r="FI120" t="inlineStr"/>
+      <c r="FJ120" t="inlineStr"/>
+      <c r="FK120" t="inlineStr"/>
+      <c r="FL120" t="inlineStr"/>
+      <c r="FM120" t="inlineStr"/>
+      <c r="FN120" t="inlineStr"/>
+      <c r="FO120" t="inlineStr"/>
+      <c r="FP120" t="inlineStr"/>
+      <c r="FQ120" t="inlineStr"/>
+      <c r="FR120" t="inlineStr"/>
+      <c r="FS120" t="inlineStr"/>
+      <c r="FT120" t="inlineStr"/>
+      <c r="FU120" t="inlineStr"/>
+      <c r="FV120" t="inlineStr"/>
+      <c r="FW120" t="inlineStr"/>
+      <c r="FX120" t="inlineStr"/>
+      <c r="FY120" t="inlineStr"/>
+      <c r="FZ120" t="inlineStr"/>
+      <c r="GA120" t="inlineStr"/>
+      <c r="GB120" t="inlineStr"/>
+      <c r="GC120" t="inlineStr"/>
+      <c r="GD120" t="inlineStr"/>
+      <c r="GE120" t="inlineStr"/>
+      <c r="GF120" t="inlineStr"/>
+      <c r="GG120" t="inlineStr"/>
+      <c r="GH120" t="inlineStr"/>
+      <c r="GI120" t="inlineStr"/>
+      <c r="GJ120" t="inlineStr"/>
+      <c r="GK120" t="inlineStr"/>
+      <c r="GL120" t="inlineStr"/>
+      <c r="GM120" t="inlineStr"/>
+      <c r="GN120" t="inlineStr"/>
+      <c r="GO120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>8WI0c7Ja</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>A9ux8Ef8</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>basilio enzo</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>4tt9cPfg</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>sissoko alpha</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>KAGBPuyQ</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>nair sohaib</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>fsOSS7y0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>riou mathis</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>McCSZuxs</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>sagna amadou</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>pC1OCXV4</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>louiserre dylan</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>29krq31i</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>sidibe kalidou</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>QPweXact</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>vallier lenny</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>27PxWKIj</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>hemia amine</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>GxfU6qGd</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>picard hugo</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>GxWPthlH</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>siwe jacques</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>dl7hEyx3</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>beunardeau quentin</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>bD4oBeZu</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>danger bradlay</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>WEf5zAtn</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>mendy bissenty</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>CjerQdJC</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>kouagba loic</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>xbSVpTij</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>renel samuel</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>Cf8ju4GK</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>hachem ryad</t>
+        </is>
+      </c>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>lUS5czaO</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>ifnaoui merwan</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>tYd2ZZ4l</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>durand damien</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr">
+        <is>
+          <t>Yw1VmcL6</t>
+        </is>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>gomis donacien</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>zH8Wrlde</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>labeau brighton</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>8IfBwmXp</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>maronnier lucas</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>EFZ6icqq</t>
+        </is>
+      </c>
+      <c r="BE121" t="inlineStr">
+        <is>
+          <t>mbaye babacar</t>
+        </is>
+      </c>
+      <c r="BF121" t="inlineStr">
+        <is>
+          <t>t8ya9KXl</t>
+        </is>
+      </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>touzghar rayan</t>
+        </is>
+      </c>
+      <c r="BH121" t="inlineStr"/>
+      <c r="BI121" t="inlineStr"/>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="BM121" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="BN121" t="inlineStr">
+        <is>
+          <t>EeeUoqnD</t>
+        </is>
+      </c>
+      <c r="BO121" t="inlineStr">
+        <is>
+          <t>bonet pepe</t>
+        </is>
+      </c>
+      <c r="BP121" t="inlineStr">
+        <is>
+          <t>Eqg3ERA3</t>
+        </is>
+      </c>
+      <c r="BQ121" t="inlineStr">
+        <is>
+          <t>botella ivann</t>
+        </is>
+      </c>
+      <c r="BR121" t="inlineStr">
+        <is>
+          <t>j3IsAvo7</t>
+        </is>
+      </c>
+      <c r="BS121" t="inlineStr">
+        <is>
+          <t>cisse kemo</t>
+        </is>
+      </c>
+      <c r="BT121" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="BU121" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="BV121" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="BW121" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="BX121" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="BY121" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="BZ121" t="inlineStr"/>
+      <c r="CA121" t="inlineStr"/>
+      <c r="CB121" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="CC121" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="CD121" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="CE121" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="CF121" t="inlineStr">
+        <is>
+          <t>McCSZuxs</t>
+        </is>
+      </c>
+      <c r="CG121" t="inlineStr">
+        <is>
+          <t>sagna amadou</t>
+        </is>
+      </c>
+      <c r="CH121" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="CI121" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="CJ121" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="CK121" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="CL121" t="inlineStr">
+        <is>
+          <t>29krq31i</t>
+        </is>
+      </c>
+      <c r="CM121" t="inlineStr">
+        <is>
+          <t>sidibe kalidou</t>
+        </is>
+      </c>
+      <c r="CN121" t="inlineStr">
+        <is>
+          <t>zH8Wrlde</t>
+        </is>
+      </c>
+      <c r="CO121" t="inlineStr">
+        <is>
+          <t>labeau brighton</t>
+        </is>
+      </c>
+      <c r="CP121" t="inlineStr">
+        <is>
+          <t>zH8Wrlde</t>
+        </is>
+      </c>
+      <c r="CQ121" t="inlineStr">
+        <is>
+          <t>labeau brighton</t>
+        </is>
+      </c>
+      <c r="CR121" t="inlineStr">
+        <is>
+          <t>GxfU6qGd</t>
+        </is>
+      </c>
+      <c r="CS121" t="inlineStr">
+        <is>
+          <t>picard hugo</t>
+        </is>
+      </c>
+      <c r="CT121" t="inlineStr">
+        <is>
+          <t>8IfBwmXp</t>
+        </is>
+      </c>
+      <c r="CU121" t="inlineStr">
+        <is>
+          <t>maronnier lucas</t>
+        </is>
+      </c>
+      <c r="CV121" t="inlineStr">
+        <is>
+          <t>8IfBwmXp</t>
+        </is>
+      </c>
+      <c r="CW121" t="inlineStr">
+        <is>
+          <t>maronnier lucas</t>
+        </is>
+      </c>
+      <c r="CX121" t="inlineStr">
+        <is>
+          <t>QPweXact</t>
+        </is>
+      </c>
+      <c r="CY121" t="inlineStr">
+        <is>
+          <t>vallier lenny</t>
+        </is>
+      </c>
+      <c r="CZ121" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="DA121" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="DB121" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="DC121" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="DD121" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="DE121" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="DF121" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="DG121" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="DH121" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="DI121" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="DJ121" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="DK121" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="DL121" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="DM121" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="DN121" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="DO121" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="DP121" t="inlineStr">
+        <is>
+          <t>Cf8ju4GK</t>
+        </is>
+      </c>
+      <c r="DQ121" t="inlineStr">
+        <is>
+          <t>hachem ryad</t>
+        </is>
+      </c>
+      <c r="DR121" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="DS121" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="DT121" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="DU121" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="DV121" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="DW121" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="DX121" t="inlineStr"/>
+      <c r="DY121" t="inlineStr"/>
+      <c r="DZ121" t="inlineStr"/>
+      <c r="EA121" t="inlineStr"/>
+      <c r="EB121" t="inlineStr"/>
+      <c r="EC121" t="inlineStr"/>
+      <c r="ED121" t="inlineStr"/>
+      <c r="EE121" t="inlineStr"/>
+      <c r="EF121" t="inlineStr"/>
+      <c r="EG121" t="inlineStr"/>
+      <c r="EH121" t="inlineStr"/>
+      <c r="EI121" t="inlineStr"/>
+      <c r="EJ121" t="inlineStr"/>
+      <c r="EK121" t="inlineStr"/>
+      <c r="EL121" t="inlineStr"/>
+      <c r="EM121" t="inlineStr"/>
+      <c r="EN121" t="inlineStr"/>
+      <c r="EO121" t="inlineStr"/>
+      <c r="EP121" t="inlineStr"/>
+      <c r="EQ121" t="inlineStr"/>
+      <c r="ER121" t="inlineStr"/>
+      <c r="ES121" t="inlineStr"/>
+      <c r="ET121" t="inlineStr"/>
+      <c r="EU121" t="inlineStr"/>
+      <c r="EV121" t="inlineStr"/>
+      <c r="EW121" t="inlineStr"/>
+      <c r="EX121" t="inlineStr">
+        <is>
+          <t>j3IsAvo7</t>
+        </is>
+      </c>
+      <c r="EY121" t="inlineStr">
+        <is>
+          <t>cisse kemo</t>
+        </is>
+      </c>
+      <c r="EZ121" t="inlineStr">
+        <is>
+          <t>j3IsAvo7</t>
+        </is>
+      </c>
+      <c r="FA121" t="inlineStr">
+        <is>
+          <t>cisse kemo</t>
+        </is>
+      </c>
+      <c r="FB121" t="inlineStr">
+        <is>
+          <t>lUS5czaO</t>
+        </is>
+      </c>
+      <c r="FC121" t="inlineStr">
+        <is>
+          <t>ifnaoui merwan</t>
+        </is>
+      </c>
+      <c r="FD121" t="inlineStr"/>
+      <c r="FE121" t="inlineStr"/>
+      <c r="FF121" t="inlineStr"/>
+      <c r="FG121" t="inlineStr"/>
+      <c r="FH121" t="inlineStr"/>
+      <c r="FI121" t="inlineStr"/>
+      <c r="FJ121" t="inlineStr"/>
+      <c r="FK121" t="inlineStr"/>
+      <c r="FL121" t="inlineStr"/>
+      <c r="FM121" t="inlineStr"/>
+      <c r="FN121" t="inlineStr"/>
+      <c r="FO121" t="inlineStr"/>
+      <c r="FP121" t="inlineStr"/>
+      <c r="FQ121" t="inlineStr"/>
+      <c r="FR121" t="inlineStr"/>
+      <c r="FS121" t="inlineStr"/>
+      <c r="FT121" t="inlineStr"/>
+      <c r="FU121" t="inlineStr"/>
+      <c r="FV121" t="inlineStr"/>
+      <c r="FW121" t="inlineStr"/>
+      <c r="FX121" t="inlineStr"/>
+      <c r="FY121" t="inlineStr"/>
+      <c r="FZ121" t="inlineStr"/>
+      <c r="GA121" t="inlineStr"/>
+      <c r="GB121" t="inlineStr"/>
+      <c r="GC121" t="inlineStr"/>
+      <c r="GD121" t="inlineStr"/>
+      <c r="GE121" t="inlineStr"/>
+      <c r="GF121" t="inlineStr"/>
+      <c r="GG121" t="inlineStr"/>
+      <c r="GH121" t="inlineStr"/>
+      <c r="GI121" t="inlineStr"/>
+      <c r="GJ121" t="inlineStr"/>
+      <c r="GK121" t="inlineStr"/>
+      <c r="GL121" t="inlineStr"/>
+      <c r="GM121" t="inlineStr"/>
+      <c r="GN121" t="inlineStr"/>
+      <c r="GO121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>QiPssnZI</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GvRRSA15</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>aymes jeremy</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CI9LnrCi</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>saintini nathanael</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>bw41ww90</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>morante leandro</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>K6gqRt3c</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>falette simon</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>zciOF0Jn</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>amraoui ayoub</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>drXPszOh</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>solvet steve</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>AuRgvOVQ</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>robin milan</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>KAGdlKQ8</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>bamba mohamed</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>hz9iLSns</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>placide johnny</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>dGEFacR1</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>bohnert florian</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>SGS1GzV5</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>akueson gustave</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>IwWAp1LB</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>guevara juan</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>tIMjIu1I</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>ariss zakaria</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>ronEz0Iq</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>ducrocq tom</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr">
+        <is>
+          <t>b9dIWhMU</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>onana cyrille</t>
+        </is>
+      </c>
+      <c r="AN122" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>vVf0mSM7</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>boutrah amine</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr">
+        <is>
+          <t>fuqL2LJ2</t>
+        </is>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>bonalair max</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>6c3rD50k</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>djaha akim</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>GM3MZsvr</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>etile yannick</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>Yye7kYuP</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>gautier luan</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>QgF8WB2F</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>kembolo francis</t>
+        </is>
+      </c>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="BE122" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="BF122" t="inlineStr">
+        <is>
+          <t>fTP84ZUd</t>
+        </is>
+      </c>
+      <c r="BG122" t="inlineStr">
+        <is>
+          <t>shamal steve</t>
+        </is>
+      </c>
+      <c r="BH122" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="BI122" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="inlineStr">
+        <is>
+          <t>vcfrwUSo</t>
+        </is>
+      </c>
+      <c r="BM122" t="inlineStr">
+        <is>
+          <t>boumaaoui mohamed amine</t>
+        </is>
+      </c>
+      <c r="BN122" t="inlineStr">
+        <is>
+          <t>4Ou8BC7i</t>
+        </is>
+      </c>
+      <c r="BO122" t="inlineStr">
+        <is>
+          <t>cisse lamine</t>
+        </is>
+      </c>
+      <c r="BP122" t="inlineStr">
+        <is>
+          <t>OdiG9Lyg</t>
+        </is>
+      </c>
+      <c r="BQ122" t="inlineStr">
+        <is>
+          <t>fabri julien</t>
+        </is>
+      </c>
+      <c r="BR122" t="inlineStr">
+        <is>
+          <t>KK953yrm</t>
+        </is>
+      </c>
+      <c r="BS122" t="inlineStr">
+        <is>
+          <t>inao oulai christ</t>
+        </is>
+      </c>
+      <c r="BT122" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="BU122" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="BV122" t="inlineStr">
+        <is>
+          <t>4C2mjUxk</t>
+        </is>
+      </c>
+      <c r="BW122" t="inlineStr">
+        <is>
+          <t>roncaglia anthony</t>
+        </is>
+      </c>
+      <c r="BX122" t="inlineStr">
+        <is>
+          <t>x6p5H6p3</t>
+        </is>
+      </c>
+      <c r="BY122" t="inlineStr">
+        <is>
+          <t>tavares dylan</t>
+        </is>
+      </c>
+      <c r="BZ122" t="inlineStr"/>
+      <c r="CA122" t="inlineStr"/>
+      <c r="CB122" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="CC122" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="CD122" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="CE122" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="CF122" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="CG122" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="CH122" t="inlineStr">
+        <is>
+          <t>fTP84ZUd</t>
+        </is>
+      </c>
+      <c r="CI122" t="inlineStr">
+        <is>
+          <t>shamal steve</t>
+        </is>
+      </c>
+      <c r="CJ122" t="inlineStr">
+        <is>
+          <t>fTP84ZUd</t>
+        </is>
+      </c>
+      <c r="CK122" t="inlineStr">
+        <is>
+          <t>shamal steve</t>
+        </is>
+      </c>
+      <c r="CL122" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="CM122" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="CN122" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="CO122" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="CP122" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="CQ122" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="CR122" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="CS122" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="CT122" t="inlineStr"/>
+      <c r="CU122" t="inlineStr"/>
+      <c r="CV122" t="inlineStr"/>
+      <c r="CW122" t="inlineStr"/>
+      <c r="CX122" t="inlineStr"/>
+      <c r="CY122" t="inlineStr"/>
+      <c r="CZ122" t="inlineStr">
+        <is>
+          <t>4Ou8BC7i</t>
+        </is>
+      </c>
+      <c r="DA122" t="inlineStr">
+        <is>
+          <t>cisse lamine</t>
+        </is>
+      </c>
+      <c r="DB122" t="inlineStr">
+        <is>
+          <t>4Ou8BC7i</t>
+        </is>
+      </c>
+      <c r="DC122" t="inlineStr">
+        <is>
+          <t>cisse lamine</t>
+        </is>
+      </c>
+      <c r="DD122" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="DE122" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="DF122" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="DG122" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="DH122" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="DI122" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="DJ122" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="DK122" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="DL122" t="inlineStr">
+        <is>
+          <t>vcfrwUSo</t>
+        </is>
+      </c>
+      <c r="DM122" t="inlineStr">
+        <is>
+          <t>boumaaoui mohamed amine</t>
+        </is>
+      </c>
+      <c r="DN122" t="inlineStr">
+        <is>
+          <t>vcfrwUSo</t>
+        </is>
+      </c>
+      <c r="DO122" t="inlineStr">
+        <is>
+          <t>boumaaoui mohamed amine</t>
+        </is>
+      </c>
+      <c r="DP122" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="DQ122" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="DR122" t="inlineStr">
+        <is>
+          <t>x6p5H6p3</t>
+        </is>
+      </c>
+      <c r="DS122" t="inlineStr">
+        <is>
+          <t>tavares dylan</t>
+        </is>
+      </c>
+      <c r="DT122" t="inlineStr">
+        <is>
+          <t>x6p5H6p3</t>
+        </is>
+      </c>
+      <c r="DU122" t="inlineStr">
+        <is>
+          <t>tavares dylan</t>
+        </is>
+      </c>
+      <c r="DV122" t="inlineStr">
+        <is>
+          <t>vVf0mSM7</t>
+        </is>
+      </c>
+      <c r="DW122" t="inlineStr">
+        <is>
+          <t>boutrah amine</t>
+        </is>
+      </c>
+      <c r="DX122" t="inlineStr"/>
+      <c r="DY122" t="inlineStr"/>
+      <c r="DZ122" t="inlineStr"/>
+      <c r="EA122" t="inlineStr"/>
+      <c r="EB122" t="inlineStr"/>
+      <c r="EC122" t="inlineStr"/>
+      <c r="ED122" t="inlineStr"/>
+      <c r="EE122" t="inlineStr"/>
+      <c r="EF122" t="inlineStr"/>
+      <c r="EG122" t="inlineStr"/>
+      <c r="EH122" t="inlineStr"/>
+      <c r="EI122" t="inlineStr"/>
+      <c r="EJ122" t="inlineStr"/>
+      <c r="EK122" t="inlineStr"/>
+      <c r="EL122" t="inlineStr"/>
+      <c r="EM122" t="inlineStr"/>
+      <c r="EN122" t="inlineStr"/>
+      <c r="EO122" t="inlineStr"/>
+      <c r="EP122" t="inlineStr"/>
+      <c r="EQ122" t="inlineStr"/>
+      <c r="ER122" t="inlineStr"/>
+      <c r="ES122" t="inlineStr"/>
+      <c r="ET122" t="inlineStr"/>
+      <c r="EU122" t="inlineStr"/>
+      <c r="EV122" t="inlineStr"/>
+      <c r="EW122" t="inlineStr"/>
+      <c r="EX122" t="inlineStr"/>
+      <c r="EY122" t="inlineStr"/>
+      <c r="EZ122" t="inlineStr"/>
+      <c r="FA122" t="inlineStr"/>
+      <c r="FB122" t="inlineStr"/>
+      <c r="FC122" t="inlineStr"/>
+      <c r="FD122" t="inlineStr"/>
+      <c r="FE122" t="inlineStr"/>
+      <c r="FF122" t="inlineStr"/>
+      <c r="FG122" t="inlineStr"/>
+      <c r="FH122" t="inlineStr"/>
+      <c r="FI122" t="inlineStr"/>
+      <c r="FJ122" t="inlineStr"/>
+      <c r="FK122" t="inlineStr"/>
+      <c r="FL122" t="inlineStr"/>
+      <c r="FM122" t="inlineStr"/>
+      <c r="FN122" t="inlineStr"/>
+      <c r="FO122" t="inlineStr"/>
+      <c r="FP122" t="inlineStr"/>
+      <c r="FQ122" t="inlineStr"/>
+      <c r="FR122" t="inlineStr"/>
+      <c r="FS122" t="inlineStr"/>
+      <c r="FT122" t="inlineStr"/>
+      <c r="FU122" t="inlineStr"/>
+      <c r="FV122" t="inlineStr"/>
+      <c r="FW122" t="inlineStr"/>
+      <c r="FX122" t="inlineStr"/>
+      <c r="FY122" t="inlineStr"/>
+      <c r="FZ122" t="inlineStr"/>
+      <c r="GA122" t="inlineStr"/>
+      <c r="GB122" t="inlineStr"/>
+      <c r="GC122" t="inlineStr"/>
+      <c r="GD122" t="inlineStr"/>
+      <c r="GE122" t="inlineStr"/>
+      <c r="GF122" t="inlineStr"/>
+      <c r="GG122" t="inlineStr"/>
+      <c r="GH122" t="inlineStr"/>
+      <c r="GI122" t="inlineStr"/>
+      <c r="GJ122" t="inlineStr"/>
+      <c r="GK122" t="inlineStr"/>
+      <c r="GL122" t="inlineStr"/>
+      <c r="GM122" t="inlineStr"/>
+      <c r="GN122" t="inlineStr"/>
+      <c r="GO122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/all/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GO122"/>
+  <dimension ref="A1:GO126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92157,6 +92157,2938 @@
       <c r="GN122" t="inlineStr"/>
       <c r="GO122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Qe5HfcWe</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>lecomte benjamin</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>WOiB5ygg</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>sacko falaye</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>hQGrDm2I</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>omeragic becir</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>pYI2rM4H</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>sagnan modibo</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>IFhobcS1</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>sylla issiaga</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>j5dSkdZI</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>ferri jordan</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>vsv6TioJ</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>savanier teji</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2qMy8CA5</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>coulibaly tanguy</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>nks9eiQ4</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>adams akor</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>p64JKtYL</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>lafont alban</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>vLPNfRe2</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>coco marcus</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>2XnIOLsp</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>pallois nicolas</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>xYHsz2uS</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>zeze nathan</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>G6Icx4DR</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>duverne jean kevin</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>2NKKC5LI</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>chirivella pedro</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>21Ny44li</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>lepenant johann</t>
+        </is>
+      </c>
+      <c r="AL123" t="inlineStr">
+        <is>
+          <t>YHDXXra7</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>thomas sorba</t>
+        </is>
+      </c>
+      <c r="AN123" t="inlineStr">
+        <is>
+          <t>0vxfG1Jf</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>kadewere tino</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>Cj5rnjpG</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>simon moses</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>4pCFSl1P</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>abline matthis</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr">
+        <is>
+          <t>GUpH52h6</t>
+        </is>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>bares gabriel</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>GKgj13Ht</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>bertaud dimitry</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>dYGOQd5o</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>chennahi theo</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>S4sVF7O0</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>dzodic stefan</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>Qwp5yt4r</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>fayad khalil</t>
+        </is>
+      </c>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>pA3wMl0B</t>
+        </is>
+      </c>
+      <c r="BE123" t="inlineStr">
+        <is>
+          <t>issoufou yanis ali</t>
+        </is>
+      </c>
+      <c r="BF123" t="inlineStr">
+        <is>
+          <t>Q7VDuZr1</t>
+        </is>
+      </c>
+      <c r="BG123" t="inlineStr">
+        <is>
+          <t>khazri wahbi</t>
+        </is>
+      </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>A1rzEd2O</t>
+        </is>
+      </c>
+      <c r="BI123" t="inlineStr">
+        <is>
+          <t>inzingoula rabby</t>
+        </is>
+      </c>
+      <c r="BJ123" t="inlineStr">
+        <is>
+          <t>QHKswk6H</t>
+        </is>
+      </c>
+      <c r="BK123" t="inlineStr">
+        <is>
+          <t>tchato enzo</t>
+        </is>
+      </c>
+      <c r="BL123" t="inlineStr">
+        <is>
+          <t>Qm7z6ES9</t>
+        </is>
+      </c>
+      <c r="BM123" t="inlineStr">
+        <is>
+          <t>acapandie mathieu</t>
+        </is>
+      </c>
+      <c r="BN123" t="inlineStr">
+        <is>
+          <t>M7BOiYYH</t>
+        </is>
+      </c>
+      <c r="BO123" t="inlineStr">
+        <is>
+          <t>amian adou kelvin</t>
+        </is>
+      </c>
+      <c r="BP123" t="inlineStr">
+        <is>
+          <t>UHFZg7zc</t>
+        </is>
+      </c>
+      <c r="BQ123" t="inlineStr">
+        <is>
+          <t>assoumani dehmaine</t>
+        </is>
+      </c>
+      <c r="BR123" t="inlineStr">
+        <is>
+          <t>AsPIAoni</t>
+        </is>
+      </c>
+      <c r="BS123" t="inlineStr">
+        <is>
+          <t>augusto douglas</t>
+        </is>
+      </c>
+      <c r="BT123" t="inlineStr">
+        <is>
+          <t>xK337SFG</t>
+        </is>
+      </c>
+      <c r="BU123" t="inlineStr">
+        <is>
+          <t>barbet hugo</t>
+        </is>
+      </c>
+      <c r="BV123" t="inlineStr">
+        <is>
+          <t>2BI6b6Qj</t>
+        </is>
+      </c>
+      <c r="BW123" t="inlineStr">
+        <is>
+          <t>cozza nicolas</t>
+        </is>
+      </c>
+      <c r="BX123" t="inlineStr">
+        <is>
+          <t>AiotaxUt</t>
+        </is>
+      </c>
+      <c r="BY123" t="inlineStr">
+        <is>
+          <t>guirassy bahereba</t>
+        </is>
+      </c>
+      <c r="BZ123" t="inlineStr">
+        <is>
+          <t>zy2QKhzd</t>
+        </is>
+      </c>
+      <c r="CA123" t="inlineStr">
+        <is>
+          <t>leroux louis</t>
+        </is>
+      </c>
+      <c r="CB123" t="inlineStr">
+        <is>
+          <t>QHKswk6H</t>
+        </is>
+      </c>
+      <c r="CC123" t="inlineStr">
+        <is>
+          <t>tchato enzo</t>
+        </is>
+      </c>
+      <c r="CD123" t="inlineStr">
+        <is>
+          <t>QHKswk6H</t>
+        </is>
+      </c>
+      <c r="CE123" t="inlineStr">
+        <is>
+          <t>tchato enzo</t>
+        </is>
+      </c>
+      <c r="CF123" t="inlineStr">
+        <is>
+          <t>IFhobcS1</t>
+        </is>
+      </c>
+      <c r="CG123" t="inlineStr">
+        <is>
+          <t>sylla issiaga</t>
+        </is>
+      </c>
+      <c r="CH123" t="inlineStr">
+        <is>
+          <t>A1rzEd2O</t>
+        </is>
+      </c>
+      <c r="CI123" t="inlineStr">
+        <is>
+          <t>inzingoula rabby</t>
+        </is>
+      </c>
+      <c r="CJ123" t="inlineStr">
+        <is>
+          <t>A1rzEd2O</t>
+        </is>
+      </c>
+      <c r="CK123" t="inlineStr">
+        <is>
+          <t>inzingoula rabby</t>
+        </is>
+      </c>
+      <c r="CL123" t="inlineStr">
+        <is>
+          <t>bkWk025d</t>
+        </is>
+      </c>
+      <c r="CM123" t="inlineStr">
+        <is>
+          <t>chotard joris</t>
+        </is>
+      </c>
+      <c r="CN123" t="inlineStr">
+        <is>
+          <t>Qwp5yt4r</t>
+        </is>
+      </c>
+      <c r="CO123" t="inlineStr">
+        <is>
+          <t>fayad khalil</t>
+        </is>
+      </c>
+      <c r="CP123" t="inlineStr">
+        <is>
+          <t>Qwp5yt4r</t>
+        </is>
+      </c>
+      <c r="CQ123" t="inlineStr">
+        <is>
+          <t>fayad khalil</t>
+        </is>
+      </c>
+      <c r="CR123" t="inlineStr">
+        <is>
+          <t>Y7pbUJA4</t>
+        </is>
+      </c>
+      <c r="CS123" t="inlineStr">
+        <is>
+          <t>al tamari mousa suleiman</t>
+        </is>
+      </c>
+      <c r="CT123" t="inlineStr">
+        <is>
+          <t>Q7VDuZr1</t>
+        </is>
+      </c>
+      <c r="CU123" t="inlineStr">
+        <is>
+          <t>khazri wahbi</t>
+        </is>
+      </c>
+      <c r="CV123" t="inlineStr">
+        <is>
+          <t>Q7VDuZr1</t>
+        </is>
+      </c>
+      <c r="CW123" t="inlineStr">
+        <is>
+          <t>khazri wahbi</t>
+        </is>
+      </c>
+      <c r="CX123" t="inlineStr">
+        <is>
+          <t>2qMy8CA5</t>
+        </is>
+      </c>
+      <c r="CY123" t="inlineStr">
+        <is>
+          <t>coulibaly tanguy</t>
+        </is>
+      </c>
+      <c r="CZ123" t="inlineStr">
+        <is>
+          <t>M7BOiYYH</t>
+        </is>
+      </c>
+      <c r="DA123" t="inlineStr">
+        <is>
+          <t>amian adou kelvin</t>
+        </is>
+      </c>
+      <c r="DB123" t="inlineStr">
+        <is>
+          <t>M7BOiYYH</t>
+        </is>
+      </c>
+      <c r="DC123" t="inlineStr">
+        <is>
+          <t>amian adou kelvin</t>
+        </is>
+      </c>
+      <c r="DD123" t="inlineStr">
+        <is>
+          <t>YHDXXra7</t>
+        </is>
+      </c>
+      <c r="DE123" t="inlineStr">
+        <is>
+          <t>thomas sorba</t>
+        </is>
+      </c>
+      <c r="DF123" t="inlineStr">
+        <is>
+          <t>roG6AGUf</t>
+        </is>
+      </c>
+      <c r="DG123" t="inlineStr">
+        <is>
+          <t>mostafa mohamed</t>
+        </is>
+      </c>
+      <c r="DH123" t="inlineStr">
+        <is>
+          <t>roG6AGUf</t>
+        </is>
+      </c>
+      <c r="DI123" t="inlineStr">
+        <is>
+          <t>mostafa mohamed</t>
+        </is>
+      </c>
+      <c r="DJ123" t="inlineStr">
+        <is>
+          <t>4pCFSl1P</t>
+        </is>
+      </c>
+      <c r="DK123" t="inlineStr">
+        <is>
+          <t>abline matthis</t>
+        </is>
+      </c>
+      <c r="DL123" t="inlineStr">
+        <is>
+          <t>zy2QKhzd</t>
+        </is>
+      </c>
+      <c r="DM123" t="inlineStr">
+        <is>
+          <t>leroux louis</t>
+        </is>
+      </c>
+      <c r="DN123" t="inlineStr">
+        <is>
+          <t>zy2QKhzd</t>
+        </is>
+      </c>
+      <c r="DO123" t="inlineStr">
+        <is>
+          <t>leroux louis</t>
+        </is>
+      </c>
+      <c r="DP123" t="inlineStr">
+        <is>
+          <t>vLPNfRe2</t>
+        </is>
+      </c>
+      <c r="DQ123" t="inlineStr">
+        <is>
+          <t>coco marcus</t>
+        </is>
+      </c>
+      <c r="DR123" t="inlineStr">
+        <is>
+          <t>AiotaxUt</t>
+        </is>
+      </c>
+      <c r="DS123" t="inlineStr">
+        <is>
+          <t>guirassy bahereba</t>
+        </is>
+      </c>
+      <c r="DT123" t="inlineStr">
+        <is>
+          <t>AiotaxUt</t>
+        </is>
+      </c>
+      <c r="DU123" t="inlineStr">
+        <is>
+          <t>guirassy bahereba</t>
+        </is>
+      </c>
+      <c r="DV123" t="inlineStr">
+        <is>
+          <t>Cj5rnjpG</t>
+        </is>
+      </c>
+      <c r="DW123" t="inlineStr">
+        <is>
+          <t>simon moses</t>
+        </is>
+      </c>
+      <c r="DX123" t="inlineStr">
+        <is>
+          <t>dSDrHenE</t>
+        </is>
+      </c>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>gueguin axel</t>
+        </is>
+      </c>
+      <c r="DZ123" t="inlineStr">
+        <is>
+          <t>4hOup61a</t>
+        </is>
+      </c>
+      <c r="EA123" t="inlineStr">
+        <is>
+          <t>jullien christopher</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>ERFuKxAR</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>kouyate boubakar</t>
+        </is>
+      </c>
+      <c r="ED123" t="inlineStr">
+        <is>
+          <t>AX8IYJcC</t>
+        </is>
+      </c>
+      <c r="EE123" t="inlineStr">
+        <is>
+          <t>mincarelli lucas</t>
+        </is>
+      </c>
+      <c r="EF123" t="inlineStr">
+        <is>
+          <t>MiH8I5Na</t>
+        </is>
+      </c>
+      <c r="EG123" t="inlineStr">
+        <is>
+          <t>castelletto jean charles</t>
+        </is>
+      </c>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>hYtVzJ13</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>centonze fabien</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>GCkY7Wy8</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>ganago igniatius</t>
+        </is>
+      </c>
+      <c r="EL123" t="inlineStr">
+        <is>
+          <t>l2t9fvR7</t>
+        </is>
+      </c>
+      <c r="EM123" t="inlineStr">
+        <is>
+          <t>mahamoud adel</t>
+        </is>
+      </c>
+      <c r="EN123" t="inlineStr">
+        <is>
+          <t>0t5Mjaa6</t>
+        </is>
+      </c>
+      <c r="EO123" t="inlineStr">
+        <is>
+          <t>mollet florent</t>
+        </is>
+      </c>
+      <c r="EP123" t="inlineStr">
+        <is>
+          <t>roG6AGUf</t>
+        </is>
+      </c>
+      <c r="EQ123" t="inlineStr">
+        <is>
+          <t>mostafa mohamed</t>
+        </is>
+      </c>
+      <c r="ER123" t="inlineStr"/>
+      <c r="ES123" t="inlineStr"/>
+      <c r="ET123" t="inlineStr"/>
+      <c r="EU123" t="inlineStr"/>
+      <c r="EV123" t="inlineStr"/>
+      <c r="EW123" t="inlineStr"/>
+      <c r="EX123" t="inlineStr">
+        <is>
+          <t>2BI6b6Qj</t>
+        </is>
+      </c>
+      <c r="EY123" t="inlineStr">
+        <is>
+          <t>cozza nicolas</t>
+        </is>
+      </c>
+      <c r="EZ123" t="inlineStr">
+        <is>
+          <t>2BI6b6Qj</t>
+        </is>
+      </c>
+      <c r="FA123" t="inlineStr">
+        <is>
+          <t>cozza nicolas</t>
+        </is>
+      </c>
+      <c r="FB123" t="inlineStr">
+        <is>
+          <t>0vxfG1Jf</t>
+        </is>
+      </c>
+      <c r="FC123" t="inlineStr">
+        <is>
+          <t>kadewere tino</t>
+        </is>
+      </c>
+      <c r="FD123" t="inlineStr">
+        <is>
+          <t>A7vSQTKq</t>
+        </is>
+      </c>
+      <c r="FE123" t="inlineStr">
+        <is>
+          <t>nordin arnaud</t>
+        </is>
+      </c>
+      <c r="FF123" t="inlineStr">
+        <is>
+          <t>G8o32H2s</t>
+        </is>
+      </c>
+      <c r="FG123" t="inlineStr">
+        <is>
+          <t>sainte luce theo</t>
+        </is>
+      </c>
+      <c r="FH123" t="inlineStr"/>
+      <c r="FI123" t="inlineStr"/>
+      <c r="FJ123" t="inlineStr"/>
+      <c r="FK123" t="inlineStr"/>
+      <c r="FL123" t="inlineStr"/>
+      <c r="FM123" t="inlineStr"/>
+      <c r="FN123" t="inlineStr"/>
+      <c r="FO123" t="inlineStr"/>
+      <c r="FP123" t="inlineStr"/>
+      <c r="FQ123" t="inlineStr"/>
+      <c r="FR123" t="inlineStr"/>
+      <c r="FS123" t="inlineStr"/>
+      <c r="FT123" t="inlineStr"/>
+      <c r="FU123" t="inlineStr"/>
+      <c r="FV123" t="inlineStr"/>
+      <c r="FW123" t="inlineStr"/>
+      <c r="FX123" t="inlineStr"/>
+      <c r="FY123" t="inlineStr"/>
+      <c r="FZ123" t="inlineStr"/>
+      <c r="GA123" t="inlineStr"/>
+      <c r="GB123" t="inlineStr"/>
+      <c r="GC123" t="inlineStr"/>
+      <c r="GD123" t="inlineStr"/>
+      <c r="GE123" t="inlineStr"/>
+      <c r="GF123" t="inlineStr"/>
+      <c r="GG123" t="inlineStr"/>
+      <c r="GH123" t="inlineStr"/>
+      <c r="GI123" t="inlineStr"/>
+      <c r="GJ123" t="inlineStr"/>
+      <c r="GK123" t="inlineStr"/>
+      <c r="GL123" t="inlineStr"/>
+      <c r="GM123" t="inlineStr"/>
+      <c r="GN123" t="inlineStr"/>
+      <c r="GO123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>OlUQhqqo</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>bizot marco</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>0IiimISF</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>lala kenny</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>GnvxP2X3</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>chardonnet brendan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>hEHAtkEC</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>le cardinal julien</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>xQENPIHR</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>amavi jordan</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>IsJ0zlTM</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>camara mahdi</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>YJ2AR519</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>magnetti hugo</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>h8g5dFkH</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>faivre romain</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>hnER3xyT</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>del castillo romain</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>MPlU0iTh</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>ajorque ludovic</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>xzssoNnp</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>sima abdallah</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>IH9cf1NH</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>larsonneur gautier</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>by5QHeY8</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>macon yvann</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>QcLd3bL1</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>batubinsika dylan</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>OYtRcGFm</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>abdelhamid yunis</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>67mIaVqd</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>cornud pierre</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>0SDVC1gR</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>fomba lamine</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>W6Xd8Gyg</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>amougou mathis</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>W6PE7nsb</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>aiki ayman</t>
+        </is>
+      </c>
+      <c r="AN124" t="inlineStr">
+        <is>
+          <t>fkTUaOi8</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>davitashvili zuriko</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>dKzjZfiI</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>cafaro mathieu</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>MDGbgDq7</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>sissoko ibrahim</t>
+        </is>
+      </c>
+      <c r="AT124" t="inlineStr">
+        <is>
+          <t>OnmmDvKS</t>
+        </is>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>camblan axel</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>zHCAxaZn</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>coudert gregoire</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>YLVl99Q1</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>coulibaly soumaila</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>xbRv7JLU</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>diop serigne</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>pniy3Ny3</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>kante ibrahim</t>
+        </is>
+      </c>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>tQMgOwhG</t>
+        </is>
+      </c>
+      <c r="BE124" t="inlineStr">
+        <is>
+          <t>martin jonas</t>
+        </is>
+      </c>
+      <c r="BF124" t="inlineStr">
+        <is>
+          <t>n5sFh1Ch</t>
+        </is>
+      </c>
+      <c r="BG124" t="inlineStr">
+        <is>
+          <t>pereira mathias</t>
+        </is>
+      </c>
+      <c r="BH124" t="inlineStr">
+        <is>
+          <t>bmj4mkKq</t>
+        </is>
+      </c>
+      <c r="BI124" t="inlineStr">
+        <is>
+          <t>luc zogbe</t>
+        </is>
+      </c>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr">
+        <is>
+          <t>2acUGEci</t>
+        </is>
+      </c>
+      <c r="BM124" t="inlineStr">
+        <is>
+          <t>appiah dennis</t>
+        </is>
+      </c>
+      <c r="BN124" t="inlineStr">
+        <is>
+          <t>fFRVaYCs</t>
+        </is>
+      </c>
+      <c r="BO124" t="inlineStr">
+        <is>
+          <t>gauthier antoine</t>
+        </is>
+      </c>
+      <c r="BP124" t="inlineStr">
+        <is>
+          <t>GGYnig7m</t>
+        </is>
+      </c>
+      <c r="BQ124" t="inlineStr">
+        <is>
+          <t>maubleu brice</t>
+        </is>
+      </c>
+      <c r="BR124" t="inlineStr">
+        <is>
+          <t>zRiphMYO</t>
+        </is>
+      </c>
+      <c r="BS124" t="inlineStr">
+        <is>
+          <t>moueffek aimen</t>
+        </is>
+      </c>
+      <c r="BT124" t="inlineStr">
+        <is>
+          <t>tArngh4I</t>
+        </is>
+      </c>
+      <c r="BU124" t="inlineStr">
+        <is>
+          <t>mouton louis</t>
+        </is>
+      </c>
+      <c r="BV124" t="inlineStr">
+        <is>
+          <t>SG64s4Ks</t>
+        </is>
+      </c>
+      <c r="BW124" t="inlineStr">
+        <is>
+          <t>nade mickael</t>
+        </is>
+      </c>
+      <c r="BX124" t="inlineStr">
+        <is>
+          <t>db3kbs2N</t>
+        </is>
+      </c>
+      <c r="BY124" t="inlineStr">
+        <is>
+          <t>petrot leo</t>
+        </is>
+      </c>
+      <c r="BZ124" t="inlineStr">
+        <is>
+          <t>S0fUJqv9</t>
+        </is>
+      </c>
+      <c r="CA124" t="inlineStr">
+        <is>
+          <t>tardieu florian</t>
+        </is>
+      </c>
+      <c r="CB124" t="inlineStr">
+        <is>
+          <t>tQMgOwhG</t>
+        </is>
+      </c>
+      <c r="CC124" t="inlineStr">
+        <is>
+          <t>martin jonas</t>
+        </is>
+      </c>
+      <c r="CD124" t="inlineStr">
+        <is>
+          <t>tQMgOwhG</t>
+        </is>
+      </c>
+      <c r="CE124" t="inlineStr">
+        <is>
+          <t>martin jonas</t>
+        </is>
+      </c>
+      <c r="CF124" t="inlineStr">
+        <is>
+          <t>xzssoNnp</t>
+        </is>
+      </c>
+      <c r="CG124" t="inlineStr">
+        <is>
+          <t>sima abdallah</t>
+        </is>
+      </c>
+      <c r="CH124" t="inlineStr">
+        <is>
+          <t>bmj4mkKq</t>
+        </is>
+      </c>
+      <c r="CI124" t="inlineStr">
+        <is>
+          <t>luc zogbe</t>
+        </is>
+      </c>
+      <c r="CJ124" t="inlineStr">
+        <is>
+          <t>bmj4mkKq</t>
+        </is>
+      </c>
+      <c r="CK124" t="inlineStr">
+        <is>
+          <t>luc zogbe</t>
+        </is>
+      </c>
+      <c r="CL124" t="inlineStr">
+        <is>
+          <t>xQENPIHR</t>
+        </is>
+      </c>
+      <c r="CM124" t="inlineStr">
+        <is>
+          <t>amavi jordan</t>
+        </is>
+      </c>
+      <c r="CN124" t="inlineStr">
+        <is>
+          <t>YLVl99Q1</t>
+        </is>
+      </c>
+      <c r="CO124" t="inlineStr">
+        <is>
+          <t>coulibaly soumaila</t>
+        </is>
+      </c>
+      <c r="CP124" t="inlineStr">
+        <is>
+          <t>YLVl99Q1</t>
+        </is>
+      </c>
+      <c r="CQ124" t="inlineStr">
+        <is>
+          <t>coulibaly soumaila</t>
+        </is>
+      </c>
+      <c r="CR124" t="inlineStr">
+        <is>
+          <t>hEHAtkEC</t>
+        </is>
+      </c>
+      <c r="CS124" t="inlineStr">
+        <is>
+          <t>le cardinal julien</t>
+        </is>
+      </c>
+      <c r="CT124" t="inlineStr">
+        <is>
+          <t>n5sFh1Ch</t>
+        </is>
+      </c>
+      <c r="CU124" t="inlineStr">
+        <is>
+          <t>pereira mathias</t>
+        </is>
+      </c>
+      <c r="CV124" t="inlineStr">
+        <is>
+          <t>n5sFh1Ch</t>
+        </is>
+      </c>
+      <c r="CW124" t="inlineStr">
+        <is>
+          <t>pereira mathias</t>
+        </is>
+      </c>
+      <c r="CX124" t="inlineStr">
+        <is>
+          <t>h8g5dFkH</t>
+        </is>
+      </c>
+      <c r="CY124" t="inlineStr">
+        <is>
+          <t>faivre romain</t>
+        </is>
+      </c>
+      <c r="CZ124" t="inlineStr">
+        <is>
+          <t>2acUGEci</t>
+        </is>
+      </c>
+      <c r="DA124" t="inlineStr">
+        <is>
+          <t>appiah dennis</t>
+        </is>
+      </c>
+      <c r="DB124" t="inlineStr">
+        <is>
+          <t>2acUGEci</t>
+        </is>
+      </c>
+      <c r="DC124" t="inlineStr">
+        <is>
+          <t>appiah dennis</t>
+        </is>
+      </c>
+      <c r="DD124" t="inlineStr">
+        <is>
+          <t>by5QHeY8</t>
+        </is>
+      </c>
+      <c r="DE124" t="inlineStr">
+        <is>
+          <t>macon yvann</t>
+        </is>
+      </c>
+      <c r="DF124" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="DG124" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="DH124" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="DI124" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="DJ124" t="inlineStr">
+        <is>
+          <t>W6PE7nsb</t>
+        </is>
+      </c>
+      <c r="DK124" t="inlineStr">
+        <is>
+          <t>aiki ayman</t>
+        </is>
+      </c>
+      <c r="DL124" t="inlineStr">
+        <is>
+          <t>zRiphMYO</t>
+        </is>
+      </c>
+      <c r="DM124" t="inlineStr">
+        <is>
+          <t>moueffek aimen</t>
+        </is>
+      </c>
+      <c r="DN124" t="inlineStr">
+        <is>
+          <t>zRiphMYO</t>
+        </is>
+      </c>
+      <c r="DO124" t="inlineStr">
+        <is>
+          <t>moueffek aimen</t>
+        </is>
+      </c>
+      <c r="DP124" t="inlineStr">
+        <is>
+          <t>0SDVC1gR</t>
+        </is>
+      </c>
+      <c r="DQ124" t="inlineStr">
+        <is>
+          <t>fomba lamine</t>
+        </is>
+      </c>
+      <c r="DR124" t="inlineStr">
+        <is>
+          <t>db3kbs2N</t>
+        </is>
+      </c>
+      <c r="DS124" t="inlineStr">
+        <is>
+          <t>petrot leo</t>
+        </is>
+      </c>
+      <c r="DT124" t="inlineStr">
+        <is>
+          <t>db3kbs2N</t>
+        </is>
+      </c>
+      <c r="DU124" t="inlineStr">
+        <is>
+          <t>petrot leo</t>
+        </is>
+      </c>
+      <c r="DV124" t="inlineStr">
+        <is>
+          <t>67mIaVqd</t>
+        </is>
+      </c>
+      <c r="DW124" t="inlineStr">
+        <is>
+          <t>cornud pierre</t>
+        </is>
+      </c>
+      <c r="DX124" t="inlineStr">
+        <is>
+          <t>pQ5GqXFF</t>
+        </is>
+      </c>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>locko bradley</t>
+        </is>
+      </c>
+      <c r="DZ124" t="inlineStr">
+        <is>
+          <t>jgQdIv76</t>
+        </is>
+      </c>
+      <c r="EA124" t="inlineStr">
+        <is>
+          <t>n diaye niakhate</t>
+        </is>
+      </c>
+      <c r="EB124" t="inlineStr"/>
+      <c r="EC124" t="inlineStr"/>
+      <c r="ED124" t="inlineStr"/>
+      <c r="EE124" t="inlineStr"/>
+      <c r="EF124" t="inlineStr">
+        <is>
+          <t>2kCSVLV8</t>
+        </is>
+      </c>
+      <c r="EG124" t="inlineStr">
+        <is>
+          <t>bentayg mahmoud</t>
+        </is>
+      </c>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>KKGaeL7f</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>briancon anthony</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr"/>
+      <c r="EK124" t="inlineStr"/>
+      <c r="EL124" t="inlineStr"/>
+      <c r="EM124" t="inlineStr"/>
+      <c r="EN124" t="inlineStr"/>
+      <c r="EO124" t="inlineStr"/>
+      <c r="EP124" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="EQ124" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="ER124" t="inlineStr">
+        <is>
+          <t>OnmmDvKS</t>
+        </is>
+      </c>
+      <c r="ES124" t="inlineStr">
+        <is>
+          <t>camblan axel</t>
+        </is>
+      </c>
+      <c r="ET124" t="inlineStr">
+        <is>
+          <t>OnmmDvKS</t>
+        </is>
+      </c>
+      <c r="EU124" t="inlineStr">
+        <is>
+          <t>camblan axel</t>
+        </is>
+      </c>
+      <c r="EV124" t="inlineStr">
+        <is>
+          <t>hnER3xyT</t>
+        </is>
+      </c>
+      <c r="EW124" t="inlineStr">
+        <is>
+          <t>del castillo romain</t>
+        </is>
+      </c>
+      <c r="EX124" t="inlineStr">
+        <is>
+          <t>S0fUJqv9</t>
+        </is>
+      </c>
+      <c r="EY124" t="inlineStr">
+        <is>
+          <t>tardieu florian</t>
+        </is>
+      </c>
+      <c r="EZ124" t="inlineStr">
+        <is>
+          <t>S0fUJqv9</t>
+        </is>
+      </c>
+      <c r="FA124" t="inlineStr">
+        <is>
+          <t>tardieu florian</t>
+        </is>
+      </c>
+      <c r="FB124" t="inlineStr">
+        <is>
+          <t>W6Xd8Gyg</t>
+        </is>
+      </c>
+      <c r="FC124" t="inlineStr">
+        <is>
+          <t>amougou mathis</t>
+        </is>
+      </c>
+      <c r="FD124" t="inlineStr"/>
+      <c r="FE124" t="inlineStr"/>
+      <c r="FF124" t="inlineStr"/>
+      <c r="FG124" t="inlineStr"/>
+      <c r="FH124" t="inlineStr"/>
+      <c r="FI124" t="inlineStr"/>
+      <c r="FJ124" t="inlineStr"/>
+      <c r="FK124" t="inlineStr"/>
+      <c r="FL124" t="inlineStr"/>
+      <c r="FM124" t="inlineStr"/>
+      <c r="FN124" t="inlineStr"/>
+      <c r="FO124" t="inlineStr"/>
+      <c r="FP124" t="inlineStr"/>
+      <c r="FQ124" t="inlineStr"/>
+      <c r="FR124" t="inlineStr"/>
+      <c r="FS124" t="inlineStr"/>
+      <c r="FT124" t="inlineStr"/>
+      <c r="FU124" t="inlineStr"/>
+      <c r="FV124" t="inlineStr"/>
+      <c r="FW124" t="inlineStr"/>
+      <c r="FX124" t="inlineStr"/>
+      <c r="FY124" t="inlineStr"/>
+      <c r="FZ124" t="inlineStr"/>
+      <c r="GA124" t="inlineStr"/>
+      <c r="GB124" t="inlineStr"/>
+      <c r="GC124" t="inlineStr"/>
+      <c r="GD124" t="inlineStr"/>
+      <c r="GE124" t="inlineStr"/>
+      <c r="GF124" t="inlineStr"/>
+      <c r="GG124" t="inlineStr"/>
+      <c r="GH124" t="inlineStr"/>
+      <c r="GI124" t="inlineStr"/>
+      <c r="GJ124" t="inlineStr"/>
+      <c r="GK124" t="inlineStr"/>
+      <c r="GL124" t="inlineStr"/>
+      <c r="GM124" t="inlineStr"/>
+      <c r="GN124" t="inlineStr"/>
+      <c r="GO124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>zoZtwwYp</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2JHnrhNN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>gurtner regis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>buhL1Onn</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>corchia sebastien</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>xQJX0yQr</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>bakayoko siaka</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>6944n3Fq</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>fofana mamadou 1998</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>4vxs1tdM</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>vita remy</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>QgfweBPT</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>gene owen</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>UBVYZus6</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>kaiboue kylian</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>6w822cDk</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>leautey antoine</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>zJWNDWUp</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>lutin rayan</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>rySVdKzI</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>mubundu manitu messy</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>MFLAEEaI</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>mafouta louis</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>fkOg2Gqj</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>mvogo yvon</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Est8UaLc</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>igor silva</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>4nPjVrMS</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>mendy formose</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>bLU8KtEd</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>talbi montassar</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>O2h5w23g</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>ngameni darline zidane</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>8vMxrdie</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>mvuka joel</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>YJhgLOwk</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>ponceau julien</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr">
+        <is>
+          <t>WzrmHcCA</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>abergel laurent</t>
+        </is>
+      </c>
+      <c r="AN125" t="inlineStr">
+        <is>
+          <t>pOt3Q6yb</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>pagis pablo</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>zTOOlq65</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>aiyegun tosin</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr">
+        <is>
+          <t>EPx2q8TS</t>
+        </is>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>boya frank</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>fsQHmhiO</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>carroll andy</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>UFCV4BZC</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>chabane amine</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>SIEq4Qzk</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>dao elyess</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>hKnfwbm3</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>fofana ibrahim cheick junior</t>
+        </is>
+      </c>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>pWfVw1vj</t>
+        </is>
+      </c>
+      <c r="BE125" t="inlineStr">
+        <is>
+          <t>sauvage alexis</t>
+        </is>
+      </c>
+      <c r="BF125" t="inlineStr">
+        <is>
+          <t>CWFxV8dL</t>
+        </is>
+      </c>
+      <c r="BG125" t="inlineStr">
+        <is>
+          <t>touho mathis</t>
+        </is>
+      </c>
+      <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr">
+        <is>
+          <t>z1as6ykH</t>
+        </is>
+      </c>
+      <c r="BM125" t="inlineStr">
+        <is>
+          <t>adjei nathaniel</t>
+        </is>
+      </c>
+      <c r="BN125" t="inlineStr">
+        <is>
+          <t>hMJmRmWR</t>
+        </is>
+      </c>
+      <c r="BO125" t="inlineStr">
+        <is>
+          <t>avom arthur</t>
+        </is>
+      </c>
+      <c r="BP125" t="inlineStr">
+        <is>
+          <t>GjVTxPsc</t>
+        </is>
+      </c>
+      <c r="BQ125" t="inlineStr">
+        <is>
+          <t>james isaac</t>
+        </is>
+      </c>
+      <c r="BR125" t="inlineStr">
+        <is>
+          <t>hbh3pcUj</t>
+        </is>
+      </c>
+      <c r="BS125" t="inlineStr">
+        <is>
+          <t>kalulu gedeon</t>
+        </is>
+      </c>
+      <c r="BT125" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="BU125" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="BV125" t="inlineStr">
+        <is>
+          <t>KAxiV8Bj</t>
+        </is>
+      </c>
+      <c r="BW125" t="inlineStr">
+        <is>
+          <t>leroy benjamin</t>
+        </is>
+      </c>
+      <c r="BX125" t="inlineStr">
+        <is>
+          <t>YByvtrWm</t>
+        </is>
+      </c>
+      <c r="BY125" t="inlineStr">
+        <is>
+          <t>soumano sambou</t>
+        </is>
+      </c>
+      <c r="BZ125" t="inlineStr"/>
+      <c r="CA125" t="inlineStr"/>
+      <c r="CB125" t="inlineStr">
+        <is>
+          <t>fsQHmhiO</t>
+        </is>
+      </c>
+      <c r="CC125" t="inlineStr">
+        <is>
+          <t>carroll andy</t>
+        </is>
+      </c>
+      <c r="CD125" t="inlineStr">
+        <is>
+          <t>fsQHmhiO</t>
+        </is>
+      </c>
+      <c r="CE125" t="inlineStr">
+        <is>
+          <t>carroll andy</t>
+        </is>
+      </c>
+      <c r="CF125" t="inlineStr">
+        <is>
+          <t>rySVdKzI</t>
+        </is>
+      </c>
+      <c r="CG125" t="inlineStr">
+        <is>
+          <t>mubundu manitu messy</t>
+        </is>
+      </c>
+      <c r="CH125" t="inlineStr">
+        <is>
+          <t>EPx2q8TS</t>
+        </is>
+      </c>
+      <c r="CI125" t="inlineStr">
+        <is>
+          <t>boya frank</t>
+        </is>
+      </c>
+      <c r="CJ125" t="inlineStr">
+        <is>
+          <t>EPx2q8TS</t>
+        </is>
+      </c>
+      <c r="CK125" t="inlineStr">
+        <is>
+          <t>boya frank</t>
+        </is>
+      </c>
+      <c r="CL125" t="inlineStr">
+        <is>
+          <t>zJWNDWUp</t>
+        </is>
+      </c>
+      <c r="CM125" t="inlineStr">
+        <is>
+          <t>lutin rayan</t>
+        </is>
+      </c>
+      <c r="CN125" t="inlineStr">
+        <is>
+          <t>hKnfwbm3</t>
+        </is>
+      </c>
+      <c r="CO125" t="inlineStr">
+        <is>
+          <t>fofana ibrahim cheick junior</t>
+        </is>
+      </c>
+      <c r="CP125" t="inlineStr">
+        <is>
+          <t>hKnfwbm3</t>
+        </is>
+      </c>
+      <c r="CQ125" t="inlineStr">
+        <is>
+          <t>fofana ibrahim cheick junior</t>
+        </is>
+      </c>
+      <c r="CR125" t="inlineStr">
+        <is>
+          <t>UBVYZus6</t>
+        </is>
+      </c>
+      <c r="CS125" t="inlineStr">
+        <is>
+          <t>kaiboue kylian</t>
+        </is>
+      </c>
+      <c r="CT125" t="inlineStr"/>
+      <c r="CU125" t="inlineStr"/>
+      <c r="CV125" t="inlineStr"/>
+      <c r="CW125" t="inlineStr"/>
+      <c r="CX125" t="inlineStr"/>
+      <c r="CY125" t="inlineStr"/>
+      <c r="CZ125" t="inlineStr">
+        <is>
+          <t>YByvtrWm</t>
+        </is>
+      </c>
+      <c r="DA125" t="inlineStr">
+        <is>
+          <t>soumano sambou</t>
+        </is>
+      </c>
+      <c r="DB125" t="inlineStr">
+        <is>
+          <t>YByvtrWm</t>
+        </is>
+      </c>
+      <c r="DC125" t="inlineStr">
+        <is>
+          <t>soumano sambou</t>
+        </is>
+      </c>
+      <c r="DD125" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="DE125" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="DF125" t="inlineStr">
+        <is>
+          <t>hMJmRmWR</t>
+        </is>
+      </c>
+      <c r="DG125" t="inlineStr">
+        <is>
+          <t>avom arthur</t>
+        </is>
+      </c>
+      <c r="DH125" t="inlineStr">
+        <is>
+          <t>hMJmRmWR</t>
+        </is>
+      </c>
+      <c r="DI125" t="inlineStr">
+        <is>
+          <t>avom arthur</t>
+        </is>
+      </c>
+      <c r="DJ125" t="inlineStr">
+        <is>
+          <t>pOt3Q6yb</t>
+        </is>
+      </c>
+      <c r="DK125" t="inlineStr">
+        <is>
+          <t>pagis pablo</t>
+        </is>
+      </c>
+      <c r="DL125" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="DM125" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="DN125" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="DO125" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="DP125" t="inlineStr">
+        <is>
+          <t>8vMxrdie</t>
+        </is>
+      </c>
+      <c r="DQ125" t="inlineStr">
+        <is>
+          <t>mvuka joel</t>
+        </is>
+      </c>
+      <c r="DR125" t="inlineStr"/>
+      <c r="DS125" t="inlineStr"/>
+      <c r="DT125" t="inlineStr"/>
+      <c r="DU125" t="inlineStr"/>
+      <c r="DV125" t="inlineStr"/>
+      <c r="DW125" t="inlineStr"/>
+      <c r="DX125" t="inlineStr"/>
+      <c r="DY125" t="inlineStr"/>
+      <c r="DZ125" t="inlineStr"/>
+      <c r="EA125" t="inlineStr"/>
+      <c r="EB125" t="inlineStr"/>
+      <c r="EC125" t="inlineStr"/>
+      <c r="ED125" t="inlineStr"/>
+      <c r="EE125" t="inlineStr"/>
+      <c r="EF125" t="inlineStr"/>
+      <c r="EG125" t="inlineStr"/>
+      <c r="EH125" t="inlineStr"/>
+      <c r="EI125" t="inlineStr"/>
+      <c r="EJ125" t="inlineStr"/>
+      <c r="EK125" t="inlineStr"/>
+      <c r="EL125" t="inlineStr"/>
+      <c r="EM125" t="inlineStr"/>
+      <c r="EN125" t="inlineStr"/>
+      <c r="EO125" t="inlineStr"/>
+      <c r="EP125" t="inlineStr"/>
+      <c r="EQ125" t="inlineStr"/>
+      <c r="ER125" t="inlineStr"/>
+      <c r="ES125" t="inlineStr"/>
+      <c r="ET125" t="inlineStr"/>
+      <c r="EU125" t="inlineStr"/>
+      <c r="EV125" t="inlineStr"/>
+      <c r="EW125" t="inlineStr"/>
+      <c r="EX125" t="inlineStr"/>
+      <c r="EY125" t="inlineStr"/>
+      <c r="EZ125" t="inlineStr"/>
+      <c r="FA125" t="inlineStr"/>
+      <c r="FB125" t="inlineStr"/>
+      <c r="FC125" t="inlineStr"/>
+      <c r="FD125" t="inlineStr"/>
+      <c r="FE125" t="inlineStr"/>
+      <c r="FF125" t="inlineStr"/>
+      <c r="FG125" t="inlineStr"/>
+      <c r="FH125" t="inlineStr"/>
+      <c r="FI125" t="inlineStr"/>
+      <c r="FJ125" t="inlineStr"/>
+      <c r="FK125" t="inlineStr"/>
+      <c r="FL125" t="inlineStr"/>
+      <c r="FM125" t="inlineStr"/>
+      <c r="FN125" t="inlineStr"/>
+      <c r="FO125" t="inlineStr"/>
+      <c r="FP125" t="inlineStr"/>
+      <c r="FQ125" t="inlineStr"/>
+      <c r="FR125" t="inlineStr"/>
+      <c r="FS125" t="inlineStr"/>
+      <c r="FT125" t="inlineStr"/>
+      <c r="FU125" t="inlineStr"/>
+      <c r="FV125" t="inlineStr"/>
+      <c r="FW125" t="inlineStr"/>
+      <c r="FX125" t="inlineStr"/>
+      <c r="FY125" t="inlineStr"/>
+      <c r="FZ125" t="inlineStr"/>
+      <c r="GA125" t="inlineStr"/>
+      <c r="GB125" t="inlineStr"/>
+      <c r="GC125" t="inlineStr"/>
+      <c r="GD125" t="inlineStr"/>
+      <c r="GE125" t="inlineStr"/>
+      <c r="GF125" t="inlineStr"/>
+      <c r="GG125" t="inlineStr"/>
+      <c r="GH125" t="inlineStr"/>
+      <c r="GI125" t="inlineStr"/>
+      <c r="GJ125" t="inlineStr"/>
+      <c r="GK125" t="inlineStr"/>
+      <c r="GL125" t="inlineStr"/>
+      <c r="GM125" t="inlineStr"/>
+      <c r="GN125" t="inlineStr"/>
+      <c r="GO125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>8lUzaKf4</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>tCw122Zu</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>oukidja alexandre</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>jZhhxxLu</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>traore ismael</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>AuzyopRB</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>udol matthieu</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>ncoSpPJ3</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>kouao koffi</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>GlPxp8Ek</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>deminguet jessy</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>06rZTKMc</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>hein gauthier</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>21NXX0AU</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>cande fali</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>OKRPP19G</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>jallow ablie</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>v9UFU7UB</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>sane ibou</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>E5Ot0kk3</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>sabaly cheikh tidiane</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Whzw3G5K</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>samassa mamadou</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>KbXo1rjj</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>vargas thibault</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>lIDA7uHl</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>ouaneh peter</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>Wh6NlULE</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>tavares yohan</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>QyXR4UTq</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>kouassi christ owen</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>h2wDEAtM</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>cherni amine</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>xjWxEtds</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>sanna sam</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>0IAHPMVG</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>thomas titouan</t>
+        </is>
+      </c>
+      <c r="AN126" t="inlineStr">
+        <is>
+          <t>2JZ0HH6Q</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>sellouki malik</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>W2tc6ZMa</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>zohi kevin</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>IZHMuCIC</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>doucoure sirine</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr">
+        <is>
+          <t>6D2EWpmi</t>
+        </is>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>asoro joel</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>xdl3kAtK</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>diallo papa amadou</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>tE85H9db</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>nduquidi joseph</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>O8reaWmD</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>sane sadibou</t>
+        </is>
+      </c>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>OADbJzj2</t>
+        </is>
+      </c>
+      <c r="BE126" t="inlineStr">
+        <is>
+          <t>sy pape</t>
+        </is>
+      </c>
+      <c r="BF126" t="inlineStr">
+        <is>
+          <t>EX50xRu9</t>
+        </is>
+      </c>
+      <c r="BG126" t="inlineStr">
+        <is>
+          <t>toure alpha</t>
+        </is>
+      </c>
+      <c r="BH126" t="inlineStr"/>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr">
+        <is>
+          <t>Amfeubd3</t>
+        </is>
+      </c>
+      <c r="BM126" t="inlineStr">
+        <is>
+          <t>adilehou moise</t>
+        </is>
+      </c>
+      <c r="BN126" t="inlineStr">
+        <is>
+          <t>OpjMuJEk</t>
+        </is>
+      </c>
+      <c r="BO126" t="inlineStr">
+        <is>
+          <t>goncalves anthony</t>
+        </is>
+      </c>
+      <c r="BP126" t="inlineStr">
+        <is>
+          <t>zXm9ns79</t>
+        </is>
+      </c>
+      <c r="BQ126" t="inlineStr">
+        <is>
+          <t>hautbois maxime</t>
+        </is>
+      </c>
+      <c r="BR126" t="inlineStr">
+        <is>
+          <t>0K3veiZ5</t>
+        </is>
+      </c>
+      <c r="BS126" t="inlineStr">
+        <is>
+          <t>kokolo williams</t>
+        </is>
+      </c>
+      <c r="BT126" t="inlineStr">
+        <is>
+          <t>h0KBtgkc</t>
+        </is>
+      </c>
+      <c r="BU126" t="inlineStr">
+        <is>
+          <t>martins lois</t>
+        </is>
+      </c>
+      <c r="BV126" t="inlineStr">
+        <is>
+          <t>UBp43Hs9</t>
+        </is>
+      </c>
+      <c r="BW126" t="inlineStr">
+        <is>
+          <t>roye jimmy</t>
+        </is>
+      </c>
+      <c r="BX126" t="inlineStr">
+        <is>
+          <t>px7nJZss</t>
+        </is>
+      </c>
+      <c r="BY126" t="inlineStr">
+        <is>
+          <t>tell jordan</t>
+        </is>
+      </c>
+      <c r="BZ126" t="inlineStr"/>
+      <c r="CA126" t="inlineStr"/>
+      <c r="CB126" t="inlineStr">
+        <is>
+          <t>xdl3kAtK</t>
+        </is>
+      </c>
+      <c r="CC126" t="inlineStr">
+        <is>
+          <t>diallo papa amadou</t>
+        </is>
+      </c>
+      <c r="CD126" t="inlineStr">
+        <is>
+          <t>xdl3kAtK</t>
+        </is>
+      </c>
+      <c r="CE126" t="inlineStr">
+        <is>
+          <t>diallo papa amadou</t>
+        </is>
+      </c>
+      <c r="CF126" t="inlineStr">
+        <is>
+          <t>21NXX0AU</t>
+        </is>
+      </c>
+      <c r="CG126" t="inlineStr">
+        <is>
+          <t>cande fali</t>
+        </is>
+      </c>
+      <c r="CH126" t="inlineStr">
+        <is>
+          <t>6D2EWpmi</t>
+        </is>
+      </c>
+      <c r="CI126" t="inlineStr">
+        <is>
+          <t>asoro joel</t>
+        </is>
+      </c>
+      <c r="CJ126" t="inlineStr">
+        <is>
+          <t>6D2EWpmi</t>
+        </is>
+      </c>
+      <c r="CK126" t="inlineStr">
+        <is>
+          <t>asoro joel</t>
+        </is>
+      </c>
+      <c r="CL126" t="inlineStr">
+        <is>
+          <t>v9UFU7UB</t>
+        </is>
+      </c>
+      <c r="CM126" t="inlineStr">
+        <is>
+          <t>sane ibou</t>
+        </is>
+      </c>
+      <c r="CN126" t="inlineStr">
+        <is>
+          <t>tE85H9db</t>
+        </is>
+      </c>
+      <c r="CO126" t="inlineStr">
+        <is>
+          <t>nduquidi joseph</t>
+        </is>
+      </c>
+      <c r="CP126" t="inlineStr">
+        <is>
+          <t>tE85H9db</t>
+        </is>
+      </c>
+      <c r="CQ126" t="inlineStr">
+        <is>
+          <t>nduquidi joseph</t>
+        </is>
+      </c>
+      <c r="CR126" t="inlineStr">
+        <is>
+          <t>GlPxp8Ek</t>
+        </is>
+      </c>
+      <c r="CS126" t="inlineStr">
+        <is>
+          <t>deminguet jessy</t>
+        </is>
+      </c>
+      <c r="CT126" t="inlineStr"/>
+      <c r="CU126" t="inlineStr"/>
+      <c r="CV126" t="inlineStr"/>
+      <c r="CW126" t="inlineStr"/>
+      <c r="CX126" t="inlineStr"/>
+      <c r="CY126" t="inlineStr"/>
+      <c r="CZ126" t="inlineStr">
+        <is>
+          <t>Amfeubd3</t>
+        </is>
+      </c>
+      <c r="DA126" t="inlineStr">
+        <is>
+          <t>adilehou moise</t>
+        </is>
+      </c>
+      <c r="DB126" t="inlineStr">
+        <is>
+          <t>Amfeubd3</t>
+        </is>
+      </c>
+      <c r="DC126" t="inlineStr">
+        <is>
+          <t>adilehou moise</t>
+        </is>
+      </c>
+      <c r="DD126" t="inlineStr">
+        <is>
+          <t>lIDA7uHl</t>
+        </is>
+      </c>
+      <c r="DE126" t="inlineStr">
+        <is>
+          <t>ouaneh peter</t>
+        </is>
+      </c>
+      <c r="DF126" t="inlineStr">
+        <is>
+          <t>px7nJZss</t>
+        </is>
+      </c>
+      <c r="DG126" t="inlineStr">
+        <is>
+          <t>tell jordan</t>
+        </is>
+      </c>
+      <c r="DH126" t="inlineStr">
+        <is>
+          <t>px7nJZss</t>
+        </is>
+      </c>
+      <c r="DI126" t="inlineStr">
+        <is>
+          <t>tell jordan</t>
+        </is>
+      </c>
+      <c r="DJ126" t="inlineStr">
+        <is>
+          <t>IZHMuCIC</t>
+        </is>
+      </c>
+      <c r="DK126" t="inlineStr">
+        <is>
+          <t>doucoure sirine</t>
+        </is>
+      </c>
+      <c r="DL126" t="inlineStr">
+        <is>
+          <t>h0KBtgkc</t>
+        </is>
+      </c>
+      <c r="DM126" t="inlineStr">
+        <is>
+          <t>martins lois</t>
+        </is>
+      </c>
+      <c r="DN126" t="inlineStr">
+        <is>
+          <t>h0KBtgkc</t>
+        </is>
+      </c>
+      <c r="DO126" t="inlineStr">
+        <is>
+          <t>martins lois</t>
+        </is>
+      </c>
+      <c r="DP126" t="inlineStr">
+        <is>
+          <t>W2tc6ZMa</t>
+        </is>
+      </c>
+      <c r="DQ126" t="inlineStr">
+        <is>
+          <t>zohi kevin</t>
+        </is>
+      </c>
+      <c r="DR126" t="inlineStr">
+        <is>
+          <t>UBp43Hs9</t>
+        </is>
+      </c>
+      <c r="DS126" t="inlineStr">
+        <is>
+          <t>roye jimmy</t>
+        </is>
+      </c>
+      <c r="DT126" t="inlineStr">
+        <is>
+          <t>UBp43Hs9</t>
+        </is>
+      </c>
+      <c r="DU126" t="inlineStr">
+        <is>
+          <t>roye jimmy</t>
+        </is>
+      </c>
+      <c r="DV126" t="inlineStr">
+        <is>
+          <t>2JZ0HH6Q</t>
+        </is>
+      </c>
+      <c r="DW126" t="inlineStr">
+        <is>
+          <t>sellouki malik</t>
+        </is>
+      </c>
+      <c r="DX126" t="inlineStr"/>
+      <c r="DY126" t="inlineStr"/>
+      <c r="DZ126" t="inlineStr"/>
+      <c r="EA126" t="inlineStr"/>
+      <c r="EB126" t="inlineStr"/>
+      <c r="EC126" t="inlineStr"/>
+      <c r="ED126" t="inlineStr"/>
+      <c r="EE126" t="inlineStr"/>
+      <c r="EF126" t="inlineStr"/>
+      <c r="EG126" t="inlineStr"/>
+      <c r="EH126" t="inlineStr"/>
+      <c r="EI126" t="inlineStr"/>
+      <c r="EJ126" t="inlineStr"/>
+      <c r="EK126" t="inlineStr"/>
+      <c r="EL126" t="inlineStr"/>
+      <c r="EM126" t="inlineStr"/>
+      <c r="EN126" t="inlineStr"/>
+      <c r="EO126" t="inlineStr"/>
+      <c r="EP126" t="inlineStr"/>
+      <c r="EQ126" t="inlineStr"/>
+      <c r="ER126" t="inlineStr"/>
+      <c r="ES126" t="inlineStr"/>
+      <c r="ET126" t="inlineStr"/>
+      <c r="EU126" t="inlineStr"/>
+      <c r="EV126" t="inlineStr"/>
+      <c r="EW126" t="inlineStr"/>
+      <c r="EX126" t="inlineStr">
+        <is>
+          <t>0K3veiZ5</t>
+        </is>
+      </c>
+      <c r="EY126" t="inlineStr">
+        <is>
+          <t>kokolo williams</t>
+        </is>
+      </c>
+      <c r="EZ126" t="inlineStr">
+        <is>
+          <t>0K3veiZ5</t>
+        </is>
+      </c>
+      <c r="FA126" t="inlineStr">
+        <is>
+          <t>kokolo williams</t>
+        </is>
+      </c>
+      <c r="FB126" t="inlineStr">
+        <is>
+          <t>h2wDEAtM</t>
+        </is>
+      </c>
+      <c r="FC126" t="inlineStr">
+        <is>
+          <t>cherni amine</t>
+        </is>
+      </c>
+      <c r="FD126" t="inlineStr"/>
+      <c r="FE126" t="inlineStr"/>
+      <c r="FF126" t="inlineStr"/>
+      <c r="FG126" t="inlineStr"/>
+      <c r="FH126" t="inlineStr"/>
+      <c r="FI126" t="inlineStr"/>
+      <c r="FJ126" t="inlineStr"/>
+      <c r="FK126" t="inlineStr"/>
+      <c r="FL126" t="inlineStr"/>
+      <c r="FM126" t="inlineStr"/>
+      <c r="FN126" t="inlineStr"/>
+      <c r="FO126" t="inlineStr"/>
+      <c r="FP126" t="inlineStr"/>
+      <c r="FQ126" t="inlineStr"/>
+      <c r="FR126" t="inlineStr"/>
+      <c r="FS126" t="inlineStr"/>
+      <c r="FT126" t="inlineStr"/>
+      <c r="FU126" t="inlineStr"/>
+      <c r="FV126" t="inlineStr"/>
+      <c r="FW126" t="inlineStr"/>
+      <c r="FX126" t="inlineStr"/>
+      <c r="FY126" t="inlineStr"/>
+      <c r="FZ126" t="inlineStr"/>
+      <c r="GA126" t="inlineStr"/>
+      <c r="GB126" t="inlineStr"/>
+      <c r="GC126" t="inlineStr"/>
+      <c r="GD126" t="inlineStr"/>
+      <c r="GE126" t="inlineStr"/>
+      <c r="GF126" t="inlineStr"/>
+      <c r="GG126" t="inlineStr"/>
+      <c r="GH126" t="inlineStr"/>
+      <c r="GI126" t="inlineStr"/>
+      <c r="GJ126" t="inlineStr"/>
+      <c r="GK126" t="inlineStr"/>
+      <c r="GL126" t="inlineStr"/>
+      <c r="GM126" t="inlineStr"/>
+      <c r="GN126" t="inlineStr"/>
+      <c r="GO126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
